--- a/sources/mercure-galant/mg-vocabulaire-estampes.xlsx
+++ b/sources/mercure-galant/mg-vocabulaire-estampes.xlsx
@@ -16,7 +16,7 @@
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="E37">
+    <comment authorId="0" ref="E36">
       <text>
         <t xml:space="preserve">Je ne comprends pas cette catégorie : un terme spécifique de plus ?
 	-Anne Piéjus
@@ -30,7 +30,7 @@
 	-Anne Piéjus</t>
       </text>
     </comment>
-    <comment authorId="0" ref="E103">
+    <comment authorId="0" ref="E102">
       <text>
         <t xml:space="preserve">En faire une sous-catégorie de "plans et vues"?
 	-Rebecca Bristow</t>
@@ -41,9 +41,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="262">
-  <si>
-    <t>identifiant (optionnel et modifiable)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="527">
+  <si>
+    <t>uuid SHERLOCK</t>
   </si>
   <si>
     <t>categorie</t>
@@ -61,769 +61,1564 @@
     <t>equivalent getty aat</t>
   </si>
   <si>
+    <t>bc1b272c-eebc-47f2-87f0-94bbf3a3aa3f</t>
+  </si>
+  <si>
     <t>Thématiques</t>
   </si>
   <si>
+    <t>ffc871a1-2724-44a1-8e56-a5a2dda83e98</t>
+  </si>
+  <si>
     <t>Allégorie et rhétorique</t>
   </si>
   <si>
+    <t>7b38fe22-5a38-4e80-a047-664d9ed270a4</t>
+  </si>
+  <si>
     <t>Emblématique</t>
   </si>
   <si>
+    <t>397bade9-bcf9-4c6a-a7ab-9b11a39ed02e</t>
+  </si>
+  <si>
     <t>Allégorie amoureuse</t>
   </si>
   <si>
+    <t>c2b58b54-5f40-4c01-a48f-8ba141dad167</t>
+  </si>
+  <si>
     <t>Énigme en figure</t>
   </si>
   <si>
+    <t>4c4ffe8a-9e2b-4119-b4a8-1ef616025aec</t>
+  </si>
+  <si>
     <t>Alphabets et écritures codées</t>
   </si>
   <si>
+    <t>65f74994-e84a-4f82-953c-d9cb58236aca</t>
+  </si>
+  <si>
     <t>Cartes allégoriques ou de galanterie</t>
   </si>
   <si>
-    <t>Arts, sciences et techniques</t>
-  </si>
-  <si>
-    <t>Génie civil</t>
+    <t>0d240e92-1939-41e1-a3e9-0cc54f83c0b9</t>
+  </si>
+  <si>
+    <t>Beaux-Arts</t>
+  </si>
+  <si>
+    <t>145a3c95-ba8f-4c40-8b51-b8d7704d6d02</t>
+  </si>
+  <si>
+    <t>Sculpture</t>
+  </si>
+  <si>
+    <t>0b565133-ad0d-4896-a636-e317f6b206ea</t>
+  </si>
+  <si>
+    <t>Peinture</t>
+  </si>
+  <si>
+    <t>89c57205-cf35-4198-8e22-306d46aaaffa</t>
+  </si>
+  <si>
+    <t>Arts et sciences</t>
+  </si>
+  <si>
+    <t>9f9be815-2cad-4f36-b1c8-6c8fb62a6309</t>
   </si>
   <si>
     <t>Anatomie</t>
   </si>
   <si>
+    <t>53779dd5-59a3-4d18-9f53-58d81302aee5</t>
+  </si>
+  <si>
+    <t>géographie</t>
+  </si>
+  <si>
+    <t>c8ba2c29-1a43-4fb7-a32a-14182e8e509d</t>
+  </si>
+  <si>
     <t>Astrologie [regrouper si besoin avec astronomie ; si thème royal, classer comme emblème]</t>
   </si>
   <si>
+    <t>b15df10c-078f-48a6-9a12-5b65b5359c6f</t>
+  </si>
+  <si>
     <t>Géométrie</t>
   </si>
   <si>
-    <t>Mécanique</t>
+    <t>f382ec49-ac8c-4408-b6a0-f454888470e3</t>
+  </si>
+  <si>
+    <t>Mécanique (y compris hydraulique, horlogerie)</t>
+  </si>
+  <si>
+    <t>305d47ad-f560-47a5-b5a8-c0ed0631fcdb</t>
   </si>
   <si>
     <t>Archéologie</t>
   </si>
   <si>
+    <t>a1d1fc5e-a387-43f9-94bd-a76a19b3d54a</t>
+  </si>
+  <si>
     <t>Architecture</t>
   </si>
   <si>
+    <t>ca259090-df0c-4bcd-96be-505d2f3a561c</t>
+  </si>
+  <si>
     <t>Architecture navale</t>
   </si>
   <si>
+    <t>f1801fcf-8144-4e0d-a399-ea5c58e7c978</t>
+  </si>
+  <si>
     <t>Astronomie</t>
   </si>
   <si>
+    <t>3b704b9a-9082-4638-88dc-bc0afe040d7a</t>
+  </si>
+  <si>
     <t>Musique</t>
   </si>
   <si>
+    <t>4e5e5c1a-4421-47d4-8234-b81cba5ccc3b</t>
+  </si>
+  <si>
     <t>Optique</t>
   </si>
   <si>
-    <t>Horlogerie</t>
+    <t>b558bf79-7edf-4677-959d-8e1fe011e12f</t>
   </si>
   <si>
     <t>Zoologie</t>
   </si>
   <si>
+    <t>aac3ea31-d787-4648-af83-77089aedf969</t>
+  </si>
+  <si>
     <t>Décor</t>
   </si>
   <si>
+    <t>e457afad-9d51-4b6b-9aea-95190de29622</t>
+  </si>
+  <si>
     <t>Objets décoratifs et d’apparat [chaises à porteurs, pagodes chinoises, cadeaux diplomatiques…]</t>
   </si>
   <si>
+    <t>63960dac-608b-410c-a036-23d2146c56f7</t>
+  </si>
+  <si>
     <t>Décor éphémère</t>
   </si>
   <si>
+    <t>c7f74823-6b53-451e-9c86-7163b1828242</t>
+  </si>
+  <si>
     <t>Plan ou description de fête</t>
   </si>
   <si>
+    <t>f56821ec-5e3f-44ec-914b-205e16ad42fc</t>
+  </si>
+  <si>
     <t>Décor de spectacle</t>
   </si>
   <si>
+    <t>c6cb77e6-df09-462a-9f32-f41c54932442</t>
+  </si>
+  <si>
     <t>Apparat</t>
   </si>
   <si>
+    <t>ea2540cc-f763-45c6-8e06-30b5cfa84c6e</t>
+  </si>
+  <si>
     <t>Décor de théâtre</t>
   </si>
   <si>
+    <t>7b0f081e-36f9-45dd-8a48-7096abc51889</t>
+  </si>
+  <si>
+    <t>f20a8f17-e80a-4591-b139-3ea95f762fb5</t>
+  </si>
+  <si>
     <t>Emblème</t>
   </si>
   <si>
+    <t>f5e36696-6d0c-422a-899f-adeae3c71dbf</t>
+  </si>
+  <si>
     <t>Mythologie</t>
   </si>
   <si>
+    <t>518da64f-d966-46aa-b5b3-115598ec7068</t>
+  </si>
+  <si>
     <t>Mythologie gréco-romaine</t>
   </si>
   <si>
+    <t>32ffaebc-b0cf-4b34-8f09-919172469a91</t>
+  </si>
+  <si>
     <t>Bacchus</t>
   </si>
   <si>
+    <t>93ac1926-47ec-4152-a76c-8366c382f482</t>
+  </si>
+  <si>
     <t>Neptune</t>
   </si>
   <si>
+    <t>cc57ce37-6d46-46c5-a273-deed2878df13</t>
+  </si>
+  <si>
     <t>Prométhée</t>
   </si>
   <si>
+    <t>08c4e435-041c-4130-a208-74ccd3e6b1dc</t>
+  </si>
+  <si>
     <t>Protée</t>
   </si>
   <si>
+    <t>cc5128ab-60c8-44f8-af53-23ec05475cdf</t>
+  </si>
+  <si>
     <t>Vénus</t>
   </si>
   <si>
-    <t>Personnages</t>
+    <t>dbd9ee72-9996-46ec-aed3-ac8635035130</t>
   </si>
   <si>
     <t>Ascagne</t>
   </si>
   <si>
+    <t>79e35aa8-43ef-4b22-9a2e-3bb29b443205</t>
+  </si>
+  <si>
     <t>Géants</t>
   </si>
   <si>
+    <t>dba0c5d0-b78d-4a7b-9b0c-93e9d52c93b1</t>
+  </si>
+  <si>
     <t>Io</t>
   </si>
   <si>
+    <t>1617f639-9650-468d-bd55-d466d556acc3</t>
+  </si>
+  <si>
     <t>Thèmes mythologiques</t>
   </si>
   <si>
+    <t>65cd719c-b518-43f2-90ce-cf586be3bb9f</t>
+  </si>
+  <si>
     <t>Chaos</t>
   </si>
   <si>
+    <t>80a26e69-a39a-474a-a9fd-c7144b0ab7fd</t>
+  </si>
+  <si>
     <t>Songe</t>
   </si>
   <si>
+    <t>f192c429-79da-4741-8dc8-4189ac828f4c</t>
+  </si>
+  <si>
     <t>Amphyon</t>
   </si>
   <si>
+    <t>5d468f2c-8cbb-4bcf-9af3-cf004619ae2c</t>
+  </si>
+  <si>
     <t>Antée</t>
   </si>
   <si>
+    <t>cc575a53-82c9-4c85-b06c-35ca7343401a</t>
+  </si>
+  <si>
+    <t>82670c25-4811-41eb-ae9d-c4531dbdef32</t>
+  </si>
+  <si>
     <t>Bellérophon</t>
   </si>
   <si>
+    <t>22fe37c2-0e31-4461-af1b-549f6a569fc7</t>
+  </si>
+  <si>
     <t>Mercure ;</t>
   </si>
   <si>
+    <t>bd22952a-51dd-412f-8765-06862ab28afb</t>
+  </si>
+  <si>
     <t>Clythie</t>
   </si>
   <si>
+    <t>527104d8-b3d7-4ee8-b60f-92e07c6ad2d7</t>
+  </si>
+  <si>
     <t>Daphné</t>
   </si>
   <si>
+    <t>91ed7840-151e-4953-b318-8f05359c2bdc</t>
+  </si>
+  <si>
     <t>Dragon du jardin des Hespérides</t>
   </si>
   <si>
+    <t>0e8fa5dc-eaab-4060-8926-8948ee9be29a</t>
+  </si>
+  <si>
     <t>Europe;</t>
   </si>
   <si>
+    <t>b331fbc4-4ab2-4390-b043-1f51f6939825</t>
+  </si>
+  <si>
     <t>Eurydice</t>
   </si>
   <si>
+    <t>623450a3-ea59-4a82-be1a-2c4c0459791a</t>
+  </si>
+  <si>
     <t>Hercule;</t>
   </si>
   <si>
+    <t>e89a653a-fcb9-40c6-962a-b06051d1b63d</t>
+  </si>
+  <si>
     <t>Hésione</t>
   </si>
   <si>
+    <t>a5cef34e-94db-4172-bce1-ae5405be5bc4</t>
+  </si>
+  <si>
     <t>Hyacinthe</t>
   </si>
   <si>
+    <t>d2016fdc-9676-4ca0-8ee6-560276f6528b</t>
+  </si>
+  <si>
     <t>Icare</t>
   </si>
   <si>
+    <t>ae58c79c-b340-4bbc-a92e-612ab3a9ead2</t>
+  </si>
+  <si>
     <t>Ino</t>
   </si>
   <si>
+    <t>6227c670-be60-4c84-9f1d-9c7847be1d9e</t>
+  </si>
+  <si>
     <t>Janus ;</t>
   </si>
   <si>
+    <t>5832deac-95a1-41e1-97ba-75d53d5793fe</t>
+  </si>
+  <si>
     <t>Jason</t>
   </si>
   <si>
+    <t>615adf7b-c6d8-444c-b3b1-7c49bfd2a51b</t>
+  </si>
+  <si>
     <t>Argonautes ;</t>
   </si>
   <si>
+    <t>13ba4774-9c3b-43d1-a766-a8566ce805f3</t>
+  </si>
+  <si>
     <t>Jupiter</t>
   </si>
   <si>
+    <t>d0a6ffcf-6541-42ee-ad02-7177fb07c142</t>
+  </si>
+  <si>
     <t>Leda</t>
   </si>
   <si>
+    <t>d24feffd-1b58-4a43-b79d-e8edfc1228e0</t>
+  </si>
+  <si>
     <t>Mars</t>
   </si>
   <si>
+    <t>475c3986-16ac-4148-a596-403155bac88e</t>
+  </si>
+  <si>
     <t>Marsyas</t>
   </si>
   <si>
+    <t>6eda1018-31af-41ab-bda6-822e8dfc78fe</t>
+  </si>
+  <si>
     <t>Médée</t>
   </si>
   <si>
+    <t>04f8a7d9-699b-4bb4-9bd9-444c0f6261da</t>
+  </si>
+  <si>
     <t>Méduse</t>
   </si>
   <si>
+    <t>5f1593f0-a5f1-4949-b2b4-c0afda23cf74</t>
+  </si>
+  <si>
     <t>Memnon</t>
   </si>
   <si>
+    <t>08537b64-3c80-4d12-b849-8232c11114b6</t>
+  </si>
+  <si>
     <t>Minerve</t>
   </si>
   <si>
+    <t>30eb1d30-29b5-4f2a-be97-aa34b2bd30a3</t>
+  </si>
+  <si>
     <t>Narcisse</t>
   </si>
   <si>
+    <t>4af283b1-ce92-466e-a285-a4d7a83565bd</t>
+  </si>
+  <si>
     <t>Neptune ;</t>
   </si>
   <si>
+    <t>3c73f3dc-68a6-47c6-8cb7-cd3e5d92055b</t>
+  </si>
+  <si>
     <t>Niobé</t>
   </si>
   <si>
+    <t>801965f9-9b54-475b-b85b-83e5dc8119ef</t>
+  </si>
+  <si>
     <t>Orythie</t>
   </si>
   <si>
+    <t>74d5fc83-da6e-43c9-a723-32228ae8054f</t>
+  </si>
+  <si>
     <t>Pallas;</t>
   </si>
   <si>
+    <t>5eb9416e-b7fc-4562-b213-4d6cf226effc</t>
+  </si>
+  <si>
     <t>Pandore</t>
   </si>
   <si>
+    <t>2e4f28e6-5421-41ca-bdc5-05aa6142ae71</t>
+  </si>
+  <si>
     <t>Phaéton</t>
   </si>
   <si>
+    <t>d39a9931-e2dc-4aef-ab2d-9d2f3b4aa61f</t>
+  </si>
+  <si>
+    <t>f3732fc7-aa9d-44d8-8130-e353db617ced</t>
+  </si>
+  <si>
     <t>Proserpine</t>
   </si>
   <si>
+    <t>33c16888-7c8a-4a89-bd5a-021921eb0dd9</t>
+  </si>
+  <si>
+    <t>2aca5cbc-88f5-4f0e-9b05-2248f0cbd8e1</t>
+  </si>
+  <si>
     <t>Pyrame et Thisbé ;</t>
   </si>
   <si>
+    <t>c1f957a7-c79a-48ee-b3b6-3d4d49851a14</t>
+  </si>
+  <si>
     <t>Remus et Romulus</t>
   </si>
   <si>
+    <t>d270b620-38ba-43c0-8350-f1e0745f23db</t>
+  </si>
+  <si>
     <t>Salmonée</t>
   </si>
   <si>
+    <t>f27f1212-69c7-4fbf-83f5-e049fc246466</t>
+  </si>
+  <si>
     <t>Serpent d'Epidaure</t>
   </si>
   <si>
+    <t>2669eb6b-a088-4f4f-93eb-777e39b1abff</t>
+  </si>
+  <si>
     <t>Taureau aux pieds d'airain;</t>
   </si>
   <si>
+    <t>40e9e536-6f84-4894-b9e6-39d0eb6f2df7</t>
+  </si>
+  <si>
+    <t>a8110a8d-c0e8-4cf6-aa0f-44205100f56d</t>
+  </si>
+  <si>
     <t>Vulcain</t>
   </si>
   <si>
+    <t>0eb86e83-0e1f-4766-b96f-fca1d7d9d587</t>
+  </si>
+  <si>
     <t>Allégorie et Rhétorique</t>
   </si>
   <si>
+    <t>c65570b0-2d59-4da1-9bbe-b677535f37d4</t>
+  </si>
+  <si>
     <t>Figures allégoriques</t>
   </si>
   <si>
+    <t>d9472929-7d74-472b-b0e4-f5a8db308777</t>
+  </si>
+  <si>
     <t>Victoire</t>
   </si>
   <si>
+    <t>0ea23c72-d61b-47e6-a9c8-6141daac5333</t>
+  </si>
+  <si>
     <t>Renommée</t>
   </si>
   <si>
+    <t>9a7371f3-7ea9-4601-b153-d2e4bc41839a</t>
+  </si>
+  <si>
     <t>Portraits et généalogie</t>
   </si>
   <si>
+    <t>a5c88f23-61c0-4f5d-9462-4a195aabdb83</t>
+  </si>
+  <si>
     <t>portraits</t>
   </si>
   <si>
+    <t>ed1ef934-8d85-4748-aa7f-5b57139a041a</t>
+  </si>
+  <si>
     <t>tables généalogiques</t>
   </si>
   <si>
+    <t>824d0bc5-2b7d-49bc-b6eb-e628bf1132de</t>
+  </si>
+  <si>
     <t>Topographie</t>
   </si>
   <si>
+    <t>b5d30e99-ee89-4d03-94a3-86bdb7a977c4</t>
+  </si>
+  <si>
     <t>Architecture navale [galères, etc.]</t>
   </si>
   <si>
+    <t>e7eb5069-2f2c-4f8d-b743-97a2b76cc945</t>
+  </si>
+  <si>
     <t>Plans et vues</t>
   </si>
   <si>
+    <t>ef7a609b-6ef7-48fe-b6b3-eb8945046782</t>
+  </si>
+  <si>
     <t>Plan de bâtiment [église, etc.]</t>
   </si>
   <si>
+    <t>b411d68d-b9bb-4902-9a19-224628a96dd4</t>
+  </si>
+  <si>
+    <t>2da149dc-0857-4697-a71a-5ddb611d0809</t>
+  </si>
+  <si>
     <t>Plans et vues militaires</t>
   </si>
   <si>
+    <t>daff59ce-53a3-477b-aca6-0b3faaa530c7</t>
+  </si>
+  <si>
     <t>Sièges et plans d'ouvrages militaires</t>
   </si>
   <si>
-    <t>Plans et descriptions militaires</t>
+    <t>f9aa5f40-41c0-40e0-9b28-1df176a7ac26</t>
+  </si>
+  <si>
+    <t>Listes et descriptions militaires</t>
+  </si>
+  <si>
+    <t>73ea466d-4a95-48d3-9436-ec68408d51d0</t>
   </si>
   <si>
     <t>Plans de bâtiments</t>
   </si>
   <si>
+    <t>99526e57-8ece-4e07-9c61-dbf0889bb795</t>
+  </si>
+  <si>
     <t>Vie militaire</t>
   </si>
   <si>
+    <t>bdd01b92-1aa9-42f7-90ba-95a5a4308f91</t>
+  </si>
+  <si>
     <t>Vie sociale</t>
   </si>
   <si>
+    <t>2b63625d-9752-49f6-b6d3-437a036ee2a0</t>
+  </si>
+  <si>
     <t>Deuil</t>
   </si>
   <si>
+    <t>a789783e-c81a-475f-a7a5-94cfaf7d9719</t>
+  </si>
+  <si>
     <t>Mode vestimentaire</t>
   </si>
   <si>
+    <t>0f21ee7c-4c02-4fda-aa06-1e4dd0328a86</t>
+  </si>
+  <si>
     <t>Noces</t>
   </si>
   <si>
+    <t>d2264197-648e-4baa-a84a-6ec413487d6f</t>
+  </si>
+  <si>
     <t>Objets</t>
   </si>
   <si>
+    <t>50ba2fb1-7ced-4890-9516-a22cdb9d5a04</t>
+  </si>
+  <si>
     <t>obélisque</t>
   </si>
   <si>
     <t>http://vocab.getty.edu/page/aat/300007021</t>
   </si>
   <si>
+    <t>be496108-cdca-4b8d-8a98-25014defaa1a</t>
+  </si>
+  <si>
     <t>Afrique</t>
   </si>
   <si>
+    <t>cae379a4-e9c5-482f-bb6d-22fbfb66c768</t>
+  </si>
+  <si>
     <t>alphabet</t>
   </si>
   <si>
+    <t>45de3b9e-b1d7-4af5-a63a-6daf05050cfa</t>
+  </si>
+  <si>
     <t>anémomètre</t>
   </si>
   <si>
+    <t>4fd063c5-a826-4c9b-a396-a10a9a8d7b38</t>
+  </si>
+  <si>
     <t>Annonciation</t>
   </si>
   <si>
+    <t>03007121-060a-42f3-88e2-bcb903419bb5</t>
+  </si>
+  <si>
     <t>apothicaire;</t>
   </si>
   <si>
+    <t>af8d50c9-e044-4fc8-8332-e9a1655afc88</t>
+  </si>
+  <si>
     <t>arc de triomphe</t>
   </si>
   <si>
+    <t>ba74c06f-883c-48c2-b90f-275ada89728c</t>
+  </si>
+  <si>
     <t>armée navale</t>
   </si>
   <si>
+    <t>1f6cd3bf-aa9c-493d-a5a6-12222b821a32</t>
+  </si>
+  <si>
     <t>armoiries</t>
   </si>
   <si>
+    <t>04a250aa-698e-4da1-a755-3821e9f932dc</t>
+  </si>
+  <si>
     <t>bal</t>
   </si>
   <si>
+    <t>acd18adc-165b-4607-b7e4-ddbcac8bc042</t>
+  </si>
+  <si>
     <t>baleine</t>
   </si>
   <si>
+    <t>5e7f9e55-4397-45b0-af9d-a88a5417a7d5</t>
+  </si>
+  <si>
     <t>table de banquet</t>
   </si>
   <si>
+    <t>2ced635a-864d-4101-9384-ebc988ad4911</t>
+  </si>
+  <si>
     <t>bataille</t>
   </si>
   <si>
+    <t>c178fca4-be40-478b-a406-4af02f18e7bc</t>
+  </si>
+  <si>
     <t>bâtiment</t>
   </si>
   <si>
+    <t>ca6ebbde-1dfb-42df-9690-c8c16fbb694e</t>
+  </si>
+  <si>
     <t>binocle</t>
   </si>
   <si>
+    <t>2c9bc3cf-9dc9-4df3-bba6-0a8839a7ef54</t>
+  </si>
+  <si>
     <t>bombe</t>
   </si>
   <si>
+    <t>52fcef1b-9893-4580-97c4-052a90baaf24</t>
+  </si>
+  <si>
     <t>bouclier</t>
   </si>
   <si>
+    <t>fc801a7f-7270-42f0-a77c-954bbe77a543</t>
+  </si>
+  <si>
     <t>boutique ou atelier</t>
   </si>
   <si>
+    <t>2ddc28af-56d8-422a-b581-acc0e4c293b1</t>
+  </si>
+  <si>
     <t>cadran ou horloge ;</t>
   </si>
   <si>
+    <t>fbff841b-0bf6-496a-a549-dc88e3f8937d</t>
+  </si>
+  <si>
     <t>camera obscura</t>
   </si>
   <si>
+    <t>f76ba55b-346c-4c9e-9932-407121bf8927</t>
+  </si>
+  <si>
     <t>camp militaire</t>
   </si>
   <si>
+    <t>396013ed-9d7a-41b6-8465-0667983af2ba</t>
+  </si>
+  <si>
     <t>canal</t>
   </si>
   <si>
+    <t>ae2eaec3-f422-4dd1-b66f-88377bcbbd2b</t>
+  </si>
+  <si>
     <t>canon</t>
   </si>
   <si>
+    <t>b57bf234-4e26-427b-a62e-fa3eee5890dc</t>
+  </si>
+  <si>
     <t>carrousel</t>
   </si>
   <si>
+    <t>37698771-9bc3-43db-a1da-5444ddb38644</t>
+  </si>
+  <si>
     <t>cénotaphe ;</t>
   </si>
   <si>
+    <t>65535f70-d05e-4f0b-9680-4061fb89070a</t>
+  </si>
+  <si>
     <t>cercle</t>
   </si>
   <si>
+    <t>eb8e2fbd-8608-47dd-bd41-1cde1c255c3b</t>
+  </si>
+  <si>
     <t>chapelle;</t>
   </si>
   <si>
+    <t>376d071d-41bb-4b0a-906e-c400ea4fd57d</t>
+  </si>
+  <si>
     <t>char</t>
   </si>
   <si>
+    <t>62118ae3-b0a8-4e17-b602-cb141dbc294e</t>
+  </si>
+  <si>
     <t>château</t>
   </si>
   <si>
+    <t>54ee474a-c6c7-4657-a616-dbc97ff7a9ef</t>
+  </si>
+  <si>
     <t>chirurgien;</t>
   </si>
   <si>
+    <t>3050bd05-5342-4b9b-b25b-853095bb4cec</t>
+  </si>
+  <si>
     <t>citadelle;</t>
   </si>
   <si>
+    <t>b16a9985-c25a-4acd-9850-526948756615</t>
+  </si>
+  <si>
     <t>cloche</t>
   </si>
   <si>
+    <t>3617d7d5-8fb6-453d-8a83-7a0c39ba56cd</t>
+  </si>
+  <si>
     <t>coiffe</t>
   </si>
   <si>
+    <t>03ae9e0b-6d2b-4009-ad22-fa1ee5f08594</t>
+  </si>
+  <si>
     <t>combat mythologique;</t>
   </si>
   <si>
+    <t>8c50712e-aa24-402e-b84d-296ec70cf7b0</t>
+  </si>
+  <si>
     <t>combat naval</t>
   </si>
   <si>
+    <t>994ab966-ccb6-4399-94e2-f65ec57d59da</t>
+  </si>
+  <si>
     <t>combles</t>
   </si>
   <si>
+    <t>a5126cae-8091-4bb4-8102-2526e835cc80</t>
+  </si>
+  <si>
     <t>comète ;</t>
   </si>
   <si>
+    <t>c1f030d0-f5ed-4413-8e54-0ef1429fca4c</t>
+  </si>
+  <si>
     <t>coq ;</t>
   </si>
   <si>
+    <t>6006e379-ce6b-44d4-9476-8d5434be888c</t>
+  </si>
+  <si>
     <t>coquillage</t>
   </si>
   <si>
+    <t>951e3283-7421-44ed-9685-973883936e30</t>
+  </si>
+  <si>
     <t>corne ;</t>
   </si>
   <si>
+    <t>a81657ab-7eab-43eb-8da1-fb97c5ca2b66</t>
+  </si>
+  <si>
     <t>croix</t>
   </si>
   <si>
+    <t>27487aa8-4e72-49d4-aa8d-c0439654a016</t>
+  </si>
+  <si>
     <t>cube</t>
   </si>
   <si>
+    <t>37ed175f-4f83-4720-987f-9055591c344a</t>
+  </si>
+  <si>
     <t>drapeau ou étendard</t>
   </si>
   <si>
+    <t>59b92f6a-2531-45e3-9762-63b36785bf0c</t>
+  </si>
+  <si>
     <t>écorce gravée;</t>
   </si>
   <si>
+    <t>7a6de221-b473-446a-83a2-e999f701d15a</t>
+  </si>
+  <si>
     <t>écriture codée;</t>
   </si>
   <si>
+    <t>70ae05d3-9586-47d5-8571-600897d82369</t>
+  </si>
+  <si>
     <t>église</t>
   </si>
   <si>
+    <t>f578e35d-3c41-4543-b5d3-ac873fc57548</t>
+  </si>
+  <si>
     <t>emblème</t>
   </si>
   <si>
+    <t>39fb6874-aa97-4702-8d80-5dcef3cd23ea</t>
+  </si>
+  <si>
     <t>énigme en figure;</t>
   </si>
   <si>
+    <t>a17e6bee-16d0-40f7-970f-c1301f13b603</t>
+  </si>
+  <si>
     <t>Épée, fer, lance</t>
   </si>
   <si>
+    <t>c79ea891-ddfa-4ac8-82b4-fd92544625cd</t>
+  </si>
+  <si>
     <t>épître</t>
   </si>
   <si>
+    <t>89667693-f0b6-470e-adb5-d3a6d510e5bc</t>
+  </si>
+  <si>
     <t>équipement militaire</t>
   </si>
   <si>
+    <t>7e2a9191-e0f4-4c2a-9485-f83ad0017cb8</t>
+  </si>
+  <si>
     <t>étendard</t>
   </si>
   <si>
+    <t>4abab260-9ecd-49b1-a3c0-9b847ebee46e</t>
+  </si>
+  <si>
     <t>étoile ;</t>
   </si>
   <si>
+    <t>2bb5b78b-820a-41d5-95f8-72333e357ba2</t>
+  </si>
+  <si>
     <t>Fer VOIR Épée</t>
   </si>
   <si>
+    <t>35ed576c-5ced-4d40-99cf-b8f7d0e395cd</t>
+  </si>
+  <si>
     <t>fer, lance ou épée ;</t>
   </si>
   <si>
+    <t>b90673b0-b35f-446b-b690-1d31b272667e</t>
+  </si>
+  <si>
     <t>fête ;</t>
   </si>
   <si>
+    <t>3aca1d93-c5b7-4835-9fc9-d9cf49f23018</t>
+  </si>
+  <si>
     <t>feu d’artifice</t>
   </si>
   <si>
+    <t>00de0dda-daa8-4221-b5c6-80ce733c688a</t>
+  </si>
+  <si>
     <t>figure géométrique</t>
   </si>
   <si>
+    <t>6d8858a0-0cdc-4ddc-8d09-a45816487717</t>
+  </si>
+  <si>
     <t>fœtus</t>
   </si>
   <si>
+    <t>38eb29d5-be81-4694-b3f9-d63dd3e09eeb</t>
+  </si>
+  <si>
     <t>fontaine;</t>
   </si>
   <si>
+    <t>ea884359-c307-4e61-913f-2d9de393f2ff</t>
+  </si>
+  <si>
     <t>forteresse</t>
   </si>
   <si>
+    <t>873e0883-141b-4200-9693-dd9ed339f36e</t>
+  </si>
+  <si>
     <t>Forteresse VOIR Citadelle</t>
   </si>
   <si>
+    <t>aa173e32-6422-4d09-b78c-1923f5dab1a2</t>
+  </si>
+  <si>
     <t>galère</t>
   </si>
   <si>
+    <t>edeb7ed4-31f9-444c-af29-1e4a9172ac72</t>
+  </si>
+  <si>
     <t>géant</t>
   </si>
   <si>
+    <t>9c993c3f-f1be-43e4-bbe0-7c922e5d26a1</t>
+  </si>
+  <si>
     <t>généalogie;</t>
   </si>
   <si>
+    <t>b5cbde4b-d312-48f6-8122-44d479089c26</t>
+  </si>
+  <si>
     <t>gigantomachie</t>
   </si>
   <si>
+    <t>565e4439-74a4-4917-99d9-dfcc3a76ce21</t>
+  </si>
+  <si>
     <t>globe terrestre</t>
   </si>
   <si>
+    <t>0cb928b2-7b6f-4908-8e9c-0c197c19ce45</t>
+  </si>
+  <si>
     <t>gondole ;</t>
   </si>
   <si>
+    <t>8d08f1c9-6f23-4993-928d-4cf749598db7</t>
+  </si>
+  <si>
     <t>grelot</t>
   </si>
   <si>
+    <t>3e8f3cbd-b2b4-4837-adc1-1082a888ffae</t>
+  </si>
+  <si>
     <t>grenade ;</t>
   </si>
   <si>
+    <t>9aeb222e-6b1c-4729-9727-7db96b211067</t>
+  </si>
+  <si>
     <t>île</t>
   </si>
   <si>
+    <t>d3dce339-25e5-4111-a050-b7b5536bd59a</t>
+  </si>
+  <si>
     <t>jardin ;</t>
   </si>
   <si>
+    <t>51189b9f-cfaf-4c01-98a9-d77d920b18c7</t>
+  </si>
+  <si>
     <t>jetons</t>
   </si>
   <si>
+    <t>8a77767a-d562-4f14-b3c7-e7e61601cb42</t>
+  </si>
+  <si>
     <t>lac ;</t>
   </si>
   <si>
+    <t>111f765d-7a77-491c-a43f-1ae8e73f72b8</t>
+  </si>
+  <si>
     <t>Lance VOIR Épée</t>
   </si>
   <si>
+    <t>5bcc849e-3526-49fc-aa48-5248326efff7</t>
+  </si>
+  <si>
     <t>lentille</t>
   </si>
   <si>
+    <t>ddbce867-b97a-4ccf-b9c3-952816213139</t>
+  </si>
+  <si>
     <t>lettre en chiffres</t>
   </si>
   <si>
+    <t>043d8a11-0aed-4da6-b411-13b05d3d3e4c</t>
+  </si>
+  <si>
     <t>Libéralité</t>
   </si>
   <si>
+    <t>a0c6c3dd-d877-4b01-8341-080c8056ea0e</t>
+  </si>
+  <si>
     <t>loterie</t>
   </si>
   <si>
+    <t>fac3e15d-aa28-4666-bbd2-8a7f7f51f2ff</t>
+  </si>
+  <si>
     <t>lunette d'optique</t>
   </si>
   <si>
+    <t>01d08a1a-34ab-46f3-a97e-51b5bac7097d</t>
+  </si>
+  <si>
+    <t>Machines</t>
+  </si>
+  <si>
+    <t>e76eb366-e02b-40b8-bca2-18e36e87ae65</t>
+  </si>
+  <si>
     <t>machine hydraulique</t>
   </si>
   <si>
+    <t>8d9f0722-6962-47df-8d1c-1c36641912ae</t>
+  </si>
+  <si>
     <t>maison ;</t>
   </si>
   <si>
+    <t>3fe7f4ce-2c05-49db-95f7-7771f1f04b82</t>
+  </si>
+  <si>
     <t>marin</t>
   </si>
   <si>
+    <t>11c0f99e-cf94-468f-a8f0-e687bde05844</t>
+  </si>
+  <si>
     <t>mascarade</t>
   </si>
   <si>
+    <t>5638ca99-37fa-4aa9-89bc-baf9c7f91f87</t>
+  </si>
+  <si>
     <t>mausolée</t>
   </si>
   <si>
+    <t>24aee532-c740-4232-bb6c-c66cf1f3f432</t>
+  </si>
+  <si>
     <t>médaille</t>
   </si>
   <si>
+    <t>c0445afb-6d05-42d2-9e2e-d5ab05dad8fd</t>
+  </si>
+  <si>
     <t>médecin;</t>
   </si>
   <si>
+    <t>5c5be69f-971b-4757-a7a7-3ecd3d18fa0b</t>
+  </si>
+  <si>
     <t>médecine</t>
   </si>
   <si>
+    <t>7b097459-6b9f-4c6d-aa62-9fe72ead5884</t>
+  </si>
+  <si>
     <t>météore</t>
   </si>
   <si>
+    <t>543bdfa3-29d1-441c-8aa1-08bb2c197a6c</t>
+  </si>
+  <si>
     <t>monnaie</t>
   </si>
   <si>
+    <t>86f3acb1-21c9-4021-9111-47e8ee238a7a</t>
+  </si>
+  <si>
     <t>monstre ;</t>
   </si>
   <si>
+    <t>ecfc7d56-a698-4dce-93c6-cc23ba6b8501</t>
+  </si>
+  <si>
     <t>montagne ;</t>
   </si>
   <si>
+    <t>366f797e-3a4c-46f7-84a2-35773b2aa5d3</t>
+  </si>
+  <si>
     <t>montre</t>
   </si>
   <si>
+    <t>1eef3526-bdfb-41c8-a20a-b024e7f4ee9a</t>
+  </si>
+  <si>
     <t>mosaïque</t>
   </si>
   <si>
+    <t>66bbb701-b1fe-44f1-867e-b123e54e986e</t>
+  </si>
+  <si>
     <t>mouton</t>
   </si>
   <si>
+    <t>5e2d692f-1e24-4568-96c3-523b432584f8</t>
+  </si>
+  <si>
     <t>noce;</t>
   </si>
   <si>
+    <t>1cdf6755-d723-4cd0-9f25-6ea8b21d9927</t>
+  </si>
+  <si>
     <t>notation musicale;</t>
   </si>
   <si>
+    <t>66cc3d7d-eab6-4791-a55c-a4cb5c80f2b9</t>
+  </si>
+  <si>
     <t>œuf</t>
   </si>
   <si>
+    <t>920c500b-9125-4838-b621-8cad20cf4936</t>
+  </si>
+  <si>
     <t>officine</t>
   </si>
   <si>
+    <t>2ed94d4d-3431-4d03-a852-1069506c54d3</t>
+  </si>
+  <si>
     <t>opéra;</t>
   </si>
   <si>
+    <t>116719b8-5713-4732-8305-10bf461a8808</t>
+  </si>
+  <si>
     <t>orientation</t>
   </si>
   <si>
+    <t>2c5ebf5e-bec0-43e4-9de4-d5a6dd1bc121</t>
+  </si>
+  <si>
     <t>outil de navigation</t>
   </si>
   <si>
+    <t>16b91308-7767-4417-b807-f67e5b3e042b</t>
+  </si>
+  <si>
     <t>pagode</t>
   </si>
   <si>
+    <t>8a57992c-4de3-4139-90de-eb0c0b05005d</t>
+  </si>
+  <si>
     <t>palais</t>
   </si>
   <si>
+    <t>e6c335b5-f067-46d4-a39e-e228dd248e6b</t>
+  </si>
+  <si>
     <t>pape ;</t>
   </si>
   <si>
+    <t>536d2f85-d939-43cf-96dc-40b0a2c693cc</t>
+  </si>
+  <si>
     <t>pièces d'artillerie</t>
   </si>
   <si>
+    <t>bd333968-7131-4b73-bd48-7e76f78fa79c</t>
+  </si>
+  <si>
     <t>piédestal</t>
   </si>
   <si>
+    <t>b35d8491-198c-496d-b9d8-513a6c6048ac</t>
+  </si>
+  <si>
     <t>place</t>
   </si>
   <si>
+    <t>886b852f-c562-4839-b0e7-041634cfdec1</t>
+  </si>
+  <si>
     <t>plan;</t>
   </si>
   <si>
+    <t>b962d7bd-9c71-4961-ac9c-df5f46875120</t>
+  </si>
+  <si>
     <t>poisson</t>
   </si>
   <si>
+    <t>aafcaa7d-05fa-4dd8-903b-d798f6da0564</t>
+  </si>
+  <si>
     <t>pont</t>
   </si>
   <si>
+    <t>e3fae53a-d81e-4c55-a793-a6f7ffe79d7b</t>
+  </si>
+  <si>
     <t>port</t>
   </si>
   <si>
+    <t>66cc5919-1b27-4f71-9cdb-092185a8eb87</t>
+  </si>
+  <si>
     <t>prophétie;</t>
   </si>
   <si>
+    <t>21245635-d7d8-4bcf-8386-8bf7e377506c</t>
+  </si>
+  <si>
     <t>rat</t>
   </si>
   <si>
+    <t>0737ebd5-ee72-4c6f-bb3f-7aef40ee98af</t>
+  </si>
+  <si>
     <t>Rhin</t>
   </si>
   <si>
+    <t>5056f9e7-107c-413e-9779-2b185fdecc40</t>
+  </si>
+  <si>
     <t>rideau</t>
   </si>
   <si>
+    <t>52b44ab0-2001-4aa8-8fe3-2a90882360b0</t>
+  </si>
+  <si>
     <t>rive</t>
   </si>
   <si>
+    <t>f44b8a55-2fe6-4171-8d07-e3397757c77e</t>
+  </si>
+  <si>
     <t>roi ;</t>
   </si>
   <si>
+    <t>386965c0-008e-46f0-8a83-1ecbc4a617f2</t>
+  </si>
+  <si>
     <t>ruisseau;</t>
   </si>
   <si>
+    <t>a0397d8c-e40b-449f-b6ec-6178bea87b7f</t>
+  </si>
+  <si>
     <t>sangsue</t>
   </si>
   <si>
+    <t>d240228c-aef2-4b28-bdf3-8caa5c8b48d7</t>
+  </si>
+  <si>
     <t>siamois</t>
   </si>
   <si>
+    <t>01e1c754-e7a0-40df-b519-a6ce2fca2cd1</t>
+  </si>
+  <si>
     <t>soleil</t>
   </si>
   <si>
+    <t>f8641ece-9d58-4c66-9d1a-f419b1cde300</t>
+  </si>
+  <si>
     <t>songe</t>
   </si>
   <si>
+    <t>1d516b17-73e7-4abd-9656-ddeb44de5ca2</t>
+  </si>
+  <si>
     <t>statue ;</t>
   </si>
   <si>
+    <t>73baa0b2-2543-43f1-99af-0cff8284bc31</t>
+  </si>
+  <si>
     <t>stèle antique</t>
   </si>
   <si>
+    <t>078c3b9f-a3a2-4f39-b0d3-7a1632bf27d9</t>
+  </si>
+  <si>
     <t>table généalogique</t>
   </si>
   <si>
+    <t>77c8aa28-d604-47a6-ace5-de4351d47740</t>
+  </si>
+  <si>
     <t>table numérique</t>
   </si>
   <si>
+    <t>97af6f33-5c93-4fa9-a627-b6a700cc5b79</t>
+  </si>
+  <si>
     <t>télescope</t>
   </si>
   <si>
+    <t>783ecbe1-740c-48c1-abd3-19bd90746f3a</t>
+  </si>
+  <si>
     <t>temple ;</t>
   </si>
   <si>
+    <t>ae62c081-653a-4188-a79a-3af5eba94f86</t>
+  </si>
+  <si>
     <t>théâtre</t>
   </si>
   <si>
+    <t>ea03dbe9-0d7b-4cc1-ab08-44fddfb9a2ff</t>
+  </si>
+  <si>
     <t>thériaque;</t>
   </si>
   <si>
+    <t>b6461048-3abb-4362-abd1-9a099251ee6b</t>
+  </si>
+  <si>
     <t>tour</t>
   </si>
   <si>
+    <t>4cac6704-fd26-41ce-aa79-a306ed5d9a87</t>
+  </si>
+  <si>
     <t>trident ;</t>
   </si>
   <si>
+    <t>70dbd362-e748-40cd-b4e1-bd355903105b</t>
+  </si>
+  <si>
     <t>triton</t>
   </si>
   <si>
+    <t>c0361a26-191b-4af1-ae8a-89d5bcf30881</t>
+  </si>
+  <si>
     <t>trône</t>
   </si>
   <si>
+    <t>3c6d676b-2039-414f-ae7a-663cea2f6211</t>
+  </si>
+  <si>
     <t>trophée</t>
   </si>
   <si>
+    <t>85e95434-a646-490f-99d3-0c5236fcda03</t>
+  </si>
+  <si>
     <t>vêtement</t>
   </si>
   <si>
+    <t>9c47d343-012e-4718-95a7-ac409a8c58c9</t>
+  </si>
+  <si>
     <t>victoire</t>
   </si>
   <si>
+    <t>c52c0126-a848-4f83-9661-90bf8f8eef02</t>
+  </si>
+  <si>
     <t>vieillard ;</t>
   </si>
   <si>
+    <t>098fc917-ff85-4932-b7b1-362f95363c18</t>
+  </si>
+  <si>
     <t>ville</t>
   </si>
   <si>
+    <t>2b192a79-7f40-4a3e-90a3-ec6408f0b9f9</t>
+  </si>
+  <si>
     <t>voûte</t>
   </si>
   <si>
+    <t>f73b7815-cfde-412c-9786-a07bef7a15e6</t>
+  </si>
+  <si>
     <t>zodiaque</t>
   </si>
   <si>
+    <t>8fba5507-207d-4b19-90d6-9d9860d14849</t>
+  </si>
+  <si>
     <t>système d'orientation spatiale</t>
   </si>
   <si>
+    <t>05e46581-fa1b-4aee-97a8-d9ca86e894a7</t>
+  </si>
+  <si>
     <t>textes</t>
   </si>
   <si>
+    <t>60d11d1c-043a-4db7-abbf-6494ba812bd0</t>
+  </si>
+  <si>
     <t>texte en arabe</t>
   </si>
   <si>
+    <t>995e2bb4-6e53-41ea-a848-4c61581c0257</t>
+  </si>
+  <si>
     <t>table d'écriture codée ;</t>
   </si>
   <si>
+    <t>2a5a8714-1df5-4c95-bfa1-f718ca74ebc3</t>
+  </si>
+  <si>
     <t>Techniques</t>
   </si>
   <si>
+    <t>a2426a2e-e7ff-459b-8a2c-62a89283d456</t>
+  </si>
+  <si>
     <t>Dessin d’architecte ou d’ingénieur</t>
   </si>
   <si>
+    <t>1dc4a653-6bc4-41aa-9816-ceaef586721d</t>
+  </si>
+  <si>
     <t>Élévation</t>
   </si>
   <si>
+    <t>4165c725-df6d-4737-a983-d3b906c1ad21</t>
+  </si>
+  <si>
     <t>Dessin scientifique</t>
   </si>
   <si>
+    <t>595168fe-86d3-4602-b0f5-459b612260d3</t>
+  </si>
+  <si>
     <t>Plan ou vue</t>
+  </si>
+  <si>
+    <t>75ad55f0-bac5-40db-b531-ea506e39ef68</t>
   </si>
   <si>
     <t>Relevé décoratif</t>
@@ -833,7 +1628,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -857,17 +1652,17 @@
     </font>
     <font>
       <color rgb="FF000000"/>
-      <name val="&quot;Arial&quot;"/>
+      <name val="Roboto"/>
     </font>
     <font>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="&quot;docs-Roboto&quot;"/>
     </font>
+    <font/>
     <font>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
-    <font/>
     <font>
       <color rgb="FF000000"/>
       <name val="&quot;Comic Sans MS&quot;"/>
@@ -888,11 +1683,18 @@
     </font>
     <font>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
       <name val="&quot;docs-Garamond&quot;"/>
     </font>
     <font>
       <u/>
       <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="10.0"/>
@@ -950,7 +1752,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -978,26 +1780,26 @@
     <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
@@ -1011,34 +1813,40 @@
     <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1047,7 +1855,7 @@
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1059,19 +1867,19 @@
     <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -1287,7 +2095,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.14"/>
+    <col customWidth="1" min="1" max="1" width="38.43"/>
     <col customWidth="1" min="2" max="2" width="20.57"/>
     <col customWidth="1" min="3" max="3" width="30.0"/>
     <col customWidth="1" min="4" max="4" width="36.43"/>
@@ -1322,9 +2130,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2"/>
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="B2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="4"/>
@@ -1333,12 +2143,14 @@
       <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="2"/>
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B3" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="5"/>
@@ -1346,3508 +2158,4154 @@
       <c r="G3" s="5"/>
     </row>
     <row r="4">
-      <c r="A4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
     </row>
     <row r="5">
-      <c r="A5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="B5" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
     </row>
     <row r="6">
-      <c r="A6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
     </row>
     <row r="7">
-      <c r="A7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="B7" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
     </row>
     <row r="8">
-      <c r="A8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="B8" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
     </row>
     <row r="9">
-      <c r="A9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="B9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="3"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
     </row>
     <row r="10">
-      <c r="A10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="B10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
     </row>
     <row r="11">
-      <c r="A11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="B11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>13</v>
+        <v>7</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>21</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
     </row>
     <row r="12">
-      <c r="A12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="B12" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="D12" s="4"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
     </row>
     <row r="13">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="B13" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="B14" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>31</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
     </row>
     <row r="15">
-      <c r="A15" s="2"/>
+      <c r="A15" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="B15" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
     </row>
     <row r="16">
-      <c r="A16" s="2"/>
+      <c r="A16" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="B16" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
     </row>
     <row r="17">
-      <c r="A17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="B17" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="5"/>
+        <v>37</v>
+      </c>
+      <c r="E17" s="11"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
     </row>
     <row r="18">
-      <c r="A18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="B18" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>21</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
     </row>
     <row r="19">
-      <c r="A19" s="2"/>
+      <c r="A19" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="B19" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
     </row>
     <row r="20">
-      <c r="A20" s="2"/>
+      <c r="A20" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="B20" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="5"/>
+        <v>41</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>43</v>
+      </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
     </row>
     <row r="21">
-      <c r="A21" s="2"/>
+      <c r="A21" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="B21" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
+        <v>45</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
     </row>
     <row r="22">
-      <c r="A22" s="2"/>
+      <c r="A22" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="B22" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
+        <v>47</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
     </row>
     <row r="23">
-      <c r="A23" s="2"/>
+      <c r="A23" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="B23" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
+        <v>49</v>
+      </c>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
     </row>
     <row r="24">
-      <c r="A24" s="2"/>
+      <c r="A24" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="B24" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
+        <v>7</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
     </row>
     <row r="25">
-      <c r="A25" s="2"/>
+      <c r="A25" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="B25" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="D25" s="3"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
     </row>
     <row r="26">
-      <c r="A26" s="13"/>
+      <c r="A26" s="13" t="s">
+        <v>54</v>
+      </c>
       <c r="B26" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
+        <v>55</v>
+      </c>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
     </row>
     <row r="27">
-      <c r="A27" s="13"/>
+      <c r="A27" s="13" t="s">
+        <v>56</v>
+      </c>
       <c r="B27" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
+        <v>57</v>
+      </c>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
     </row>
     <row r="28">
-      <c r="A28" s="13"/>
+      <c r="A28" s="13" t="s">
+        <v>58</v>
+      </c>
       <c r="B28" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
+        <v>59</v>
+      </c>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
     </row>
     <row r="29">
-      <c r="A29" s="13"/>
+      <c r="A29" s="13" t="s">
+        <v>60</v>
+      </c>
       <c r="B29" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
+        <v>61</v>
+      </c>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
     </row>
     <row r="30">
-      <c r="A30" s="13"/>
+      <c r="A30" s="13" t="s">
+        <v>62</v>
+      </c>
       <c r="B30" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
+        <v>63</v>
+      </c>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
     </row>
     <row r="31">
-      <c r="A31" s="13"/>
+      <c r="A31" s="13" t="s">
+        <v>64</v>
+      </c>
       <c r="B31" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
+        <v>65</v>
+      </c>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
     </row>
     <row r="32">
-      <c r="A32" s="13"/>
+      <c r="A32" s="13" t="s">
+        <v>66</v>
+      </c>
       <c r="B32" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D32" s="9"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
     </row>
     <row r="33">
-      <c r="A33" s="13"/>
+      <c r="A33" s="13" t="s">
+        <v>67</v>
+      </c>
       <c r="B33" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
+        <v>11</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
     </row>
     <row r="34">
-      <c r="A34" s="13"/>
+      <c r="A34" s="13" t="s">
+        <v>69</v>
+      </c>
       <c r="B34" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
+        <v>70</v>
+      </c>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
     </row>
     <row r="35">
-      <c r="A35" s="13"/>
+      <c r="A35" s="13" t="s">
+        <v>71</v>
+      </c>
       <c r="B35" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
+        <v>70</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
     </row>
     <row r="36">
-      <c r="A36" s="13"/>
+      <c r="A36" s="13" t="s">
+        <v>73</v>
+      </c>
       <c r="B36" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
+        <v>72</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
     </row>
     <row r="37">
-      <c r="A37" s="13"/>
+      <c r="A37" s="13" t="s">
+        <v>75</v>
+      </c>
       <c r="B37" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E37" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="F37" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="14"/>
       <c r="G37" s="14"/>
     </row>
     <row r="38">
-      <c r="A38" s="13"/>
+      <c r="A38" s="13" t="s">
+        <v>77</v>
+      </c>
       <c r="B38" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E38" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F38" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F38" s="14"/>
       <c r="G38" s="14"/>
     </row>
     <row r="39">
-      <c r="A39" s="13"/>
+      <c r="A39" s="13" t="s">
+        <v>79</v>
+      </c>
       <c r="B39" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E39" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="F39" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="F39" s="14"/>
       <c r="G39" s="14"/>
     </row>
     <row r="40">
-      <c r="A40" s="13"/>
+      <c r="A40" s="13" t="s">
+        <v>81</v>
+      </c>
       <c r="B40" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E40" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F40" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F40" s="14"/>
       <c r="G40" s="14"/>
     </row>
     <row r="41">
-      <c r="A41" s="13"/>
+      <c r="A41" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="B41" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E41" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F41" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="F41" s="14"/>
       <c r="G41" s="14"/>
     </row>
     <row r="42">
-      <c r="A42" s="13"/>
+      <c r="A42" s="13" t="s">
+        <v>85</v>
+      </c>
       <c r="B42" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E42" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="F42" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="F42" s="14"/>
       <c r="G42" s="14"/>
     </row>
     <row r="43">
-      <c r="A43" s="13"/>
+      <c r="A43" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="B43" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E43" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="F43" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F43" s="14"/>
       <c r="G43" s="14"/>
     </row>
     <row r="44">
-      <c r="A44" s="13"/>
+      <c r="A44" s="13" t="s">
+        <v>89</v>
+      </c>
       <c r="B44" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E44" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F44" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="F44" s="14"/>
       <c r="G44" s="14"/>
     </row>
     <row r="45">
-      <c r="A45" s="13"/>
+      <c r="A45" s="13" t="s">
+        <v>91</v>
+      </c>
       <c r="B45" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E45" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F45" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="F45" s="14"/>
       <c r="G45" s="14"/>
     </row>
     <row r="46">
-      <c r="A46" s="13"/>
+      <c r="A46" s="13" t="s">
+        <v>93</v>
+      </c>
       <c r="B46" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E46" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="F46" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F46" s="14"/>
       <c r="G46" s="14"/>
     </row>
     <row r="47">
-      <c r="A47" s="13"/>
+      <c r="A47" s="13" t="s">
+        <v>95</v>
+      </c>
       <c r="B47" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E47" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="F47" s="15"/>
-      <c r="G47" s="14"/>
+        <v>72</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="F47" s="16"/>
+      <c r="G47" s="17"/>
     </row>
     <row r="48">
-      <c r="A48" s="13"/>
+      <c r="A48" s="13" t="s">
+        <v>97</v>
+      </c>
       <c r="B48" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E48" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="F48" s="15"/>
-      <c r="G48" s="14"/>
+        <v>72</v>
+      </c>
+      <c r="E48" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F48" s="16"/>
+      <c r="G48" s="17"/>
     </row>
     <row r="49">
-      <c r="A49" s="13"/>
+      <c r="A49" s="13" t="s">
+        <v>99</v>
+      </c>
       <c r="B49" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="F49" s="16"/>
       <c r="G49" s="17"/>
     </row>
     <row r="50">
-      <c r="A50" s="13"/>
+      <c r="A50" s="13" t="s">
+        <v>100</v>
+      </c>
       <c r="B50" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="F50" s="16"/>
       <c r="G50" s="17"/>
     </row>
     <row r="51">
-      <c r="A51" s="13"/>
+      <c r="A51" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="B51" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="F51" s="16"/>
       <c r="G51" s="17"/>
     </row>
     <row r="52">
-      <c r="A52" s="13"/>
+      <c r="A52" s="13" t="s">
+        <v>104</v>
+      </c>
       <c r="B52" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E52" s="16" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="F52" s="16"/>
       <c r="G52" s="17"/>
     </row>
     <row r="53">
-      <c r="A53" s="13"/>
+      <c r="A53" s="13" t="s">
+        <v>106</v>
+      </c>
       <c r="B53" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E53" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="F53" s="16"/>
-      <c r="G53" s="17"/>
+        <v>72</v>
+      </c>
+      <c r="E53" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="F53" s="18"/>
+      <c r="G53" s="19"/>
     </row>
     <row r="54">
-      <c r="A54" s="13"/>
+      <c r="A54" s="13" t="s">
+        <v>108</v>
+      </c>
       <c r="B54" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="F54" s="16"/>
       <c r="G54" s="17"/>
     </row>
     <row r="55">
-      <c r="A55" s="13"/>
+      <c r="A55" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="B55" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E55" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="F55" s="18"/>
-      <c r="G55" s="19"/>
+        <v>72</v>
+      </c>
+      <c r="E55" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="F55" s="16"/>
+      <c r="G55" s="17"/>
     </row>
     <row r="56">
-      <c r="A56" s="13"/>
+      <c r="A56" s="13" t="s">
+        <v>112</v>
+      </c>
       <c r="B56" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="F56" s="16"/>
       <c r="G56" s="17"/>
     </row>
     <row r="57">
-      <c r="A57" s="13"/>
+      <c r="A57" s="13" t="s">
+        <v>114</v>
+      </c>
       <c r="B57" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="F57" s="16"/>
       <c r="G57" s="17"/>
     </row>
     <row r="58">
-      <c r="A58" s="13"/>
+      <c r="A58" s="13" t="s">
+        <v>116</v>
+      </c>
       <c r="B58" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>57</v>
+        <v>117</v>
       </c>
       <c r="F58" s="16"/>
       <c r="G58" s="17"/>
     </row>
     <row r="59">
-      <c r="A59" s="13"/>
+      <c r="A59" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="B59" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="F59" s="16"/>
       <c r="G59" s="17"/>
     </row>
     <row r="60">
-      <c r="A60" s="13"/>
+      <c r="A60" s="13" t="s">
+        <v>120</v>
+      </c>
       <c r="B60" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E60" s="16" t="s">
-        <v>59</v>
+        <v>121</v>
       </c>
       <c r="F60" s="16"/>
       <c r="G60" s="17"/>
     </row>
     <row r="61">
-      <c r="A61" s="13"/>
+      <c r="A61" s="13" t="s">
+        <v>122</v>
+      </c>
       <c r="B61" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="F61" s="16"/>
       <c r="G61" s="17"/>
     </row>
     <row r="62">
-      <c r="A62" s="13"/>
+      <c r="A62" s="13" t="s">
+        <v>124</v>
+      </c>
       <c r="B62" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="F62" s="16"/>
       <c r="G62" s="17"/>
     </row>
     <row r="63">
-      <c r="A63" s="13"/>
+      <c r="A63" s="13" t="s">
+        <v>126</v>
+      </c>
       <c r="B63" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E63" s="16" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="F63" s="16"/>
       <c r="G63" s="17"/>
     </row>
     <row r="64">
-      <c r="A64" s="13"/>
+      <c r="A64" s="13" t="s">
+        <v>128</v>
+      </c>
       <c r="B64" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>63</v>
+        <v>129</v>
       </c>
       <c r="F64" s="16"/>
       <c r="G64" s="17"/>
     </row>
     <row r="65">
-      <c r="A65" s="13"/>
+      <c r="A65" s="13" t="s">
+        <v>130</v>
+      </c>
       <c r="B65" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>64</v>
+        <v>131</v>
       </c>
       <c r="F65" s="16"/>
       <c r="G65" s="17"/>
     </row>
     <row r="66">
-      <c r="A66" s="13"/>
+      <c r="A66" s="13" t="s">
+        <v>132</v>
+      </c>
       <c r="B66" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="F66" s="16"/>
       <c r="G66" s="17"/>
     </row>
     <row r="67">
-      <c r="A67" s="13"/>
+      <c r="A67" s="13" t="s">
+        <v>134</v>
+      </c>
       <c r="B67" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="F67" s="16"/>
       <c r="G67" s="17"/>
     </row>
     <row r="68">
-      <c r="A68" s="13"/>
+      <c r="A68" s="13" t="s">
+        <v>136</v>
+      </c>
       <c r="B68" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>67</v>
+        <v>137</v>
       </c>
       <c r="F68" s="16"/>
       <c r="G68" s="17"/>
     </row>
     <row r="69">
-      <c r="A69" s="13"/>
+      <c r="A69" s="13" t="s">
+        <v>138</v>
+      </c>
       <c r="B69" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>68</v>
+        <v>139</v>
       </c>
       <c r="F69" s="16"/>
       <c r="G69" s="17"/>
     </row>
     <row r="70">
-      <c r="A70" s="13"/>
+      <c r="A70" s="13" t="s">
+        <v>140</v>
+      </c>
       <c r="B70" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>69</v>
+        <v>141</v>
       </c>
       <c r="F70" s="16"/>
       <c r="G70" s="17"/>
     </row>
     <row r="71">
-      <c r="A71" s="13"/>
+      <c r="A71" s="13" t="s">
+        <v>142</v>
+      </c>
       <c r="B71" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>70</v>
+        <v>143</v>
       </c>
       <c r="F71" s="16"/>
       <c r="G71" s="17"/>
     </row>
     <row r="72">
-      <c r="A72" s="13"/>
+      <c r="A72" s="13" t="s">
+        <v>144</v>
+      </c>
       <c r="B72" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E72" s="16" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="F72" s="16"/>
       <c r="G72" s="17"/>
     </row>
     <row r="73">
-      <c r="A73" s="13"/>
+      <c r="A73" s="13" t="s">
+        <v>146</v>
+      </c>
       <c r="B73" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>72</v>
+        <v>147</v>
       </c>
       <c r="F73" s="16"/>
       <c r="G73" s="17"/>
     </row>
     <row r="74">
-      <c r="A74" s="13"/>
+      <c r="A74" s="13" t="s">
+        <v>148</v>
+      </c>
       <c r="B74" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E74" s="16" t="s">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="F74" s="16"/>
       <c r="G74" s="17"/>
     </row>
     <row r="75">
-      <c r="A75" s="13"/>
+      <c r="A75" s="13" t="s">
+        <v>150</v>
+      </c>
       <c r="B75" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D75" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E75" s="16" t="s">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="F75" s="16"/>
       <c r="G75" s="17"/>
     </row>
     <row r="76">
-      <c r="A76" s="13"/>
+      <c r="A76" s="13" t="s">
+        <v>152</v>
+      </c>
       <c r="B76" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E76" s="16" t="s">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="F76" s="16"/>
       <c r="G76" s="17"/>
     </row>
     <row r="77">
-      <c r="A77" s="13"/>
+      <c r="A77" s="13" t="s">
+        <v>154</v>
+      </c>
       <c r="B77" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="F77" s="16"/>
       <c r="G77" s="17"/>
     </row>
     <row r="78">
-      <c r="A78" s="13"/>
+      <c r="A78" s="13" t="s">
+        <v>156</v>
+      </c>
       <c r="B78" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E78" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="F78" s="16"/>
-      <c r="G78" s="17"/>
+        <v>72</v>
+      </c>
+      <c r="E78" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F78" s="18"/>
+      <c r="G78" s="19"/>
     </row>
     <row r="79">
-      <c r="A79" s="13"/>
+      <c r="A79" s="13" t="s">
+        <v>158</v>
+      </c>
       <c r="B79" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D79" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E79" s="16" t="s">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="F79" s="16"/>
       <c r="G79" s="17"/>
     </row>
     <row r="80">
-      <c r="A80" s="13"/>
+      <c r="A80" s="13" t="s">
+        <v>160</v>
+      </c>
       <c r="B80" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E80" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="F80" s="18"/>
-      <c r="G80" s="19"/>
+        <v>72</v>
+      </c>
+      <c r="E80" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F80" s="16"/>
+      <c r="G80" s="17"/>
     </row>
     <row r="81">
-      <c r="A81" s="13"/>
+      <c r="A81" s="13" t="s">
+        <v>161</v>
+      </c>
       <c r="B81" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D81" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E81" s="16" t="s">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="F81" s="16"/>
       <c r="G81" s="17"/>
     </row>
     <row r="82">
-      <c r="A82" s="13"/>
+      <c r="A82" s="13" t="s">
+        <v>163</v>
+      </c>
       <c r="B82" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E82" s="16" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="F82" s="16"/>
       <c r="G82" s="17"/>
     </row>
     <row r="83">
-      <c r="A83" s="13"/>
+      <c r="A83" s="13" t="s">
+        <v>164</v>
+      </c>
       <c r="B83" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E83" s="16" t="s">
-        <v>81</v>
+        <v>165</v>
       </c>
       <c r="F83" s="16"/>
       <c r="G83" s="17"/>
     </row>
     <row r="84">
-      <c r="A84" s="13"/>
+      <c r="A84" s="13" t="s">
+        <v>166</v>
+      </c>
       <c r="B84" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E84" s="16" t="s">
-        <v>40</v>
+        <v>167</v>
       </c>
       <c r="F84" s="16"/>
       <c r="G84" s="17"/>
     </row>
     <row r="85">
-      <c r="A85" s="13"/>
+      <c r="A85" s="13" t="s">
+        <v>168</v>
+      </c>
       <c r="B85" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C85" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E85" s="16" t="s">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="F85" s="16"/>
       <c r="G85" s="17"/>
     </row>
     <row r="86">
-      <c r="A86" s="13"/>
+      <c r="A86" s="13" t="s">
+        <v>170</v>
+      </c>
       <c r="B86" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E86" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="F86" s="16"/>
-      <c r="G86" s="17"/>
+        <v>72</v>
+      </c>
+      <c r="E86" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="F86" s="18"/>
+      <c r="G86" s="19"/>
     </row>
     <row r="87">
-      <c r="A87" s="13"/>
+      <c r="A87" s="13" t="s">
+        <v>172</v>
+      </c>
       <c r="B87" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C87" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D87" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E87" s="16" t="s">
-        <v>84</v>
+        <v>173</v>
       </c>
       <c r="F87" s="16"/>
       <c r="G87" s="17"/>
     </row>
     <row r="88">
-      <c r="A88" s="13"/>
+      <c r="A88" s="13" t="s">
+        <v>174</v>
+      </c>
       <c r="B88" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D88" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E88" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="F88" s="18"/>
-      <c r="G88" s="19"/>
+        <v>72</v>
+      </c>
+      <c r="E88" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="F88" s="16"/>
+      <c r="G88" s="17"/>
     </row>
     <row r="89">
-      <c r="A89" s="13"/>
+      <c r="A89" s="13" t="s">
+        <v>175</v>
+      </c>
       <c r="B89" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C89" s="14" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D89" s="14" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E89" s="16" t="s">
-        <v>86</v>
+        <v>176</v>
       </c>
       <c r="F89" s="16"/>
       <c r="G89" s="17"/>
     </row>
     <row r="90">
-      <c r="A90" s="13"/>
+      <c r="A90" s="13" t="s">
+        <v>177</v>
+      </c>
       <c r="B90" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C90" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D90" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E90" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="F90" s="16"/>
-      <c r="G90" s="17"/>
+        <v>7</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="D90" s="14"/>
+      <c r="E90" s="16"/>
+      <c r="F90" s="15"/>
+      <c r="G90" s="15"/>
     </row>
     <row r="91">
-      <c r="A91" s="13"/>
+      <c r="A91" s="13" t="s">
+        <v>179</v>
+      </c>
       <c r="B91" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>35</v>
+        <v>178</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E91" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="F91" s="16"/>
-      <c r="G91" s="17"/>
+        <v>180</v>
+      </c>
+      <c r="E91" s="16"/>
+      <c r="F91" s="15"/>
+      <c r="G91" s="15"/>
     </row>
     <row r="92">
-      <c r="A92" s="13"/>
+      <c r="A92" s="13" t="s">
+        <v>181</v>
+      </c>
       <c r="B92" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>88</v>
+        <v>178</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E92" s="16"/>
-      <c r="F92" s="13"/>
-      <c r="G92" s="13"/>
+        <v>180</v>
+      </c>
+      <c r="E92" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="F92" s="15"/>
+      <c r="G92" s="15"/>
     </row>
     <row r="93">
-      <c r="A93" s="20"/>
+      <c r="A93" s="13" t="s">
+        <v>183</v>
+      </c>
       <c r="B93" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C93" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="D93" s="15" t="s">
-        <v>89</v>
+        <v>7</v>
+      </c>
+      <c r="C93" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="D93" s="14" t="s">
+        <v>180</v>
       </c>
       <c r="E93" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="F93" s="20"/>
-      <c r="G93" s="20"/>
+        <v>184</v>
+      </c>
+      <c r="F93" s="15"/>
+      <c r="G93" s="15"/>
     </row>
     <row r="94">
-      <c r="A94" s="20"/>
+      <c r="A94" s="13" t="s">
+        <v>185</v>
+      </c>
       <c r="B94" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C94" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="D94" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="E94" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="F94" s="20"/>
-      <c r="G94" s="20"/>
+        <v>7</v>
+      </c>
+      <c r="C94" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="F94" s="15"/>
+      <c r="G94" s="15"/>
     </row>
     <row r="95">
-      <c r="A95" s="13"/>
+      <c r="A95" s="13" t="s">
+        <v>187</v>
+      </c>
       <c r="B95" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C95" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="F95" s="13"/>
-      <c r="G95" s="13"/>
+        <v>186</v>
+      </c>
+      <c r="D95" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="F95" s="15"/>
+      <c r="G95" s="15"/>
     </row>
     <row r="96">
-      <c r="A96" s="13"/>
+      <c r="A96" s="13" t="s">
+        <v>189</v>
+      </c>
       <c r="B96" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C96" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D96" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="F96" s="13"/>
-      <c r="G96" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="C96" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="D96" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="F96" s="15"/>
+      <c r="G96" s="15"/>
     </row>
     <row r="97">
-      <c r="A97" s="13"/>
+      <c r="A97" s="13" t="s">
+        <v>191</v>
+      </c>
       <c r="B97" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C97" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D97" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="F97" s="13"/>
-      <c r="G97" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="C97" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="D97" s="14"/>
+      <c r="F97" s="15"/>
+      <c r="G97" s="15"/>
     </row>
     <row r="98">
-      <c r="A98" s="20"/>
+      <c r="A98" s="13" t="s">
+        <v>193</v>
+      </c>
       <c r="B98" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C98" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D98" s="15"/>
-      <c r="F98" s="20"/>
-      <c r="G98" s="20"/>
+        <v>7</v>
+      </c>
+      <c r="C98" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="D98" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="F98" s="15"/>
+      <c r="G98" s="15"/>
     </row>
     <row r="99">
-      <c r="A99" s="13"/>
+      <c r="A99" s="13" t="s">
+        <v>195</v>
+      </c>
       <c r="B99" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C99" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="D99" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="F99" s="13"/>
-      <c r="G99" s="13"/>
+        <v>192</v>
+      </c>
+      <c r="D99" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="E99" s="15"/>
+      <c r="F99" s="15"/>
+      <c r="G99" s="15"/>
     </row>
     <row r="100">
-      <c r="A100" s="13"/>
+      <c r="A100" s="13" t="s">
+        <v>197</v>
+      </c>
       <c r="B100" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>95</v>
+        <v>192</v>
       </c>
       <c r="D100" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E100" s="13"/>
-      <c r="F100" s="13"/>
-      <c r="G100" s="13"/>
+        <v>196</v>
+      </c>
+      <c r="E100" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="F100" s="15"/>
+      <c r="G100" s="15"/>
     </row>
     <row r="101">
-      <c r="A101" s="13"/>
+      <c r="A101" s="13" t="s">
+        <v>199</v>
+      </c>
       <c r="B101" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>95</v>
+        <v>192</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E101" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F101" s="13"/>
-      <c r="G101" s="13"/>
+        <v>196</v>
+      </c>
+      <c r="E101" s="15"/>
+      <c r="F101" s="15"/>
+      <c r="G101" s="15"/>
     </row>
     <row r="102">
-      <c r="A102" s="13"/>
+      <c r="A102" s="13" t="s">
+        <v>200</v>
+      </c>
       <c r="B102" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>95</v>
+        <v>192</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E102" s="13"/>
-      <c r="F102" s="13"/>
-      <c r="G102" s="13"/>
+        <v>196</v>
+      </c>
+      <c r="E102" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="F102" s="15"/>
+      <c r="G102" s="15"/>
     </row>
     <row r="103">
-      <c r="A103" s="13"/>
+      <c r="A103" s="13" t="s">
+        <v>202</v>
+      </c>
       <c r="B103" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C103" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D103" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E103" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="F103" s="13"/>
-      <c r="G103" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="C103" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="D103" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="E103" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="F103" s="14"/>
+      <c r="G103" s="15"/>
     </row>
     <row r="104">
-      <c r="A104" s="13"/>
+      <c r="A104" s="13" t="s">
+        <v>204</v>
+      </c>
       <c r="B104" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>95</v>
+        <v>192</v>
       </c>
       <c r="D104" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E104" s="15" t="s">
-        <v>100</v>
+        <v>196</v>
+      </c>
+      <c r="E104" s="20" t="s">
+        <v>205</v>
       </c>
       <c r="F104" s="15"/>
-      <c r="G104" s="13"/>
+      <c r="G104" s="15"/>
     </row>
     <row r="105">
-      <c r="A105" s="13"/>
+      <c r="A105" s="13" t="s">
+        <v>206</v>
+      </c>
       <c r="B105" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C105" s="14" t="s">
-        <v>95</v>
+        <v>192</v>
       </c>
       <c r="D105" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E105" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="F105" s="13"/>
-      <c r="G105" s="13"/>
+        <v>196</v>
+      </c>
+      <c r="E105" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="F105" s="15"/>
+      <c r="G105" s="15"/>
     </row>
     <row r="106">
-      <c r="A106" s="13"/>
-      <c r="B106" s="3"/>
-      <c r="C106" s="14"/>
-      <c r="D106" s="14"/>
-      <c r="E106" s="14"/>
-      <c r="F106" s="13"/>
-      <c r="G106" s="13"/>
+      <c r="A106" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="D106" s="15"/>
+      <c r="E106" s="21"/>
+      <c r="F106" s="15"/>
+      <c r="G106" s="15"/>
     </row>
     <row r="107">
-      <c r="A107" s="13"/>
-      <c r="B107" s="3"/>
-      <c r="C107" s="14"/>
-      <c r="D107" s="14"/>
-      <c r="E107" s="14"/>
-      <c r="F107" s="13"/>
-      <c r="G107" s="13"/>
+      <c r="A107" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C107" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="D107" s="15"/>
+      <c r="E107" s="15"/>
+      <c r="F107" s="15"/>
+      <c r="G107" s="15"/>
     </row>
     <row r="108">
-      <c r="A108" s="13"/>
+      <c r="A108" s="13" t="s">
+        <v>212</v>
+      </c>
       <c r="B108" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C108" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D108" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E108" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="F108" s="13"/>
-      <c r="G108" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="C108" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="D108" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="E108" s="15"/>
+      <c r="F108" s="15"/>
+      <c r="G108" s="15"/>
     </row>
     <row r="109">
-      <c r="A109" s="13"/>
+      <c r="A109" s="13" t="s">
+        <v>214</v>
+      </c>
       <c r="B109" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="D109" s="13"/>
-      <c r="E109" s="21"/>
-      <c r="F109" s="13"/>
-      <c r="G109" s="13"/>
+        <v>211</v>
+      </c>
+      <c r="D109" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="E109" s="15"/>
+      <c r="F109" s="15"/>
+      <c r="G109" s="15"/>
     </row>
     <row r="110">
-      <c r="A110" s="13"/>
+      <c r="A110" s="13" t="s">
+        <v>216</v>
+      </c>
       <c r="B110" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D110" s="13"/>
-      <c r="E110" s="13"/>
-      <c r="F110" s="13"/>
-      <c r="G110" s="13"/>
+        <v>211</v>
+      </c>
+      <c r="D110" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="E110" s="15"/>
+      <c r="F110" s="15"/>
+      <c r="G110" s="15"/>
     </row>
     <row r="111">
-      <c r="A111" s="13"/>
+      <c r="A111" s="22" t="s">
+        <v>218</v>
+      </c>
       <c r="B111" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C111" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D111" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="E111" s="13"/>
-      <c r="F111" s="13"/>
-      <c r="G111" s="13"/>
+        <v>219</v>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="13"/>
-      <c r="B112" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C112" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D112" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="E112" s="13"/>
-      <c r="F112" s="13"/>
-      <c r="G112" s="13"/>
+      <c r="A112" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="B112" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="D112" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="G112" s="23" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" s="13"/>
-      <c r="B113" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C113" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D113" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="E113" s="13"/>
-      <c r="F113" s="13"/>
-      <c r="G113" s="13"/>
+      <c r="A113" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="B113" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="D113" s="16" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="114">
-      <c r="B114" s="3" t="s">
-        <v>108</v>
+      <c r="A114" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="B114" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="D114" s="24" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="115">
+      <c r="A115" s="22" t="s">
+        <v>227</v>
+      </c>
       <c r="B115" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D115" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="G115" s="23" t="s">
-        <v>110</v>
+        <v>219</v>
+      </c>
+      <c r="D115" s="16" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="116">
+      <c r="A116" s="22" t="s">
+        <v>229</v>
+      </c>
       <c r="B116" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D116" s="16" t="s">
-        <v>111</v>
+        <v>230</v>
       </c>
     </row>
     <row r="117">
+      <c r="A117" s="22" t="s">
+        <v>231</v>
+      </c>
       <c r="B117" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D117" s="24" t="s">
-        <v>112</v>
+        <v>219</v>
+      </c>
+      <c r="D117" s="16" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="118">
+      <c r="A118" s="22" t="s">
+        <v>233</v>
+      </c>
       <c r="B118" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D118" s="16" t="s">
-        <v>113</v>
+        <v>219</v>
+      </c>
+      <c r="D118" s="24" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="119">
+      <c r="A119" s="22" t="s">
+        <v>235</v>
+      </c>
       <c r="B119" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D119" s="16" t="s">
-        <v>114</v>
+        <v>219</v>
+      </c>
+      <c r="D119" s="24" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="120">
+      <c r="A120" s="22" t="s">
+        <v>237</v>
+      </c>
       <c r="B120" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D120" s="16" t="s">
-        <v>115</v>
+        <v>219</v>
+      </c>
+      <c r="D120" s="24" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="121">
+      <c r="A121" s="22" t="s">
+        <v>239</v>
+      </c>
       <c r="B121" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D121" s="24" t="s">
-        <v>116</v>
+        <v>240</v>
       </c>
     </row>
     <row r="122">
+      <c r="A122" s="22" t="s">
+        <v>241</v>
+      </c>
       <c r="B122" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D122" s="24" t="s">
-        <v>117</v>
+        <v>242</v>
       </c>
     </row>
     <row r="123">
+      <c r="A123" s="22" t="s">
+        <v>243</v>
+      </c>
       <c r="B123" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D123" s="24" t="s">
-        <v>118</v>
+        <v>244</v>
       </c>
     </row>
     <row r="124">
+      <c r="A124" s="22" t="s">
+        <v>245</v>
+      </c>
       <c r="B124" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D124" s="24" t="s">
-        <v>119</v>
+        <v>219</v>
+      </c>
+      <c r="D124" s="16" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="125">
+      <c r="A125" s="25" t="s">
+        <v>247</v>
+      </c>
       <c r="B125" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D125" s="24" t="s">
-        <v>120</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="C125" s="26"/>
+      <c r="D125" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="E125" s="26"/>
+      <c r="F125" s="26"/>
+      <c r="G125" s="26"/>
+      <c r="H125" s="26"/>
+      <c r="I125" s="26"/>
+      <c r="J125" s="26"/>
+      <c r="K125" s="26"/>
+      <c r="L125" s="26"/>
+      <c r="M125" s="26"/>
+      <c r="N125" s="26"/>
+      <c r="O125" s="26"/>
+      <c r="P125" s="26"/>
+      <c r="Q125" s="26"/>
+      <c r="R125" s="26"/>
+      <c r="S125" s="26"/>
+      <c r="T125" s="26"/>
+      <c r="U125" s="26"/>
+      <c r="V125" s="26"/>
+      <c r="W125" s="26"/>
+      <c r="X125" s="26"/>
+      <c r="Y125" s="26"/>
+      <c r="Z125" s="26"/>
+      <c r="AA125" s="26"/>
+      <c r="AB125" s="26"/>
     </row>
     <row r="126">
+      <c r="A126" s="25" t="s">
+        <v>249</v>
+      </c>
       <c r="B126" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D126" s="24" t="s">
-        <v>121</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="C126" s="26"/>
+      <c r="D126" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="E126" s="26"/>
+      <c r="F126" s="26"/>
+      <c r="G126" s="26"/>
+      <c r="H126" s="26"/>
+      <c r="I126" s="26"/>
+      <c r="J126" s="26"/>
+      <c r="K126" s="26"/>
+      <c r="L126" s="26"/>
+      <c r="M126" s="26"/>
+      <c r="N126" s="26"/>
+      <c r="O126" s="26"/>
+      <c r="P126" s="26"/>
+      <c r="Q126" s="26"/>
+      <c r="R126" s="26"/>
+      <c r="S126" s="26"/>
+      <c r="T126" s="26"/>
+      <c r="U126" s="26"/>
+      <c r="V126" s="26"/>
+      <c r="W126" s="26"/>
+      <c r="X126" s="26"/>
+      <c r="Y126" s="26"/>
+      <c r="Z126" s="26"/>
+      <c r="AA126" s="26"/>
+      <c r="AB126" s="26"/>
     </row>
     <row r="127">
+      <c r="A127" s="25" t="s">
+        <v>251</v>
+      </c>
       <c r="B127" s="22" t="s">
-        <v>108</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="C127" s="26"/>
       <c r="D127" s="16" t="s">
-        <v>122</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="E127" s="26"/>
+      <c r="F127" s="26"/>
+      <c r="G127" s="26"/>
+      <c r="H127" s="26"/>
+      <c r="I127" s="26"/>
+      <c r="J127" s="26"/>
+      <c r="K127" s="26"/>
+      <c r="L127" s="26"/>
+      <c r="M127" s="26"/>
+      <c r="N127" s="26"/>
+      <c r="O127" s="26"/>
+      <c r="P127" s="26"/>
+      <c r="Q127" s="26"/>
+      <c r="R127" s="26"/>
+      <c r="S127" s="26"/>
+      <c r="T127" s="26"/>
+      <c r="U127" s="26"/>
+      <c r="V127" s="26"/>
+      <c r="W127" s="26"/>
+      <c r="X127" s="26"/>
+      <c r="Y127" s="26"/>
+      <c r="Z127" s="26"/>
+      <c r="AA127" s="26"/>
+      <c r="AB127" s="26"/>
     </row>
     <row r="128">
-      <c r="A128" s="25"/>
+      <c r="A128" s="25" t="s">
+        <v>253</v>
+      </c>
       <c r="B128" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="C128" s="25"/>
+        <v>219</v>
+      </c>
+      <c r="C128" s="26"/>
       <c r="D128" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="E128" s="25"/>
-      <c r="F128" s="25"/>
-      <c r="G128" s="25"/>
-      <c r="H128" s="25"/>
-      <c r="I128" s="25"/>
-      <c r="J128" s="25"/>
-      <c r="K128" s="25"/>
-      <c r="L128" s="25"/>
-      <c r="M128" s="25"/>
-      <c r="N128" s="25"/>
-      <c r="O128" s="25"/>
-      <c r="P128" s="25"/>
-      <c r="Q128" s="25"/>
-      <c r="R128" s="25"/>
-      <c r="S128" s="25"/>
-      <c r="T128" s="25"/>
-      <c r="U128" s="25"/>
-      <c r="V128" s="25"/>
-      <c r="W128" s="25"/>
-      <c r="X128" s="25"/>
-      <c r="Y128" s="25"/>
-      <c r="Z128" s="25"/>
-      <c r="AA128" s="25"/>
-      <c r="AB128" s="25"/>
+        <v>254</v>
+      </c>
+      <c r="E128" s="26"/>
+      <c r="F128" s="26"/>
+      <c r="G128" s="26"/>
+      <c r="H128" s="26"/>
+      <c r="I128" s="26"/>
+      <c r="J128" s="26"/>
+      <c r="K128" s="26"/>
+      <c r="L128" s="26"/>
+      <c r="M128" s="26"/>
+      <c r="N128" s="26"/>
+      <c r="O128" s="26"/>
+      <c r="P128" s="26"/>
+      <c r="Q128" s="26"/>
+      <c r="R128" s="26"/>
+      <c r="S128" s="26"/>
+      <c r="T128" s="26"/>
+      <c r="U128" s="26"/>
+      <c r="V128" s="26"/>
+      <c r="W128" s="26"/>
+      <c r="X128" s="26"/>
+      <c r="Y128" s="26"/>
+      <c r="Z128" s="26"/>
+      <c r="AA128" s="26"/>
+      <c r="AB128" s="26"/>
     </row>
     <row r="129">
-      <c r="A129" s="25"/>
+      <c r="A129" s="25" t="s">
+        <v>255</v>
+      </c>
       <c r="B129" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="C129" s="25"/>
+        <v>219</v>
+      </c>
+      <c r="C129" s="26"/>
       <c r="D129" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="E129" s="25"/>
-      <c r="F129" s="25"/>
-      <c r="G129" s="25"/>
-      <c r="H129" s="25"/>
-      <c r="I129" s="25"/>
-      <c r="J129" s="25"/>
-      <c r="K129" s="25"/>
-      <c r="L129" s="25"/>
-      <c r="M129" s="25"/>
-      <c r="N129" s="25"/>
-      <c r="O129" s="25"/>
-      <c r="P129" s="25"/>
-      <c r="Q129" s="25"/>
-      <c r="R129" s="25"/>
-      <c r="S129" s="25"/>
-      <c r="T129" s="25"/>
-      <c r="U129" s="25"/>
-      <c r="V129" s="25"/>
-      <c r="W129" s="25"/>
-      <c r="X129" s="25"/>
-      <c r="Y129" s="25"/>
-      <c r="Z129" s="25"/>
-      <c r="AA129" s="25"/>
-      <c r="AB129" s="25"/>
+        <v>256</v>
+      </c>
+      <c r="E129" s="26"/>
+      <c r="F129" s="26"/>
+      <c r="G129" s="26"/>
+      <c r="H129" s="26"/>
+      <c r="I129" s="26"/>
+      <c r="J129" s="26"/>
+      <c r="K129" s="26"/>
+      <c r="L129" s="26"/>
+      <c r="M129" s="26"/>
+      <c r="N129" s="26"/>
+      <c r="O129" s="26"/>
+      <c r="P129" s="26"/>
+      <c r="Q129" s="26"/>
+      <c r="R129" s="26"/>
+      <c r="S129" s="26"/>
+      <c r="T129" s="26"/>
+      <c r="U129" s="26"/>
+      <c r="V129" s="26"/>
+      <c r="W129" s="26"/>
+      <c r="X129" s="26"/>
+      <c r="Y129" s="26"/>
+      <c r="Z129" s="26"/>
+      <c r="AA129" s="26"/>
+      <c r="AB129" s="26"/>
     </row>
     <row r="130">
-      <c r="A130" s="25"/>
+      <c r="A130" s="25" t="s">
+        <v>257</v>
+      </c>
       <c r="B130" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="C130" s="25"/>
+        <v>219</v>
+      </c>
+      <c r="C130" s="26"/>
       <c r="D130" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="E130" s="25"/>
-      <c r="F130" s="25"/>
-      <c r="G130" s="25"/>
-      <c r="H130" s="25"/>
-      <c r="I130" s="25"/>
-      <c r="J130" s="25"/>
-      <c r="K130" s="25"/>
-      <c r="L130" s="25"/>
-      <c r="M130" s="25"/>
-      <c r="N130" s="25"/>
-      <c r="O130" s="25"/>
-      <c r="P130" s="25"/>
-      <c r="Q130" s="25"/>
-      <c r="R130" s="25"/>
-      <c r="S130" s="25"/>
-      <c r="T130" s="25"/>
-      <c r="U130" s="25"/>
-      <c r="V130" s="25"/>
-      <c r="W130" s="25"/>
-      <c r="X130" s="25"/>
-      <c r="Y130" s="25"/>
-      <c r="Z130" s="25"/>
-      <c r="AA130" s="25"/>
-      <c r="AB130" s="25"/>
+        <v>258</v>
+      </c>
+      <c r="E130" s="26"/>
+      <c r="F130" s="26"/>
+      <c r="G130" s="26"/>
+      <c r="H130" s="26"/>
+      <c r="I130" s="26"/>
+      <c r="J130" s="26"/>
+      <c r="K130" s="26"/>
+      <c r="L130" s="26"/>
+      <c r="M130" s="26"/>
+      <c r="N130" s="26"/>
+      <c r="O130" s="26"/>
+      <c r="P130" s="26"/>
+      <c r="Q130" s="26"/>
+      <c r="R130" s="26"/>
+      <c r="S130" s="26"/>
+      <c r="T130" s="26"/>
+      <c r="U130" s="26"/>
+      <c r="V130" s="26"/>
+      <c r="W130" s="26"/>
+      <c r="X130" s="26"/>
+      <c r="Y130" s="26"/>
+      <c r="Z130" s="26"/>
+      <c r="AA130" s="26"/>
+      <c r="AB130" s="26"/>
     </row>
     <row r="131">
-      <c r="A131" s="25"/>
+      <c r="A131" s="25" t="s">
+        <v>259</v>
+      </c>
       <c r="B131" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="C131" s="25"/>
+        <v>219</v>
+      </c>
+      <c r="C131" s="26"/>
       <c r="D131" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="E131" s="25"/>
-      <c r="F131" s="25"/>
-      <c r="G131" s="25"/>
-      <c r="H131" s="25"/>
-      <c r="I131" s="25"/>
-      <c r="J131" s="25"/>
-      <c r="K131" s="25"/>
-      <c r="L131" s="25"/>
-      <c r="M131" s="25"/>
-      <c r="N131" s="25"/>
-      <c r="O131" s="25"/>
-      <c r="P131" s="25"/>
-      <c r="Q131" s="25"/>
-      <c r="R131" s="25"/>
-      <c r="S131" s="25"/>
-      <c r="T131" s="25"/>
-      <c r="U131" s="25"/>
-      <c r="V131" s="25"/>
-      <c r="W131" s="25"/>
-      <c r="X131" s="25"/>
-      <c r="Y131" s="25"/>
-      <c r="Z131" s="25"/>
-      <c r="AA131" s="25"/>
-      <c r="AB131" s="25"/>
+        <v>260</v>
+      </c>
+      <c r="E131" s="26"/>
+      <c r="F131" s="26"/>
+      <c r="G131" s="26"/>
+      <c r="H131" s="26"/>
+      <c r="I131" s="26"/>
+      <c r="J131" s="26"/>
+      <c r="K131" s="26"/>
+      <c r="L131" s="26"/>
+      <c r="M131" s="26"/>
+      <c r="N131" s="26"/>
+      <c r="O131" s="26"/>
+      <c r="P131" s="26"/>
+      <c r="Q131" s="26"/>
+      <c r="R131" s="26"/>
+      <c r="S131" s="26"/>
+      <c r="T131" s="26"/>
+      <c r="U131" s="26"/>
+      <c r="V131" s="26"/>
+      <c r="W131" s="26"/>
+      <c r="X131" s="26"/>
+      <c r="Y131" s="26"/>
+      <c r="Z131" s="26"/>
+      <c r="AA131" s="26"/>
+      <c r="AB131" s="26"/>
     </row>
     <row r="132">
-      <c r="A132" s="25"/>
+      <c r="A132" s="25" t="s">
+        <v>261</v>
+      </c>
       <c r="B132" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="C132" s="25"/>
+        <v>219</v>
+      </c>
+      <c r="C132" s="26"/>
       <c r="D132" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="E132" s="25"/>
-      <c r="F132" s="25"/>
-      <c r="G132" s="25"/>
-      <c r="H132" s="25"/>
-      <c r="I132" s="25"/>
-      <c r="J132" s="25"/>
-      <c r="K132" s="25"/>
-      <c r="L132" s="25"/>
-      <c r="M132" s="25"/>
-      <c r="N132" s="25"/>
-      <c r="O132" s="25"/>
-      <c r="P132" s="25"/>
-      <c r="Q132" s="25"/>
-      <c r="R132" s="25"/>
-      <c r="S132" s="25"/>
-      <c r="T132" s="25"/>
-      <c r="U132" s="25"/>
-      <c r="V132" s="25"/>
-      <c r="W132" s="25"/>
-      <c r="X132" s="25"/>
-      <c r="Y132" s="25"/>
-      <c r="Z132" s="25"/>
-      <c r="AA132" s="25"/>
-      <c r="AB132" s="25"/>
+        <v>262</v>
+      </c>
+      <c r="E132" s="26"/>
+      <c r="F132" s="26"/>
+      <c r="G132" s="26"/>
+      <c r="H132" s="26"/>
+      <c r="I132" s="26"/>
+      <c r="J132" s="26"/>
+      <c r="K132" s="26"/>
+      <c r="L132" s="26"/>
+      <c r="M132" s="26"/>
+      <c r="N132" s="26"/>
+      <c r="O132" s="26"/>
+      <c r="P132" s="26"/>
+      <c r="Q132" s="26"/>
+      <c r="R132" s="26"/>
+      <c r="S132" s="26"/>
+      <c r="T132" s="26"/>
+      <c r="U132" s="26"/>
+      <c r="V132" s="26"/>
+      <c r="W132" s="26"/>
+      <c r="X132" s="26"/>
+      <c r="Y132" s="26"/>
+      <c r="Z132" s="26"/>
+      <c r="AA132" s="26"/>
+      <c r="AB132" s="26"/>
     </row>
     <row r="133">
-      <c r="A133" s="25"/>
+      <c r="A133" s="25" t="s">
+        <v>263</v>
+      </c>
       <c r="B133" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="C133" s="25"/>
-      <c r="D133" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="E133" s="25"/>
-      <c r="F133" s="25"/>
-      <c r="G133" s="25"/>
-      <c r="H133" s="25"/>
-      <c r="I133" s="25"/>
-      <c r="J133" s="25"/>
-      <c r="K133" s="25"/>
-      <c r="L133" s="25"/>
-      <c r="M133" s="25"/>
-      <c r="N133" s="25"/>
-      <c r="O133" s="25"/>
-      <c r="P133" s="25"/>
-      <c r="Q133" s="25"/>
-      <c r="R133" s="25"/>
-      <c r="S133" s="25"/>
-      <c r="T133" s="25"/>
-      <c r="U133" s="25"/>
-      <c r="V133" s="25"/>
-      <c r="W133" s="25"/>
-      <c r="X133" s="25"/>
-      <c r="Y133" s="25"/>
-      <c r="Z133" s="25"/>
-      <c r="AA133" s="25"/>
-      <c r="AB133" s="25"/>
+        <v>219</v>
+      </c>
+      <c r="C133" s="26"/>
+      <c r="D133" s="24" t="s">
+        <v>264</v>
+      </c>
+      <c r="E133" s="26"/>
+      <c r="F133" s="26"/>
+      <c r="G133" s="26"/>
+      <c r="H133" s="26"/>
+      <c r="I133" s="26"/>
+      <c r="J133" s="26"/>
+      <c r="K133" s="26"/>
+      <c r="L133" s="26"/>
+      <c r="M133" s="26"/>
+      <c r="N133" s="26"/>
+      <c r="O133" s="26"/>
+      <c r="P133" s="26"/>
+      <c r="Q133" s="26"/>
+      <c r="R133" s="26"/>
+      <c r="S133" s="26"/>
+      <c r="T133" s="26"/>
+      <c r="U133" s="26"/>
+      <c r="V133" s="26"/>
+      <c r="W133" s="26"/>
+      <c r="X133" s="26"/>
+      <c r="Y133" s="26"/>
+      <c r="Z133" s="26"/>
+      <c r="AA133" s="26"/>
+      <c r="AB133" s="26"/>
     </row>
     <row r="134">
-      <c r="A134" s="25"/>
+      <c r="A134" s="25" t="s">
+        <v>265</v>
+      </c>
       <c r="B134" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="C134" s="25"/>
+        <v>219</v>
+      </c>
+      <c r="C134" s="26"/>
       <c r="D134" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="E134" s="25"/>
-      <c r="F134" s="25"/>
-      <c r="G134" s="25"/>
-      <c r="H134" s="25"/>
-      <c r="I134" s="25"/>
-      <c r="J134" s="25"/>
-      <c r="K134" s="25"/>
-      <c r="L134" s="25"/>
-      <c r="M134" s="25"/>
-      <c r="N134" s="25"/>
-      <c r="O134" s="25"/>
-      <c r="P134" s="25"/>
-      <c r="Q134" s="25"/>
-      <c r="R134" s="25"/>
-      <c r="S134" s="25"/>
-      <c r="T134" s="25"/>
-      <c r="U134" s="25"/>
-      <c r="V134" s="25"/>
-      <c r="W134" s="25"/>
-      <c r="X134" s="25"/>
-      <c r="Y134" s="25"/>
-      <c r="Z134" s="25"/>
-      <c r="AA134" s="25"/>
-      <c r="AB134" s="25"/>
+        <v>266</v>
+      </c>
+      <c r="E134" s="26"/>
+      <c r="F134" s="26"/>
+      <c r="G134" s="26"/>
+      <c r="H134" s="26"/>
+      <c r="I134" s="26"/>
+      <c r="J134" s="26"/>
+      <c r="K134" s="26"/>
+      <c r="L134" s="26"/>
+      <c r="M134" s="26"/>
+      <c r="N134" s="26"/>
+      <c r="O134" s="26"/>
+      <c r="P134" s="26"/>
+      <c r="Q134" s="26"/>
+      <c r="R134" s="26"/>
+      <c r="S134" s="26"/>
+      <c r="T134" s="26"/>
+      <c r="U134" s="26"/>
+      <c r="V134" s="26"/>
+      <c r="W134" s="26"/>
+      <c r="X134" s="26"/>
+      <c r="Y134" s="26"/>
+      <c r="Z134" s="26"/>
+      <c r="AA134" s="26"/>
+      <c r="AB134" s="26"/>
     </row>
     <row r="135">
-      <c r="A135" s="25"/>
+      <c r="A135" s="25" t="s">
+        <v>267</v>
+      </c>
       <c r="B135" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="C135" s="25"/>
+        <v>219</v>
+      </c>
+      <c r="C135" s="26"/>
       <c r="D135" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="E135" s="25"/>
-      <c r="F135" s="25"/>
-      <c r="G135" s="25"/>
-      <c r="H135" s="25"/>
-      <c r="I135" s="25"/>
-      <c r="J135" s="25"/>
-      <c r="K135" s="25"/>
-      <c r="L135" s="25"/>
-      <c r="M135" s="25"/>
-      <c r="N135" s="25"/>
-      <c r="O135" s="25"/>
-      <c r="P135" s="25"/>
-      <c r="Q135" s="25"/>
-      <c r="R135" s="25"/>
-      <c r="S135" s="25"/>
-      <c r="T135" s="25"/>
-      <c r="U135" s="25"/>
-      <c r="V135" s="25"/>
-      <c r="W135" s="25"/>
-      <c r="X135" s="25"/>
-      <c r="Y135" s="25"/>
-      <c r="Z135" s="25"/>
-      <c r="AA135" s="25"/>
-      <c r="AB135" s="25"/>
+        <v>268</v>
+      </c>
+      <c r="E135" s="26"/>
+      <c r="F135" s="26"/>
+      <c r="G135" s="26"/>
+      <c r="H135" s="26"/>
+      <c r="I135" s="26"/>
+      <c r="J135" s="26"/>
+      <c r="K135" s="26"/>
+      <c r="L135" s="26"/>
+      <c r="M135" s="26"/>
+      <c r="N135" s="26"/>
+      <c r="O135" s="26"/>
+      <c r="P135" s="26"/>
+      <c r="Q135" s="26"/>
+      <c r="R135" s="26"/>
+      <c r="S135" s="26"/>
+      <c r="T135" s="26"/>
+      <c r="U135" s="26"/>
+      <c r="V135" s="26"/>
+      <c r="W135" s="26"/>
+      <c r="X135" s="26"/>
+      <c r="Y135" s="26"/>
+      <c r="Z135" s="26"/>
+      <c r="AA135" s="26"/>
+      <c r="AB135" s="26"/>
     </row>
     <row r="136">
-      <c r="A136" s="25"/>
+      <c r="A136" s="25" t="s">
+        <v>269</v>
+      </c>
       <c r="B136" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="C136" s="25"/>
-      <c r="D136" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="E136" s="25"/>
-      <c r="F136" s="25"/>
-      <c r="G136" s="25"/>
-      <c r="H136" s="25"/>
-      <c r="I136" s="25"/>
-      <c r="J136" s="25"/>
-      <c r="K136" s="25"/>
-      <c r="L136" s="25"/>
-      <c r="M136" s="25"/>
-      <c r="N136" s="25"/>
-      <c r="O136" s="25"/>
-      <c r="P136" s="25"/>
-      <c r="Q136" s="25"/>
-      <c r="R136" s="25"/>
-      <c r="S136" s="25"/>
-      <c r="T136" s="25"/>
-      <c r="U136" s="25"/>
-      <c r="V136" s="25"/>
-      <c r="W136" s="25"/>
-      <c r="X136" s="25"/>
-      <c r="Y136" s="25"/>
-      <c r="Z136" s="25"/>
-      <c r="AA136" s="25"/>
-      <c r="AB136" s="25"/>
+        <v>219</v>
+      </c>
+      <c r="C136" s="26"/>
+      <c r="D136" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="E136" s="26"/>
+      <c r="F136" s="26"/>
+      <c r="G136" s="26"/>
+      <c r="H136" s="26"/>
+      <c r="I136" s="26"/>
+      <c r="J136" s="26"/>
+      <c r="K136" s="26"/>
+      <c r="L136" s="26"/>
+      <c r="M136" s="26"/>
+      <c r="N136" s="26"/>
+      <c r="O136" s="26"/>
+      <c r="P136" s="26"/>
+      <c r="Q136" s="26"/>
+      <c r="R136" s="26"/>
+      <c r="S136" s="26"/>
+      <c r="T136" s="26"/>
+      <c r="U136" s="26"/>
+      <c r="V136" s="26"/>
+      <c r="W136" s="26"/>
+      <c r="X136" s="26"/>
+      <c r="Y136" s="26"/>
+      <c r="Z136" s="26"/>
+      <c r="AA136" s="26"/>
+      <c r="AB136" s="26"/>
     </row>
     <row r="137">
-      <c r="A137" s="25"/>
+      <c r="A137" s="25" t="s">
+        <v>271</v>
+      </c>
       <c r="B137" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="C137" s="25"/>
+        <v>219</v>
+      </c>
+      <c r="C137" s="26"/>
       <c r="D137" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="E137" s="25"/>
-      <c r="F137" s="25"/>
-      <c r="G137" s="25"/>
-      <c r="H137" s="25"/>
-      <c r="I137" s="25"/>
-      <c r="J137" s="25"/>
-      <c r="K137" s="25"/>
-      <c r="L137" s="25"/>
-      <c r="M137" s="25"/>
-      <c r="N137" s="25"/>
-      <c r="O137" s="25"/>
-      <c r="P137" s="25"/>
-      <c r="Q137" s="25"/>
-      <c r="R137" s="25"/>
-      <c r="S137" s="25"/>
-      <c r="T137" s="25"/>
-      <c r="U137" s="25"/>
-      <c r="V137" s="25"/>
-      <c r="W137" s="25"/>
-      <c r="X137" s="25"/>
-      <c r="Y137" s="25"/>
-      <c r="Z137" s="25"/>
-      <c r="AA137" s="25"/>
-      <c r="AB137" s="25"/>
+        <v>272</v>
+      </c>
+      <c r="E137" s="26"/>
+      <c r="F137" s="26"/>
+      <c r="G137" s="26"/>
+      <c r="H137" s="26"/>
+      <c r="I137" s="26"/>
+      <c r="J137" s="26"/>
+      <c r="K137" s="26"/>
+      <c r="L137" s="26"/>
+      <c r="M137" s="26"/>
+      <c r="N137" s="26"/>
+      <c r="O137" s="26"/>
+      <c r="P137" s="26"/>
+      <c r="Q137" s="26"/>
+      <c r="R137" s="26"/>
+      <c r="S137" s="26"/>
+      <c r="T137" s="26"/>
+      <c r="U137" s="26"/>
+      <c r="V137" s="26"/>
+      <c r="W137" s="26"/>
+      <c r="X137" s="26"/>
+      <c r="Y137" s="26"/>
+      <c r="Z137" s="26"/>
+      <c r="AA137" s="26"/>
+      <c r="AB137" s="26"/>
     </row>
     <row r="138">
-      <c r="A138" s="25"/>
+      <c r="A138" s="22" t="s">
+        <v>273</v>
+      </c>
       <c r="B138" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="C138" s="25"/>
+        <v>219</v>
+      </c>
       <c r="D138" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="E138" s="25"/>
-      <c r="F138" s="25"/>
-      <c r="G138" s="25"/>
-      <c r="H138" s="25"/>
-      <c r="I138" s="25"/>
-      <c r="J138" s="25"/>
-      <c r="K138" s="25"/>
-      <c r="L138" s="25"/>
-      <c r="M138" s="25"/>
-      <c r="N138" s="25"/>
-      <c r="O138" s="25"/>
-      <c r="P138" s="25"/>
-      <c r="Q138" s="25"/>
-      <c r="R138" s="25"/>
-      <c r="S138" s="25"/>
-      <c r="T138" s="25"/>
-      <c r="U138" s="25"/>
-      <c r="V138" s="25"/>
-      <c r="W138" s="25"/>
-      <c r="X138" s="25"/>
-      <c r="Y138" s="25"/>
-      <c r="Z138" s="25"/>
-      <c r="AA138" s="25"/>
-      <c r="AB138" s="25"/>
+        <v>274</v>
+      </c>
     </row>
     <row r="139">
-      <c r="A139" s="25"/>
+      <c r="A139" s="22" t="s">
+        <v>275</v>
+      </c>
       <c r="B139" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="C139" s="25"/>
+        <v>219</v>
+      </c>
       <c r="D139" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="E139" s="25"/>
-      <c r="F139" s="25"/>
-      <c r="G139" s="25"/>
-      <c r="H139" s="25"/>
-      <c r="I139" s="25"/>
-      <c r="J139" s="25"/>
-      <c r="K139" s="25"/>
-      <c r="L139" s="25"/>
-      <c r="M139" s="25"/>
-      <c r="N139" s="25"/>
-      <c r="O139" s="25"/>
-      <c r="P139" s="25"/>
-      <c r="Q139" s="25"/>
-      <c r="R139" s="25"/>
-      <c r="S139" s="25"/>
-      <c r="T139" s="25"/>
-      <c r="U139" s="25"/>
-      <c r="V139" s="25"/>
-      <c r="W139" s="25"/>
-      <c r="X139" s="25"/>
-      <c r="Y139" s="25"/>
-      <c r="Z139" s="25"/>
-      <c r="AA139" s="25"/>
-      <c r="AB139" s="25"/>
+        <v>276</v>
+      </c>
     </row>
     <row r="140">
-      <c r="A140" s="25"/>
+      <c r="A140" s="22" t="s">
+        <v>277</v>
+      </c>
       <c r="B140" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="C140" s="25"/>
+        <v>219</v>
+      </c>
       <c r="D140" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="E140" s="25"/>
-      <c r="F140" s="25"/>
-      <c r="G140" s="25"/>
-      <c r="H140" s="25"/>
-      <c r="I140" s="25"/>
-      <c r="J140" s="25"/>
-      <c r="K140" s="25"/>
-      <c r="L140" s="25"/>
-      <c r="M140" s="25"/>
-      <c r="N140" s="25"/>
-      <c r="O140" s="25"/>
-      <c r="P140" s="25"/>
-      <c r="Q140" s="25"/>
-      <c r="R140" s="25"/>
-      <c r="S140" s="25"/>
-      <c r="T140" s="25"/>
-      <c r="U140" s="25"/>
-      <c r="V140" s="25"/>
-      <c r="W140" s="25"/>
-      <c r="X140" s="25"/>
-      <c r="Y140" s="25"/>
-      <c r="Z140" s="25"/>
-      <c r="AA140" s="25"/>
-      <c r="AB140" s="25"/>
+        <v>278</v>
+      </c>
     </row>
     <row r="141">
+      <c r="A141" s="22" t="s">
+        <v>279</v>
+      </c>
       <c r="B141" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D141" s="16" t="s">
-        <v>136</v>
+        <v>280</v>
       </c>
     </row>
     <row r="142">
+      <c r="A142" s="22" t="s">
+        <v>281</v>
+      </c>
       <c r="B142" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D142" s="16" t="s">
-        <v>137</v>
+        <v>282</v>
       </c>
     </row>
     <row r="143">
+      <c r="A143" s="22" t="s">
+        <v>283</v>
+      </c>
       <c r="B143" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D143" s="16" t="s">
-        <v>138</v>
+        <v>284</v>
       </c>
     </row>
     <row r="144">
+      <c r="A144" s="22" t="s">
+        <v>285</v>
+      </c>
       <c r="B144" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D144" s="16" t="s">
-        <v>139</v>
+        <v>286</v>
       </c>
     </row>
     <row r="145">
+      <c r="A145" s="22" t="s">
+        <v>287</v>
+      </c>
       <c r="B145" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D145" s="16" t="s">
-        <v>140</v>
+        <v>288</v>
       </c>
     </row>
     <row r="146">
+      <c r="A146" s="22" t="s">
+        <v>289</v>
+      </c>
       <c r="B146" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D146" s="16" t="s">
-        <v>141</v>
+        <v>290</v>
       </c>
     </row>
     <row r="147">
+      <c r="A147" s="22" t="s">
+        <v>291</v>
+      </c>
       <c r="B147" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D147" s="16" t="s">
-        <v>142</v>
+        <v>292</v>
       </c>
     </row>
     <row r="148">
+      <c r="A148" s="22" t="s">
+        <v>293</v>
+      </c>
       <c r="B148" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D148" s="16" t="s">
-        <v>143</v>
+        <v>294</v>
       </c>
     </row>
     <row r="149">
+      <c r="A149" s="22" t="s">
+        <v>295</v>
+      </c>
       <c r="B149" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D149" s="16" t="s">
-        <v>144</v>
+        <v>296</v>
       </c>
     </row>
     <row r="150">
+      <c r="A150" s="22" t="s">
+        <v>297</v>
+      </c>
       <c r="B150" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D150" s="16" t="s">
-        <v>145</v>
+        <v>298</v>
       </c>
     </row>
     <row r="151">
+      <c r="A151" s="22" t="s">
+        <v>299</v>
+      </c>
       <c r="B151" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D151" s="16" t="s">
-        <v>146</v>
+        <v>300</v>
       </c>
     </row>
     <row r="152">
+      <c r="A152" s="22" t="s">
+        <v>301</v>
+      </c>
       <c r="B152" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D152" s="16" t="s">
-        <v>147</v>
+        <v>219</v>
+      </c>
+      <c r="D152" s="24" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="153">
+      <c r="A153" s="22" t="s">
+        <v>303</v>
+      </c>
       <c r="B153" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D153" s="16" t="s">
-        <v>148</v>
+        <v>304</v>
       </c>
     </row>
     <row r="154">
+      <c r="A154" s="22" t="s">
+        <v>305</v>
+      </c>
       <c r="B154" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D154" s="16" t="s">
-        <v>149</v>
+        <v>306</v>
       </c>
     </row>
     <row r="155">
+      <c r="A155" s="22" t="s">
+        <v>307</v>
+      </c>
       <c r="B155" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D155" s="24" t="s">
-        <v>150</v>
+        <v>219</v>
+      </c>
+      <c r="D155" s="16" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="156">
+      <c r="A156" s="22" t="s">
+        <v>309</v>
+      </c>
       <c r="B156" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D156" s="16" t="s">
-        <v>151</v>
+        <v>310</v>
       </c>
     </row>
     <row r="157">
+      <c r="A157" s="22" t="s">
+        <v>311</v>
+      </c>
       <c r="B157" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D157" s="16" t="s">
-        <v>152</v>
+        <v>312</v>
       </c>
     </row>
     <row r="158">
+      <c r="A158" s="22" t="s">
+        <v>313</v>
+      </c>
       <c r="B158" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D158" s="16" t="s">
-        <v>153</v>
+        <v>314</v>
       </c>
     </row>
     <row r="159">
+      <c r="A159" s="22" t="s">
+        <v>315</v>
+      </c>
       <c r="B159" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D159" s="16" t="s">
-        <v>154</v>
+        <v>316</v>
       </c>
     </row>
     <row r="160">
+      <c r="A160" s="22" t="s">
+        <v>317</v>
+      </c>
       <c r="B160" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D160" s="16" t="s">
-        <v>155</v>
+        <v>219</v>
+      </c>
+      <c r="D160" s="24" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="161">
+      <c r="A161" s="22" t="s">
+        <v>319</v>
+      </c>
       <c r="B161" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D161" s="16" t="s">
-        <v>156</v>
+        <v>320</v>
       </c>
     </row>
     <row r="162">
+      <c r="A162" s="22" t="s">
+        <v>321</v>
+      </c>
       <c r="B162" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D162" s="16" t="s">
-        <v>157</v>
+        <v>322</v>
       </c>
     </row>
     <row r="163">
+      <c r="A163" s="22" t="s">
+        <v>323</v>
+      </c>
       <c r="B163" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D163" s="24" t="s">
-        <v>158</v>
+        <v>219</v>
+      </c>
+      <c r="D163" s="16" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="164">
+      <c r="A164" s="22" t="s">
+        <v>325</v>
+      </c>
       <c r="B164" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D164" s="16" t="s">
-        <v>159</v>
+        <v>326</v>
       </c>
     </row>
     <row r="165">
+      <c r="A165" s="22" t="s">
+        <v>327</v>
+      </c>
       <c r="B165" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D165" s="16" t="s">
-        <v>160</v>
+        <v>219</v>
+      </c>
+      <c r="D165" s="24" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="166">
+      <c r="A166" s="22" t="s">
+        <v>329</v>
+      </c>
       <c r="B166" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D166" s="16" t="s">
-        <v>161</v>
+        <v>330</v>
       </c>
     </row>
     <row r="167">
+      <c r="A167" s="22" t="s">
+        <v>331</v>
+      </c>
       <c r="B167" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D167" s="16" t="s">
-        <v>162</v>
+        <v>332</v>
       </c>
     </row>
     <row r="168">
+      <c r="A168" s="22" t="s">
+        <v>333</v>
+      </c>
       <c r="B168" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D168" s="24" t="s">
-        <v>163</v>
+        <v>219</v>
+      </c>
+      <c r="D168" s="16" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="169">
+      <c r="A169" s="22" t="s">
+        <v>335</v>
+      </c>
       <c r="B169" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D169" s="16" t="s">
-        <v>164</v>
+        <v>336</v>
       </c>
     </row>
     <row r="170">
+      <c r="A170" s="22" t="s">
+        <v>337</v>
+      </c>
       <c r="B170" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D170" s="16" t="s">
-        <v>165</v>
+        <v>338</v>
       </c>
     </row>
     <row r="171">
+      <c r="A171" s="22" t="s">
+        <v>339</v>
+      </c>
       <c r="B171" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D171" s="16" t="s">
-        <v>166</v>
+        <v>340</v>
       </c>
     </row>
     <row r="172">
+      <c r="A172" s="22" t="s">
+        <v>341</v>
+      </c>
       <c r="B172" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D172" s="16" t="s">
-        <v>167</v>
+        <v>342</v>
       </c>
     </row>
     <row r="173">
+      <c r="A173" s="22" t="s">
+        <v>343</v>
+      </c>
       <c r="B173" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D173" s="16" t="s">
-        <v>168</v>
+        <v>219</v>
+      </c>
+      <c r="D173" s="24" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="174">
+      <c r="A174" s="22" t="s">
+        <v>345</v>
+      </c>
       <c r="B174" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D174" s="16" t="s">
-        <v>169</v>
+        <v>346</v>
       </c>
     </row>
     <row r="175">
+      <c r="A175" s="22" t="s">
+        <v>347</v>
+      </c>
       <c r="B175" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D175" s="16" t="s">
-        <v>170</v>
+        <v>348</v>
       </c>
     </row>
     <row r="176">
+      <c r="A176" s="22" t="s">
+        <v>349</v>
+      </c>
       <c r="B176" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D176" s="24" t="s">
-        <v>171</v>
+        <v>219</v>
+      </c>
+      <c r="D176" s="18" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="177">
+      <c r="A177" s="22" t="s">
+        <v>351</v>
+      </c>
       <c r="B177" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D177" s="16" t="s">
-        <v>172</v>
+        <v>352</v>
       </c>
     </row>
     <row r="178">
+      <c r="A178" s="22" t="s">
+        <v>353</v>
+      </c>
       <c r="B178" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D178" s="16" t="s">
-        <v>173</v>
+        <v>354</v>
       </c>
     </row>
     <row r="179">
+      <c r="A179" s="22" t="s">
+        <v>355</v>
+      </c>
       <c r="B179" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D179" s="18" t="s">
-        <v>174</v>
+        <v>219</v>
+      </c>
+      <c r="D179" s="16" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="180">
+      <c r="A180" s="22" t="s">
+        <v>357</v>
+      </c>
       <c r="B180" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D180" s="16" t="s">
-        <v>175</v>
+        <v>358</v>
       </c>
     </row>
     <row r="181">
+      <c r="A181" s="22" t="s">
+        <v>359</v>
+      </c>
       <c r="B181" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D181" s="16" t="s">
-        <v>176</v>
+        <v>360</v>
       </c>
     </row>
     <row r="182">
+      <c r="A182" s="22" t="s">
+        <v>361</v>
+      </c>
       <c r="B182" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D182" s="16" t="s">
-        <v>177</v>
+        <v>362</v>
       </c>
     </row>
     <row r="183">
+      <c r="A183" s="22" t="s">
+        <v>363</v>
+      </c>
       <c r="B183" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D183" s="16" t="s">
-        <v>178</v>
+        <v>364</v>
       </c>
     </row>
     <row r="184">
+      <c r="A184" s="22" t="s">
+        <v>365</v>
+      </c>
       <c r="B184" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D184" s="16" t="s">
-        <v>179</v>
+        <v>366</v>
       </c>
     </row>
     <row r="185">
+      <c r="A185" s="22" t="s">
+        <v>367</v>
+      </c>
       <c r="B185" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D185" s="16" t="s">
-        <v>180</v>
+        <v>368</v>
       </c>
     </row>
     <row r="186">
+      <c r="A186" s="22" t="s">
+        <v>369</v>
+      </c>
       <c r="B186" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D186" s="16" t="s">
-        <v>181</v>
+        <v>219</v>
+      </c>
+      <c r="D186" s="24" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="187">
+      <c r="A187" s="22" t="s">
+        <v>371</v>
+      </c>
       <c r="B187" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D187" s="16" t="s">
-        <v>182</v>
+        <v>372</v>
       </c>
     </row>
     <row r="188">
+      <c r="A188" s="22" t="s">
+        <v>373</v>
+      </c>
       <c r="B188" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D188" s="16" t="s">
-        <v>183</v>
+        <v>374</v>
       </c>
     </row>
     <row r="189">
+      <c r="A189" s="22" t="s">
+        <v>375</v>
+      </c>
       <c r="B189" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D189" s="24" t="s">
-        <v>184</v>
+        <v>219</v>
+      </c>
+      <c r="D189" s="16" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="190">
+      <c r="A190" s="22" t="s">
+        <v>377</v>
+      </c>
       <c r="B190" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D190" s="16" t="s">
-        <v>185</v>
+        <v>378</v>
       </c>
     </row>
     <row r="191">
+      <c r="A191" s="22" t="s">
+        <v>379</v>
+      </c>
       <c r="B191" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D191" s="16" t="s">
-        <v>186</v>
+        <v>380</v>
       </c>
     </row>
     <row r="192">
+      <c r="A192" s="22" t="s">
+        <v>381</v>
+      </c>
       <c r="B192" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D192" s="16" t="s">
-        <v>187</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="E192" s="27"/>
     </row>
     <row r="193">
-      <c r="B193" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D193" s="16" t="s">
-        <v>188</v>
+      <c r="A193" s="22" t="s">
+        <v>383</v>
+      </c>
+      <c r="B193" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="E193" s="27" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="194">
+      <c r="A194" s="22" t="s">
+        <v>385</v>
+      </c>
       <c r="B194" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D194" s="16" t="s">
-        <v>189</v>
+        <v>386</v>
       </c>
     </row>
     <row r="195">
+      <c r="A195" s="22" t="s">
+        <v>387</v>
+      </c>
       <c r="B195" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D195" s="26" t="s">
-        <v>190</v>
+        <v>219</v>
+      </c>
+      <c r="D195" s="16" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="196">
+      <c r="A196" s="22" t="s">
+        <v>389</v>
+      </c>
       <c r="B196" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D196" s="16" t="s">
-        <v>191</v>
+        <v>390</v>
       </c>
     </row>
     <row r="197">
+      <c r="A197" s="22" t="s">
+        <v>391</v>
+      </c>
       <c r="B197" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D197" s="16" t="s">
-        <v>192</v>
+        <v>392</v>
       </c>
     </row>
     <row r="198">
+      <c r="A198" s="22" t="s">
+        <v>393</v>
+      </c>
       <c r="B198" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D198" s="16" t="s">
-        <v>193</v>
+        <v>394</v>
       </c>
     </row>
     <row r="199">
+      <c r="A199" s="22" t="s">
+        <v>395</v>
+      </c>
       <c r="B199" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D199" s="16" t="s">
-        <v>194</v>
+        <v>396</v>
       </c>
     </row>
     <row r="200">
+      <c r="A200" s="22" t="s">
+        <v>397</v>
+      </c>
       <c r="B200" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D200" s="16" t="s">
-        <v>195</v>
+        <v>398</v>
       </c>
     </row>
     <row r="201">
+      <c r="A201" s="22" t="s">
+        <v>399</v>
+      </c>
       <c r="B201" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D201" s="16" t="s">
-        <v>196</v>
+        <v>400</v>
       </c>
     </row>
     <row r="202">
+      <c r="A202" s="22" t="s">
+        <v>401</v>
+      </c>
       <c r="B202" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D202" s="16" t="s">
-        <v>197</v>
+        <v>402</v>
       </c>
     </row>
     <row r="203">
+      <c r="A203" s="22" t="s">
+        <v>403</v>
+      </c>
       <c r="B203" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D203" s="16" t="s">
-        <v>198</v>
+        <v>404</v>
       </c>
     </row>
     <row r="204">
+      <c r="A204" s="22" t="s">
+        <v>405</v>
+      </c>
       <c r="B204" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D204" s="16" t="s">
-        <v>199</v>
+        <v>406</v>
       </c>
     </row>
     <row r="205">
+      <c r="A205" s="22" t="s">
+        <v>407</v>
+      </c>
       <c r="B205" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D205" s="16" t="s">
-        <v>200</v>
+        <v>408</v>
       </c>
     </row>
     <row r="206">
+      <c r="A206" s="22" t="s">
+        <v>409</v>
+      </c>
       <c r="B206" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D206" s="16" t="s">
-        <v>201</v>
+        <v>410</v>
       </c>
     </row>
     <row r="207">
+      <c r="A207" s="22" t="s">
+        <v>411</v>
+      </c>
       <c r="B207" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D207" s="16" t="s">
-        <v>202</v>
+        <v>412</v>
       </c>
     </row>
     <row r="208">
+      <c r="A208" s="22" t="s">
+        <v>413</v>
+      </c>
       <c r="B208" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D208" s="16" t="s">
-        <v>203</v>
+        <v>414</v>
       </c>
     </row>
     <row r="209">
+      <c r="A209" s="22" t="s">
+        <v>415</v>
+      </c>
       <c r="B209" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D209" s="16" t="s">
-        <v>204</v>
+        <v>416</v>
       </c>
     </row>
     <row r="210">
+      <c r="A210" s="22" t="s">
+        <v>417</v>
+      </c>
       <c r="B210" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D210" s="16" t="s">
-        <v>205</v>
+        <v>418</v>
       </c>
     </row>
     <row r="211">
+      <c r="A211" s="22" t="s">
+        <v>419</v>
+      </c>
       <c r="B211" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D211" s="16" t="s">
-        <v>206</v>
+        <v>420</v>
       </c>
     </row>
     <row r="212">
+      <c r="A212" s="22" t="s">
+        <v>421</v>
+      </c>
       <c r="B212" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D212" s="16" t="s">
-        <v>207</v>
+        <v>422</v>
       </c>
     </row>
     <row r="213">
+      <c r="A213" s="22" t="s">
+        <v>423</v>
+      </c>
       <c r="B213" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D213" s="16" t="s">
-        <v>208</v>
+        <v>424</v>
       </c>
     </row>
     <row r="214">
+      <c r="A214" s="22" t="s">
+        <v>425</v>
+      </c>
       <c r="B214" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D214" s="16" t="s">
-        <v>209</v>
+        <v>426</v>
       </c>
     </row>
     <row r="215">
+      <c r="A215" s="22" t="s">
+        <v>427</v>
+      </c>
       <c r="B215" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D215" s="16" t="s">
-        <v>210</v>
+        <v>428</v>
       </c>
     </row>
     <row r="216">
+      <c r="A216" s="22" t="s">
+        <v>429</v>
+      </c>
       <c r="B216" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D216" s="16" t="s">
-        <v>211</v>
+        <v>430</v>
       </c>
     </row>
     <row r="217">
+      <c r="A217" s="22" t="s">
+        <v>431</v>
+      </c>
       <c r="B217" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D217" s="16" t="s">
-        <v>212</v>
+        <v>432</v>
       </c>
     </row>
     <row r="218">
+      <c r="A218" s="22" t="s">
+        <v>433</v>
+      </c>
       <c r="B218" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D218" s="16" t="s">
-        <v>213</v>
+        <v>219</v>
+      </c>
+      <c r="D218" s="29" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="219">
+      <c r="A219" s="22" t="s">
+        <v>435</v>
+      </c>
       <c r="B219" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D219" s="16" t="s">
-        <v>214</v>
+        <v>436</v>
       </c>
     </row>
     <row r="220">
+      <c r="A220" s="22" t="s">
+        <v>437</v>
+      </c>
       <c r="B220" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D220" s="27" t="s">
-        <v>215</v>
+        <v>219</v>
+      </c>
+      <c r="D220" s="16" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="221">
+      <c r="A221" s="22" t="s">
+        <v>439</v>
+      </c>
       <c r="B221" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D221" s="16" t="s">
-        <v>216</v>
+        <v>440</v>
       </c>
     </row>
     <row r="222">
+      <c r="A222" s="22" t="s">
+        <v>441</v>
+      </c>
       <c r="B222" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D222" s="16" t="s">
-        <v>217</v>
+        <v>442</v>
       </c>
     </row>
     <row r="223">
+      <c r="A223" s="22" t="s">
+        <v>443</v>
+      </c>
       <c r="B223" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D223" s="16" t="s">
-        <v>218</v>
+        <v>444</v>
       </c>
     </row>
     <row r="224">
+      <c r="A224" s="22" t="s">
+        <v>445</v>
+      </c>
       <c r="B224" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D224" s="16" t="s">
-        <v>219</v>
+        <v>446</v>
       </c>
     </row>
     <row r="225">
+      <c r="A225" s="22" t="s">
+        <v>447</v>
+      </c>
       <c r="B225" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D225" s="16" t="s">
-        <v>220</v>
+        <v>448</v>
       </c>
     </row>
     <row r="226">
+      <c r="A226" s="22" t="s">
+        <v>449</v>
+      </c>
       <c r="B226" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D226" s="16" t="s">
-        <v>221</v>
+        <v>450</v>
       </c>
     </row>
     <row r="227">
+      <c r="A227" s="22" t="s">
+        <v>451</v>
+      </c>
       <c r="B227" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D227" s="16" t="s">
-        <v>222</v>
+        <v>452</v>
       </c>
     </row>
     <row r="228">
+      <c r="A228" s="22" t="s">
+        <v>453</v>
+      </c>
       <c r="B228" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D228" s="16" t="s">
-        <v>223</v>
+        <v>454</v>
       </c>
     </row>
     <row r="229">
+      <c r="A229" s="22" t="s">
+        <v>455</v>
+      </c>
       <c r="B229" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D229" s="16" t="s">
-        <v>224</v>
+        <v>456</v>
       </c>
     </row>
     <row r="230">
+      <c r="A230" s="22" t="s">
+        <v>457</v>
+      </c>
       <c r="B230" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D230" s="16" t="s">
-        <v>225</v>
+        <v>458</v>
       </c>
     </row>
     <row r="231">
+      <c r="A231" s="22" t="s">
+        <v>459</v>
+      </c>
       <c r="B231" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D231" s="16" t="s">
-        <v>226</v>
+        <v>460</v>
       </c>
     </row>
     <row r="232">
+      <c r="A232" s="22" t="s">
+        <v>461</v>
+      </c>
       <c r="B232" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D232" s="16" t="s">
-        <v>227</v>
+        <v>462</v>
       </c>
     </row>
     <row r="233">
+      <c r="A233" s="22" t="s">
+        <v>463</v>
+      </c>
       <c r="B233" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D233" s="16" t="s">
-        <v>228</v>
+        <v>464</v>
       </c>
     </row>
     <row r="234">
+      <c r="A234" s="22" t="s">
+        <v>465</v>
+      </c>
       <c r="B234" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D234" s="16" t="s">
-        <v>229</v>
+        <v>466</v>
       </c>
     </row>
     <row r="235">
+      <c r="A235" s="22" t="s">
+        <v>467</v>
+      </c>
       <c r="B235" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D235" s="16" t="s">
-        <v>230</v>
+        <v>468</v>
       </c>
     </row>
     <row r="236">
+      <c r="A236" s="22" t="s">
+        <v>469</v>
+      </c>
       <c r="B236" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D236" s="16" t="s">
-        <v>231</v>
+        <v>470</v>
       </c>
     </row>
     <row r="237">
+      <c r="A237" s="22" t="s">
+        <v>471</v>
+      </c>
       <c r="B237" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D237" s="16" t="s">
-        <v>232</v>
+        <v>472</v>
       </c>
     </row>
     <row r="238">
+      <c r="A238" s="22" t="s">
+        <v>473</v>
+      </c>
       <c r="B238" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D238" s="16" t="s">
-        <v>233</v>
+        <v>474</v>
       </c>
     </row>
     <row r="239">
+      <c r="A239" s="22" t="s">
+        <v>475</v>
+      </c>
       <c r="B239" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D239" s="16" t="s">
-        <v>234</v>
+        <v>476</v>
       </c>
     </row>
     <row r="240">
+      <c r="A240" s="22" t="s">
+        <v>477</v>
+      </c>
       <c r="B240" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D240" s="16" t="s">
-        <v>235</v>
+        <v>478</v>
       </c>
     </row>
     <row r="241">
+      <c r="A241" s="22" t="s">
+        <v>479</v>
+      </c>
       <c r="B241" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D241" s="16" t="s">
-        <v>236</v>
+        <v>480</v>
       </c>
     </row>
     <row r="242">
+      <c r="A242" s="22" t="s">
+        <v>481</v>
+      </c>
       <c r="B242" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D242" s="16" t="s">
-        <v>237</v>
+        <v>482</v>
       </c>
     </row>
     <row r="243">
+      <c r="A243" s="22" t="s">
+        <v>483</v>
+      </c>
       <c r="B243" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D243" s="16" t="s">
-        <v>238</v>
+        <v>484</v>
       </c>
     </row>
     <row r="244">
+      <c r="A244" s="22" t="s">
+        <v>485</v>
+      </c>
       <c r="B244" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D244" s="16" t="s">
-        <v>239</v>
+        <v>486</v>
       </c>
     </row>
     <row r="245">
+      <c r="A245" s="22" t="s">
+        <v>487</v>
+      </c>
       <c r="B245" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D245" s="16" t="s">
-        <v>240</v>
+        <v>488</v>
       </c>
     </row>
     <row r="246">
+      <c r="A246" s="22" t="s">
+        <v>489</v>
+      </c>
       <c r="B246" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D246" s="16" t="s">
-        <v>241</v>
+        <v>490</v>
       </c>
     </row>
     <row r="247">
+      <c r="A247" s="22" t="s">
+        <v>491</v>
+      </c>
       <c r="B247" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D247" s="16" t="s">
-        <v>242</v>
+        <v>492</v>
       </c>
     </row>
     <row r="248">
+      <c r="A248" s="22" t="s">
+        <v>493</v>
+      </c>
       <c r="B248" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D248" s="16" t="s">
-        <v>243</v>
+        <v>494</v>
       </c>
     </row>
     <row r="249">
+      <c r="A249" s="22" t="s">
+        <v>495</v>
+      </c>
       <c r="B249" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D249" s="16" t="s">
-        <v>244</v>
+        <v>496</v>
       </c>
     </row>
     <row r="250">
+      <c r="A250" s="22" t="s">
+        <v>497</v>
+      </c>
       <c r="B250" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D250" s="16" t="s">
-        <v>245</v>
+        <v>498</v>
       </c>
     </row>
     <row r="251">
+      <c r="A251" s="22" t="s">
+        <v>499</v>
+      </c>
       <c r="B251" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D251" s="16" t="s">
-        <v>246</v>
+        <v>500</v>
       </c>
     </row>
     <row r="252">
+      <c r="A252" s="22" t="s">
+        <v>501</v>
+      </c>
       <c r="B252" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D252" s="16" t="s">
-        <v>247</v>
+        <v>502</v>
       </c>
     </row>
     <row r="253">
+      <c r="A253" s="22" t="s">
+        <v>503</v>
+      </c>
       <c r="B253" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D253" s="16" t="s">
-        <v>248</v>
+        <v>504</v>
       </c>
     </row>
     <row r="254">
+      <c r="A254" s="22" t="s">
+        <v>505</v>
+      </c>
       <c r="B254" s="22" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="D254" s="16" t="s">
-        <v>249</v>
+        <v>506</v>
       </c>
     </row>
     <row r="255">
+      <c r="A255" s="22" t="s">
+        <v>507</v>
+      </c>
       <c r="B255" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D255" s="16" t="s">
-        <v>250</v>
+        <v>219</v>
+      </c>
+      <c r="C255" s="22"/>
+      <c r="D255" s="30" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="256">
+      <c r="A256" s="22" t="s">
+        <v>509</v>
+      </c>
       <c r="B256" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D256" s="16" t="s">
-        <v>251</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="C256" s="22" t="s">
+        <v>510</v>
+      </c>
+      <c r="D256" s="16"/>
     </row>
     <row r="257">
+      <c r="A257" s="22" t="s">
+        <v>511</v>
+      </c>
       <c r="B257" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="C257" s="22"/>
-      <c r="D257" s="28" t="s">
-        <v>252</v>
+        <v>219</v>
+      </c>
+      <c r="C257" s="22" t="s">
+        <v>510</v>
+      </c>
+      <c r="D257" s="16" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="258">
-      <c r="B258" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="C258" s="29" t="s">
-        <v>253</v>
-      </c>
-      <c r="D258" s="16"/>
+      <c r="A258" s="22" t="s">
+        <v>513</v>
+      </c>
+      <c r="B258" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="C258" s="22" t="s">
+        <v>510</v>
+      </c>
+      <c r="D258" s="31" t="s">
+        <v>514</v>
+      </c>
     </row>
     <row r="259">
-      <c r="B259" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="C259" s="29" t="s">
-        <v>253</v>
-      </c>
-      <c r="D259" s="16" t="s">
-        <v>254</v>
-      </c>
+      <c r="A259" s="22" t="s">
+        <v>515</v>
+      </c>
+      <c r="B259" s="22" t="s">
+        <v>516</v>
+      </c>
+      <c r="C259" s="22"/>
+      <c r="D259" s="32"/>
     </row>
     <row r="260">
+      <c r="A260" s="22" t="s">
+        <v>517</v>
+      </c>
       <c r="B260" s="22" t="s">
-        <v>108</v>
+        <v>516</v>
       </c>
       <c r="C260" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="D260" s="26" t="s">
-        <v>255</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="D260" s="32"/>
     </row>
     <row r="261">
-      <c r="B261" s="29" t="s">
-        <v>256</v>
-      </c>
-      <c r="C261" s="22"/>
-      <c r="D261" s="30"/>
+      <c r="A261" s="22" t="s">
+        <v>519</v>
+      </c>
+      <c r="B261" s="22" t="s">
+        <v>516</v>
+      </c>
+      <c r="C261" s="22" t="s">
+        <v>520</v>
+      </c>
+      <c r="D261" s="32"/>
     </row>
     <row r="262">
+      <c r="A262" s="22" t="s">
+        <v>521</v>
+      </c>
       <c r="B262" s="22" t="s">
-        <v>256</v>
+        <v>516</v>
       </c>
       <c r="C262" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="D262" s="30"/>
+        <v>522</v>
+      </c>
+      <c r="D262" s="32"/>
     </row>
     <row r="263">
+      <c r="A263" s="22" t="s">
+        <v>523</v>
+      </c>
       <c r="B263" s="22" t="s">
-        <v>256</v>
+        <v>516</v>
       </c>
       <c r="C263" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="D263" s="30"/>
+        <v>524</v>
+      </c>
+      <c r="D263" s="32"/>
     </row>
     <row r="264">
+      <c r="A264" s="22" t="s">
+        <v>525</v>
+      </c>
       <c r="B264" s="22" t="s">
-        <v>256</v>
+        <v>516</v>
       </c>
       <c r="C264" s="22" t="s">
-        <v>259</v>
-      </c>
-      <c r="D264" s="30"/>
+        <v>526</v>
+      </c>
+      <c r="D264" s="33"/>
     </row>
     <row r="265">
-      <c r="B265" s="22" t="s">
-        <v>256</v>
-      </c>
-      <c r="C265" s="22" t="s">
-        <v>260</v>
-      </c>
-      <c r="D265" s="30"/>
+      <c r="D265" s="32"/>
     </row>
     <row r="266">
-      <c r="B266" s="22" t="s">
-        <v>256</v>
-      </c>
-      <c r="C266" s="22" t="s">
-        <v>261</v>
-      </c>
-      <c r="D266" s="31"/>
+      <c r="D266" s="32"/>
     </row>
     <row r="267">
-      <c r="D267" s="31"/>
+      <c r="D267" s="32"/>
     </row>
     <row r="268">
-      <c r="D268" s="31"/>
+      <c r="D268" s="34"/>
     </row>
     <row r="269">
-      <c r="D269" s="30"/>
+      <c r="D269" s="32"/>
     </row>
     <row r="270">
-      <c r="D270" s="30"/>
+      <c r="D270" s="32"/>
     </row>
     <row r="271">
-      <c r="D271" s="30"/>
+      <c r="D271" s="32"/>
     </row>
     <row r="272">
-      <c r="D272" s="32"/>
+      <c r="D272" s="34"/>
     </row>
     <row r="273">
-      <c r="D273" s="30"/>
+      <c r="D273" s="35"/>
     </row>
     <row r="274">
-      <c r="D274" s="30"/>
+      <c r="D274" s="32"/>
     </row>
     <row r="275">
-      <c r="D275" s="30"/>
+      <c r="D275" s="32"/>
     </row>
     <row r="276">
       <c r="D276" s="32"/>
     </row>
     <row r="277">
-      <c r="D277" s="33"/>
+      <c r="D277" s="34"/>
     </row>
     <row r="278">
-      <c r="D278" s="30"/>
+      <c r="D278" s="32"/>
     </row>
     <row r="279">
-      <c r="D279" s="30"/>
+      <c r="D279" s="32"/>
     </row>
     <row r="280">
-      <c r="D280" s="30"/>
+      <c r="D280" s="32"/>
     </row>
     <row r="281">
-      <c r="D281" s="32"/>
+      <c r="D281" s="34"/>
     </row>
     <row r="282">
-      <c r="D282" s="30"/>
+      <c r="D282" s="32"/>
     </row>
     <row r="283">
-      <c r="D283" s="30"/>
+      <c r="D283" s="36"/>
     </row>
     <row r="284">
-      <c r="D284" s="30"/>
+      <c r="D284" s="34"/>
     </row>
     <row r="285">
-      <c r="D285" s="32"/>
+      <c r="D285" s="34"/>
     </row>
     <row r="286">
-      <c r="D286" s="30"/>
+      <c r="D286" s="36"/>
     </row>
     <row r="287">
-      <c r="D287" s="34"/>
+      <c r="D287" s="36"/>
     </row>
     <row r="288">
-      <c r="D288" s="32"/>
+      <c r="D288" s="36"/>
     </row>
     <row r="289">
-      <c r="D289" s="32"/>
+      <c r="D289" s="36"/>
     </row>
     <row r="290">
       <c r="D290" s="34"/>
     </row>
     <row r="291">
-      <c r="D291" s="34"/>
+      <c r="D291" s="37"/>
     </row>
     <row r="292">
-      <c r="D292" s="34"/>
+      <c r="D292" s="36"/>
     </row>
     <row r="293">
-      <c r="D293" s="34"/>
+      <c r="D293" s="36"/>
     </row>
     <row r="294">
-      <c r="D294" s="32"/>
+      <c r="D294" s="34"/>
     </row>
     <row r="295">
-      <c r="D295" s="35"/>
+      <c r="D295" s="36"/>
     </row>
     <row r="296">
-      <c r="D296" s="34"/>
+      <c r="D296" s="36"/>
     </row>
     <row r="297">
       <c r="D297" s="34"/>
     </row>
     <row r="298">
-      <c r="D298" s="32"/>
+      <c r="D298" s="36"/>
     </row>
     <row r="299">
-      <c r="D299" s="34"/>
+      <c r="D299" s="36"/>
     </row>
     <row r="300">
       <c r="D300" s="34"/>
     </row>
     <row r="301">
-      <c r="D301" s="32"/>
+      <c r="D301" s="34"/>
     </row>
     <row r="302">
-      <c r="D302" s="34"/>
+      <c r="D302" s="36"/>
     </row>
     <row r="303">
-      <c r="D303" s="34"/>
+      <c r="D303" s="36"/>
     </row>
     <row r="304">
-      <c r="D304" s="32"/>
+      <c r="D304" s="36"/>
     </row>
     <row r="305">
-      <c r="D305" s="32"/>
+      <c r="D305" s="34"/>
     </row>
     <row r="306">
-      <c r="D306" s="34"/>
+      <c r="D306" s="36"/>
     </row>
     <row r="307">
-      <c r="D307" s="34"/>
+      <c r="D307" s="36"/>
     </row>
     <row r="308">
-      <c r="D308" s="34"/>
+      <c r="D308" s="36"/>
     </row>
     <row r="309">
-      <c r="D309" s="32"/>
+      <c r="D309" s="36"/>
     </row>
     <row r="310">
-      <c r="D310" s="34"/>
+      <c r="D310" s="36"/>
     </row>
     <row r="311">
-      <c r="D311" s="34"/>
+      <c r="D311" s="36"/>
     </row>
     <row r="312">
       <c r="D312" s="34"/>
     </row>
     <row r="313">
-      <c r="D313" s="34"/>
+      <c r="D313" s="36"/>
     </row>
     <row r="314">
-      <c r="D314" s="34"/>
+      <c r="D314" s="36"/>
     </row>
     <row r="315">
       <c r="D315" s="34"/>
     </row>
     <row r="316">
-      <c r="D316" s="32"/>
+      <c r="D316" s="36"/>
     </row>
     <row r="317">
-      <c r="D317" s="34"/>
+      <c r="D317" s="36"/>
     </row>
     <row r="318">
       <c r="D318" s="34"/>
     </row>
     <row r="319">
-      <c r="D319" s="32"/>
+      <c r="D319" s="34"/>
     </row>
     <row r="320">
       <c r="D320" s="34"/>
     </row>
     <row r="321">
-      <c r="D321" s="34"/>
+      <c r="D321" s="36"/>
     </row>
     <row r="322">
-      <c r="D322" s="32"/>
+      <c r="D322" s="36"/>
     </row>
     <row r="323">
-      <c r="D323" s="32"/>
+      <c r="D323" s="34"/>
     </row>
     <row r="324">
-      <c r="D324" s="32"/>
+      <c r="D324" s="34"/>
     </row>
     <row r="325">
-      <c r="D325" s="34"/>
+      <c r="D325" s="36"/>
     </row>
     <row r="326">
-      <c r="D326" s="34"/>
+      <c r="D326" s="36"/>
     </row>
     <row r="327">
-      <c r="D327" s="32"/>
+      <c r="D327" s="36"/>
     </row>
     <row r="328">
-      <c r="D328" s="32"/>
+      <c r="D328" s="36"/>
     </row>
     <row r="329">
       <c r="D329" s="34"/>
     </row>
     <row r="330">
-      <c r="D330" s="34"/>
+      <c r="D330" s="36"/>
     </row>
     <row r="331">
       <c r="D331" s="34"/>
@@ -4856,82 +6314,82 @@
       <c r="D332" s="34"/>
     </row>
     <row r="333">
-      <c r="D333" s="32"/>
+      <c r="D333" s="36"/>
     </row>
     <row r="334">
-      <c r="D334" s="34"/>
+      <c r="D334" s="36"/>
     </row>
     <row r="335">
-      <c r="D335" s="32"/>
+      <c r="D335" s="36"/>
     </row>
     <row r="336">
-      <c r="D336" s="32"/>
+      <c r="D336" s="34"/>
     </row>
     <row r="337">
       <c r="D337" s="34"/>
     </row>
     <row r="338">
-      <c r="D338" s="34"/>
+      <c r="D338" s="36"/>
     </row>
     <row r="339">
-      <c r="D339" s="34"/>
+      <c r="D339" s="36"/>
     </row>
     <row r="340">
-      <c r="D340" s="32"/>
+      <c r="D340" s="37"/>
     </row>
     <row r="341">
-      <c r="D341" s="32"/>
+      <c r="D341" s="36"/>
     </row>
     <row r="342">
-      <c r="D342" s="34"/>
+      <c r="D342" s="36"/>
     </row>
     <row r="343">
-      <c r="D343" s="34"/>
+      <c r="D343" s="36"/>
     </row>
     <row r="344">
-      <c r="D344" s="35"/>
+      <c r="D344" s="36"/>
     </row>
     <row r="345">
-      <c r="D345" s="34"/>
+      <c r="D345" s="36"/>
     </row>
     <row r="346">
-      <c r="D346" s="34"/>
+      <c r="D346" s="36"/>
     </row>
     <row r="347">
-      <c r="D347" s="34"/>
+      <c r="D347" s="36"/>
     </row>
     <row r="348">
-      <c r="D348" s="34"/>
+      <c r="D348" s="36"/>
     </row>
     <row r="349">
-      <c r="D349" s="34"/>
+      <c r="D349" s="37"/>
     </row>
     <row r="350">
-      <c r="D350" s="34"/>
+      <c r="D350" s="36"/>
     </row>
     <row r="351">
-      <c r="D351" s="34"/>
+      <c r="D351" s="36"/>
     </row>
     <row r="352">
-      <c r="D352" s="34"/>
+      <c r="D352" s="36"/>
     </row>
     <row r="353">
-      <c r="D353" s="35"/>
+      <c r="D353" s="36"/>
     </row>
     <row r="354">
-      <c r="D354" s="34"/>
+      <c r="D354" s="36"/>
     </row>
     <row r="355">
-      <c r="D355" s="34"/>
+      <c r="D355" s="38"/>
     </row>
     <row r="356">
-      <c r="D356" s="34"/>
+      <c r="D356" s="38"/>
     </row>
     <row r="357">
-      <c r="D357" s="34"/>
+      <c r="D357" s="36"/>
     </row>
     <row r="358">
-      <c r="D358" s="34"/>
+      <c r="D358" s="39"/>
     </row>
     <row r="359">
       <c r="D359" s="36"/>
@@ -4940,169 +6398,169 @@
       <c r="D360" s="36"/>
     </row>
     <row r="361">
-      <c r="D361" s="34"/>
+      <c r="D361" s="36"/>
     </row>
     <row r="362">
-      <c r="D362" s="37"/>
+      <c r="D362" s="36"/>
     </row>
     <row r="363">
-      <c r="D363" s="34"/>
+      <c r="D363" s="36"/>
     </row>
     <row r="364">
-      <c r="D364" s="34"/>
+      <c r="D364" s="36"/>
     </row>
     <row r="365">
-      <c r="D365" s="34"/>
+      <c r="D365" s="36"/>
     </row>
     <row r="366">
-      <c r="D366" s="34"/>
+      <c r="D366" s="36"/>
     </row>
     <row r="367">
-      <c r="D367" s="34"/>
+      <c r="D367" s="36"/>
     </row>
     <row r="368">
-      <c r="D368" s="34"/>
+      <c r="D368" s="36"/>
     </row>
     <row r="369">
-      <c r="D369" s="34"/>
+      <c r="D369" s="39"/>
     </row>
     <row r="370">
-      <c r="D370" s="34"/>
+      <c r="D370" s="36"/>
     </row>
     <row r="371">
-      <c r="D371" s="34"/>
+      <c r="D371" s="36"/>
     </row>
     <row r="372">
-      <c r="D372" s="34"/>
+      <c r="D372" s="36"/>
     </row>
     <row r="373">
-      <c r="D373" s="37"/>
+      <c r="D373" s="36"/>
     </row>
     <row r="374">
-      <c r="D374" s="34"/>
+      <c r="D374" s="36"/>
     </row>
     <row r="375">
-      <c r="D375" s="34"/>
+      <c r="D375" s="36"/>
     </row>
     <row r="376">
-      <c r="D376" s="34"/>
+      <c r="D376" s="36"/>
     </row>
     <row r="377">
-      <c r="D377" s="34"/>
+      <c r="D377" s="36"/>
     </row>
     <row r="378">
-      <c r="D378" s="34"/>
+      <c r="D378" s="36"/>
     </row>
     <row r="379">
-      <c r="D379" s="34"/>
+      <c r="D379" s="36"/>
     </row>
     <row r="380">
-      <c r="D380" s="34"/>
+      <c r="D380" s="36"/>
     </row>
     <row r="381">
-      <c r="D381" s="34"/>
+      <c r="D381" s="36"/>
     </row>
     <row r="382">
-      <c r="D382" s="34"/>
+      <c r="D382" s="36"/>
     </row>
     <row r="383">
-      <c r="D383" s="34"/>
+      <c r="D383" s="40"/>
     </row>
     <row r="384">
-      <c r="D384" s="34"/>
+      <c r="D384" s="36"/>
     </row>
     <row r="385">
-      <c r="D385" s="34"/>
+      <c r="D385" s="36"/>
     </row>
     <row r="386">
-      <c r="D386" s="34"/>
+      <c r="D386" s="36"/>
     </row>
     <row r="387">
-      <c r="D387" s="38"/>
+      <c r="D387" s="36"/>
     </row>
     <row r="388">
-      <c r="D388" s="34"/>
+      <c r="D388" s="36"/>
     </row>
     <row r="389">
-      <c r="D389" s="34"/>
+      <c r="D389" s="39"/>
     </row>
     <row r="390">
-      <c r="D390" s="34"/>
+      <c r="D390" s="39"/>
     </row>
     <row r="391">
-      <c r="D391" s="34"/>
+      <c r="D391" s="36"/>
     </row>
     <row r="392">
-      <c r="D392" s="34"/>
+      <c r="D392" s="36"/>
     </row>
     <row r="393">
-      <c r="D393" s="37"/>
+      <c r="D393" s="36"/>
     </row>
     <row r="394">
       <c r="D394" s="37"/>
     </row>
     <row r="395">
-      <c r="D395" s="34"/>
+      <c r="D395" s="36"/>
     </row>
     <row r="396">
-      <c r="D396" s="34"/>
+      <c r="D396" s="36"/>
     </row>
     <row r="397">
-      <c r="D397" s="34"/>
+      <c r="D397" s="36"/>
     </row>
     <row r="398">
-      <c r="D398" s="35"/>
+      <c r="D398" s="36"/>
     </row>
     <row r="399">
-      <c r="D399" s="34"/>
+      <c r="D399" s="36"/>
     </row>
     <row r="400">
-      <c r="D400" s="34"/>
+      <c r="D400" s="36"/>
     </row>
     <row r="401">
-      <c r="D401" s="34"/>
+      <c r="D401" s="37"/>
     </row>
     <row r="402">
-      <c r="D402" s="34"/>
+      <c r="D402" s="36"/>
     </row>
     <row r="403">
-      <c r="D403" s="34"/>
+      <c r="D403" s="36"/>
     </row>
     <row r="404">
-      <c r="D404" s="34"/>
+      <c r="D404" s="39"/>
     </row>
     <row r="405">
-      <c r="D405" s="35"/>
+      <c r="D405" s="41"/>
     </row>
     <row r="406">
-      <c r="D406" s="34"/>
+      <c r="D406" s="39"/>
     </row>
     <row r="407">
-      <c r="D407" s="34"/>
+      <c r="D407" s="39"/>
     </row>
     <row r="408">
-      <c r="D408" s="37"/>
+      <c r="D408" s="39"/>
     </row>
     <row r="409">
       <c r="D409" s="39"/>
     </row>
     <row r="410">
-      <c r="D410" s="37"/>
+      <c r="D410" s="39"/>
     </row>
     <row r="411">
-      <c r="D411" s="37"/>
+      <c r="D411" s="39"/>
     </row>
     <row r="412">
-      <c r="D412" s="37"/>
+      <c r="D412" s="41"/>
     </row>
     <row r="413">
-      <c r="D413" s="37"/>
+      <c r="D413" s="41"/>
     </row>
     <row r="414">
-      <c r="D414" s="37"/>
+      <c r="D414" s="39"/>
     </row>
     <row r="415">
-      <c r="D415" s="37"/>
+      <c r="D415" s="39"/>
     </row>
     <row r="416">
       <c r="D416" s="39"/>
@@ -5111,38 +6569,26 @@
       <c r="D417" s="39"/>
     </row>
     <row r="418">
-      <c r="D418" s="37"/>
+      <c r="D418" s="39"/>
     </row>
     <row r="419">
-      <c r="D419" s="37"/>
+      <c r="D419" s="39"/>
     </row>
     <row r="420">
-      <c r="D420" s="37"/>
+      <c r="D420" s="42"/>
     </row>
     <row r="421">
-      <c r="D421" s="37"/>
+      <c r="D421" s="39"/>
     </row>
     <row r="422">
-      <c r="D422" s="37"/>
+      <c r="D422" s="39"/>
     </row>
     <row r="423">
-      <c r="D423" s="37"/>
-    </row>
-    <row r="424">
-      <c r="D424" s="40"/>
-    </row>
-    <row r="425">
-      <c r="D425" s="37"/>
-    </row>
-    <row r="426">
-      <c r="D426" s="37"/>
-    </row>
-    <row r="427">
-      <c r="D427" s="37"/>
+      <c r="D423" s="39"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId2" ref="G115"/>
+    <hyperlink r:id="rId2" ref="G112"/>
   </hyperlinks>
   <drawing r:id="rId3"/>
   <legacyDrawing r:id="rId4"/>

--- a/sources/mercure-galant/mg-vocabulaire-estampes.xlsx
+++ b/sources/mercure-galant/mg-vocabulaire-estampes.xlsx
@@ -16,7 +16,7 @@
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="E36">
+    <comment authorId="0" ref="E37">
       <text>
         <t xml:space="preserve">Je ne comprends pas cette catégorie : un terme spécifique de plus ?
 	-Anne Piéjus
@@ -30,7 +30,7 @@
 	-Anne Piéjus</t>
       </text>
     </comment>
-    <comment authorId="0" ref="E102">
+    <comment authorId="0" ref="E107">
       <text>
         <t xml:space="preserve">En faire une sous-catégorie de "plans et vues"?
 	-Rebecca Bristow</t>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="556">
   <si>
     <t>uuid SHERLOCK</t>
   </si>
@@ -205,6 +205,12 @@
     <t>Décor</t>
   </si>
   <si>
+    <t>a90d7941-4161-4cd1-9cb6-743e64808eef</t>
+  </si>
+  <si>
+    <t>Décor architectural</t>
+  </si>
+  <si>
     <t>e457afad-9d51-4b6b-9aea-95190de29622</t>
   </si>
   <si>
@@ -313,9 +319,6 @@
     <t>1617f639-9650-468d-bd55-d466d556acc3</t>
   </si>
   <si>
-    <t>Thèmes mythologiques</t>
-  </si>
-  <si>
     <t>65cd719c-b518-43f2-90ce-cf586be3bb9f</t>
   </si>
   <si>
@@ -589,15 +592,39 @@
     <t>d9472929-7d74-472b-b0e4-f5a8db308777</t>
   </si>
   <si>
+    <t>Foi</t>
+  </si>
+  <si>
+    <t>ec5204b2-ae90-48e6-ba6e-0b3c6f6de0bb</t>
+  </si>
+  <si>
+    <t>Hérésie</t>
+  </si>
+  <si>
+    <t>0ea23c72-d61b-47e6-a9c8-6141daac5333</t>
+  </si>
+  <si>
+    <t>Justice</t>
+  </si>
+  <si>
+    <t>494ff45a-b4ed-43e3-b847-4855faa9f7e8</t>
+  </si>
+  <si>
+    <t>Paix</t>
+  </si>
+  <si>
+    <t>5d4b345e-c6c4-4bb4-a2cb-d22fb349bf83</t>
+  </si>
+  <si>
+    <t>Renommée</t>
+  </si>
+  <si>
+    <t>e5d5fa87-b9f7-4f74-be52-692a8039c3ba</t>
+  </si>
+  <si>
     <t>Victoire</t>
   </si>
   <si>
-    <t>0ea23c72-d61b-47e6-a9c8-6141daac5333</t>
-  </si>
-  <si>
-    <t>Renommée</t>
-  </si>
-  <si>
     <t>9a7371f3-7ea9-4601-b153-d2e4bc41839a</t>
   </si>
   <si>
@@ -607,13 +634,13 @@
     <t>a5c88f23-61c0-4f5d-9462-4a195aabdb83</t>
   </si>
   <si>
-    <t>portraits</t>
+    <t>Portraits</t>
   </si>
   <si>
     <t>ed1ef934-8d85-4748-aa7f-5b57139a041a</t>
   </si>
   <si>
-    <t>tables généalogiques</t>
+    <t>Tables généalogiques</t>
   </si>
   <si>
     <t>824d0bc5-2b7d-49bc-b6eb-e628bf1132de</t>
@@ -625,9 +652,6 @@
     <t>b5d30e99-ee89-4d03-94a3-86bdb7a977c4</t>
   </si>
   <si>
-    <t>Architecture navale [galères, etc.]</t>
-  </si>
-  <si>
     <t>e7eb5069-2f2c-4f8d-b743-97a2b76cc945</t>
   </si>
   <si>
@@ -718,6 +742,12 @@
     <t>Afrique</t>
   </si>
   <si>
+    <t>bbafa2c8-89dd-42e3-9e10-9f8cb68de3e0</t>
+  </si>
+  <si>
+    <t>aigle</t>
+  </si>
+  <si>
     <t>cae379a4-e9c5-482f-bb6d-22fbfb66c768</t>
   </si>
   <si>
@@ -739,7 +769,7 @@
     <t>03007121-060a-42f3-88e2-bcb903419bb5</t>
   </si>
   <si>
-    <t>apothicaire;</t>
+    <t>apothicaire</t>
   </si>
   <si>
     <t>af8d50c9-e044-4fc8-8332-e9a1655afc88</t>
@@ -751,6 +781,12 @@
     <t>ba74c06f-883c-48c2-b90f-275ada89728c</t>
   </si>
   <si>
+    <t>armée</t>
+  </si>
+  <si>
+    <t>42be6bc4-3d04-4794-a180-9868a0b96e99</t>
+  </si>
+  <si>
     <t>armée navale</t>
   </si>
   <si>
@@ -865,7 +901,7 @@
     <t>eb8e2fbd-8608-47dd-bd41-1cde1c255c3b</t>
   </si>
   <si>
-    <t>chapelle;</t>
+    <t>chapelle</t>
   </si>
   <si>
     <t>376d071d-41bb-4b0a-906e-c400ea4fd57d</t>
@@ -880,6 +916,12 @@
     <t>château</t>
   </si>
   <si>
+    <t>48e7a96b-367f-4428-8d25-f0801f203109</t>
+  </si>
+  <si>
+    <t>cheval</t>
+  </si>
+  <si>
     <t>54ee474a-c6c7-4657-a616-dbc97ff7a9ef</t>
   </si>
   <si>
@@ -904,6 +946,12 @@
     <t>coiffe</t>
   </si>
   <si>
+    <t>ec26e419-6de7-4cfb-8062-2a047cf0fa9c</t>
+  </si>
+  <si>
+    <t>colonne</t>
+  </si>
+  <si>
     <t>03ae9e0b-6d2b-4009-ad22-fa1ee5f08594</t>
   </si>
   <si>
@@ -997,7 +1045,7 @@
     <t>a17e6bee-16d0-40f7-970f-c1301f13b603</t>
   </si>
   <si>
-    <t>Épée, fer, lance</t>
+    <t>épée, fer, lance</t>
   </si>
   <si>
     <t>c79ea891-ddfa-4ac8-82b4-fd92544625cd</t>
@@ -1027,7 +1075,7 @@
     <t>2bb5b78b-820a-41d5-95f8-72333e357ba2</t>
   </si>
   <si>
-    <t>Fer VOIR Épée</t>
+    <t>fer VOIR épée</t>
   </si>
   <si>
     <t>35ed576c-5ced-4d40-99cf-b8f7d0e395cd</t>
@@ -1153,7 +1201,7 @@
     <t>111f765d-7a77-491c-a43f-1ae8e73f72b8</t>
   </si>
   <si>
-    <t>Lance VOIR Épée</t>
+    <t>lance VOIR épée</t>
   </si>
   <si>
     <t>5bcc849e-3526-49fc-aa48-5248326efff7</t>
@@ -1189,7 +1237,7 @@
     <t>01d08a1a-34ab-46f3-a97e-51b5bac7097d</t>
   </si>
   <si>
-    <t>Machines</t>
+    <t>machines</t>
   </si>
   <si>
     <t>e76eb366-e02b-40b8-bca2-18e36e87ae65</t>
@@ -1240,6 +1288,12 @@
     <t>médecine</t>
   </si>
   <si>
+    <t>43f3767a-7cc7-4466-9fca-256ec35c914b</t>
+  </si>
+  <si>
+    <t>mer</t>
+  </si>
+  <si>
     <t>7b097459-6b9f-4c6d-aa62-9fe72ead5884</t>
   </si>
   <si>
@@ -1414,6 +1468,12 @@
     <t>rive</t>
   </si>
   <si>
+    <t>39deddfa-9544-4b25-acf6-3d57b16807f9</t>
+  </si>
+  <si>
+    <t>rivière</t>
+  </si>
+  <si>
     <t>f44b8a55-2fe6-4171-8d07-e3397757c77e</t>
   </si>
   <si>
@@ -1591,21 +1651,30 @@
     <t>2a5a8714-1df5-4c95-bfa1-f718ca74ebc3</t>
   </si>
   <si>
-    <t>Techniques</t>
+    <t>Techniques de représentation</t>
   </si>
   <si>
     <t>a2426a2e-e7ff-459b-8a2c-62a89283d456</t>
   </si>
   <si>
-    <t>Dessin d’architecte ou d’ingénieur</t>
-  </si>
-  <si>
     <t>1dc4a653-6bc4-41aa-9816-ceaef586721d</t>
   </si>
   <si>
     <t>Élévation</t>
   </si>
   <si>
+    <t>2c841767-d9f1-4625-891d-d1678d3ac55b</t>
+  </si>
+  <si>
+    <t>plan cartographique</t>
+  </si>
+  <si>
+    <t>c833de17-295e-4488-8bab-e0df7deb6fa7</t>
+  </si>
+  <si>
+    <t>plan topographique</t>
+  </si>
+  <si>
     <t>4165c725-df6d-4737-a983-d3b906c1ad21</t>
   </si>
   <si>
@@ -1615,20 +1684,38 @@
     <t>595168fe-86d3-4602-b0f5-459b612260d3</t>
   </si>
   <si>
-    <t>Plan ou vue</t>
+    <t>relevé cartographique</t>
   </si>
   <si>
     <t>75ad55f0-bac5-40db-b531-ea506e39ef68</t>
   </si>
   <si>
     <t>Relevé décoratif</t>
+  </si>
+  <si>
+    <t>16ea0aa0-ceb0-4762-8c98-f1df5a92db6d</t>
+  </si>
+  <si>
+    <t>Techniques de gravure</t>
+  </si>
+  <si>
+    <t>f00a9443-466e-4be8-af02-5efc140c5c37</t>
+  </si>
+  <si>
+    <t>eau-forte</t>
+  </si>
+  <si>
+    <t>e8f2bb4f-f1ff-40bc-970f-3afc4087146e</t>
+  </si>
+  <si>
+    <t>burin</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1658,7 +1745,6 @@
       <color rgb="FF000000"/>
       <name val="&quot;docs-Roboto&quot;"/>
     </font>
-    <font/>
     <font>
       <color theme="1"/>
       <name val="Arial"/>
@@ -1694,12 +1780,13 @@
       <color rgb="FF0000FF"/>
     </font>
     <font>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Comic Sans MS"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="&quot;Arial&quot;"/>
     </font>
     <font>
       <sz val="12.0"/>
@@ -1719,12 +1806,18 @@
       <name val="&quot;Times New Roman&quot;"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FFFF"/>
+        <bgColor rgb="FF00FFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -1752,7 +1845,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1795,11 +1888,11 @@
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
@@ -1810,8 +1903,11 @@
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -1819,67 +1915,67 @@
     <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf borderId="2" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -2097,8 +2193,8 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="38.43"/>
     <col customWidth="1" min="2" max="2" width="20.57"/>
-    <col customWidth="1" min="3" max="3" width="30.0"/>
-    <col customWidth="1" min="4" max="4" width="36.43"/>
+    <col customWidth="1" min="3" max="3" width="21.0"/>
+    <col customWidth="1" min="4" max="4" width="21.14"/>
     <col customWidth="1" min="5" max="5" width="31.86"/>
     <col customWidth="1" min="6" max="7" width="37.14"/>
   </cols>
@@ -2528,7 +2624,7 @@
       <c r="G25" s="12"/>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -2537,12 +2633,12 @@
       <c r="C26" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
     </row>
     <row r="27">
       <c r="A27" s="13" t="s">
@@ -2554,12 +2650,12 @@
       <c r="C27" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
     </row>
     <row r="28">
       <c r="A28" s="13" t="s">
@@ -2571,12 +2667,12 @@
       <c r="C28" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
     </row>
     <row r="29">
       <c r="A29" s="13" t="s">
@@ -2588,12 +2684,12 @@
       <c r="C29" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
     </row>
     <row r="30">
       <c r="A30" s="13" t="s">
@@ -2605,12 +2701,12 @@
       <c r="C30" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
     </row>
     <row r="31">
       <c r="A31" s="13" t="s">
@@ -2622,12 +2718,12 @@
       <c r="C31" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
     </row>
     <row r="32">
       <c r="A32" s="13" t="s">
@@ -2636,30 +2732,30 @@
       <c r="B32" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
+      <c r="C32" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
     </row>
     <row r="33">
       <c r="A33" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D33" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
     </row>
     <row r="34">
       <c r="A34" s="13" t="s">
@@ -2668,13 +2764,15 @@
       <c r="B34" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
     </row>
     <row r="35">
       <c r="A35" s="13" t="s">
@@ -2683,15 +2781,13 @@
       <c r="B35" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" s="14" t="s">
+      <c r="C35" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
     </row>
     <row r="36">
       <c r="A36" s="13" t="s">
@@ -2700,15 +2796,13 @@
       <c r="B36" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" s="14" t="s">
+      <c r="C36" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="D36" s="13" t="s">
         <v>74</v>
       </c>
+      <c r="E36" s="14"/>
       <c r="F36" s="14"/>
       <c r="G36" s="14"/>
     </row>
@@ -2719,17 +2813,17 @@
       <c r="B37" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C37" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D37" s="14" t="s">
+      <c r="C37" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="D37" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
     </row>
     <row r="38">
       <c r="A38" s="13" t="s">
@@ -2738,17 +2832,17 @@
       <c r="B38" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D38" s="14" t="s">
+      <c r="C38" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="D38" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E38" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
     </row>
     <row r="39">
       <c r="A39" s="13" t="s">
@@ -2757,17 +2851,17 @@
       <c r="B39" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D39" s="14" t="s">
+      <c r="C39" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="D39" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E39" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
     </row>
     <row r="40">
       <c r="A40" s="13" t="s">
@@ -2776,17 +2870,17 @@
       <c r="B40" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C40" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D40" s="14" t="s">
+      <c r="C40" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="D40" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E40" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
     </row>
     <row r="41">
       <c r="A41" s="13" t="s">
@@ -2795,17 +2889,17 @@
       <c r="B41" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C41" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D41" s="14" t="s">
+      <c r="C41" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="D41" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E41" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
     </row>
     <row r="42">
       <c r="A42" s="13" t="s">
@@ -2814,17 +2908,17 @@
       <c r="B42" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D42" s="14" t="s">
+      <c r="C42" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="D42" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E42" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
     </row>
     <row r="43">
       <c r="A43" s="13" t="s">
@@ -2833,17 +2927,17 @@
       <c r="B43" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D43" s="14" t="s">
+      <c r="C43" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="D43" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E43" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
     </row>
     <row r="44">
       <c r="A44" s="13" t="s">
@@ -2852,17 +2946,17 @@
       <c r="B44" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D44" s="14" t="s">
+      <c r="C44" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="D44" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E44" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
     </row>
     <row r="45">
       <c r="A45" s="13" t="s">
@@ -2871,93 +2965,91 @@
       <c r="B45" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D45" s="14" t="s">
+      <c r="C45" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E45" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
+      <c r="D45" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
     </row>
     <row r="46">
       <c r="A46" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E46" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
     </row>
     <row r="47">
       <c r="A47" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E47" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D47" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E47" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="F47" s="16"/>
-      <c r="G47" s="17"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
     </row>
     <row r="48">
       <c r="A48" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E48" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E48" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="F48" s="16"/>
-      <c r="G48" s="17"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="16"/>
     </row>
     <row r="49">
       <c r="A49" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E49" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E49" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="F49" s="16"/>
-      <c r="G49" s="17"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="16"/>
     </row>
     <row r="50">
       <c r="A50" s="13" t="s">
@@ -2966,587 +3058,587 @@
       <c r="B50" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D50" s="14" t="s">
+      <c r="C50" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E50" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="F50" s="16"/>
-      <c r="G50" s="17"/>
+      <c r="D50" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="F50" s="15"/>
+      <c r="G50" s="16"/>
     </row>
     <row r="51">
       <c r="A51" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E51" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D51" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E51" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="F51" s="16"/>
-      <c r="G51" s="17"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="16"/>
     </row>
     <row r="52">
       <c r="A52" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E52" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E52" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="F52" s="16"/>
-      <c r="G52" s="17"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="16"/>
     </row>
     <row r="53">
       <c r="A53" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E53" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="F53" s="18"/>
-      <c r="G53" s="19"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="16"/>
     </row>
     <row r="54">
       <c r="A54" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E54" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D54" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E54" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="F54" s="16"/>
-      <c r="G54" s="17"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="18"/>
     </row>
     <row r="55">
       <c r="A55" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E55" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D55" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E55" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="F55" s="16"/>
-      <c r="G55" s="17"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="16"/>
     </row>
     <row r="56">
       <c r="A56" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E56" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D56" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E56" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="F56" s="16"/>
-      <c r="G56" s="17"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="16"/>
     </row>
     <row r="57">
       <c r="A57" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E57" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D57" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E57" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="F57" s="16"/>
-      <c r="G57" s="17"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="16"/>
     </row>
     <row r="58">
       <c r="A58" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E58" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D58" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E58" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="F58" s="16"/>
-      <c r="G58" s="17"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="16"/>
     </row>
     <row r="59">
       <c r="A59" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E59" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D59" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E59" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="F59" s="16"/>
-      <c r="G59" s="17"/>
+      <c r="F59" s="15"/>
+      <c r="G59" s="16"/>
     </row>
     <row r="60">
       <c r="A60" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E60" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D60" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E60" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="F60" s="16"/>
-      <c r="G60" s="17"/>
+      <c r="F60" s="15"/>
+      <c r="G60" s="16"/>
     </row>
     <row r="61">
       <c r="A61" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E61" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D61" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E61" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="F61" s="16"/>
-      <c r="G61" s="17"/>
+      <c r="F61" s="15"/>
+      <c r="G61" s="16"/>
     </row>
     <row r="62">
       <c r="A62" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D62" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E62" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D62" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E62" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="F62" s="16"/>
-      <c r="G62" s="17"/>
+      <c r="F62" s="15"/>
+      <c r="G62" s="16"/>
     </row>
     <row r="63">
       <c r="A63" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E63" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D63" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E63" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="F63" s="16"/>
-      <c r="G63" s="17"/>
+      <c r="F63" s="15"/>
+      <c r="G63" s="16"/>
     </row>
     <row r="64">
       <c r="A64" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E64" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D64" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E64" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="F64" s="16"/>
-      <c r="G64" s="17"/>
+      <c r="F64" s="15"/>
+      <c r="G64" s="16"/>
     </row>
     <row r="65">
       <c r="A65" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E65" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D65" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E65" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="F65" s="16"/>
-      <c r="G65" s="17"/>
+      <c r="F65" s="15"/>
+      <c r="G65" s="16"/>
     </row>
     <row r="66">
       <c r="A66" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E66" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C66" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D66" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E66" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="F66" s="16"/>
-      <c r="G66" s="17"/>
+      <c r="F66" s="15"/>
+      <c r="G66" s="16"/>
     </row>
     <row r="67">
       <c r="A67" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E67" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C67" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D67" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E67" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="F67" s="16"/>
-      <c r="G67" s="17"/>
+      <c r="F67" s="15"/>
+      <c r="G67" s="16"/>
     </row>
     <row r="68">
       <c r="A68" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D68" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E68" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C68" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D68" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E68" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="F68" s="16"/>
-      <c r="G68" s="17"/>
+      <c r="F68" s="15"/>
+      <c r="G68" s="16"/>
     </row>
     <row r="69">
       <c r="A69" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E69" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C69" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D69" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E69" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="F69" s="16"/>
-      <c r="G69" s="17"/>
+      <c r="F69" s="15"/>
+      <c r="G69" s="16"/>
     </row>
     <row r="70">
       <c r="A70" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E70" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C70" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D70" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E70" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="F70" s="16"/>
-      <c r="G70" s="17"/>
+      <c r="F70" s="15"/>
+      <c r="G70" s="16"/>
     </row>
     <row r="71">
       <c r="A71" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E71" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C71" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D71" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E71" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="F71" s="16"/>
-      <c r="G71" s="17"/>
+      <c r="F71" s="15"/>
+      <c r="G71" s="16"/>
     </row>
     <row r="72">
       <c r="A72" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E72" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C72" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D72" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E72" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="F72" s="16"/>
-      <c r="G72" s="17"/>
+      <c r="F72" s="15"/>
+      <c r="G72" s="16"/>
     </row>
     <row r="73">
       <c r="A73" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E73" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C73" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D73" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E73" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="F73" s="16"/>
-      <c r="G73" s="17"/>
+      <c r="F73" s="15"/>
+      <c r="G73" s="16"/>
     </row>
     <row r="74">
       <c r="A74" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E74" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C74" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D74" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E74" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="F74" s="16"/>
-      <c r="G74" s="17"/>
+      <c r="F74" s="15"/>
+      <c r="G74" s="16"/>
     </row>
     <row r="75">
       <c r="A75" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E75" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C75" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D75" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E75" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="F75" s="16"/>
-      <c r="G75" s="17"/>
+      <c r="F75" s="15"/>
+      <c r="G75" s="16"/>
     </row>
     <row r="76">
       <c r="A76" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E76" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="B76" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C76" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D76" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E76" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="F76" s="16"/>
-      <c r="G76" s="17"/>
+      <c r="F76" s="15"/>
+      <c r="G76" s="16"/>
     </row>
     <row r="77">
       <c r="A77" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E77" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C77" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D77" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E77" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="F77" s="16"/>
-      <c r="G77" s="17"/>
+      <c r="F77" s="15"/>
+      <c r="G77" s="16"/>
     </row>
     <row r="78">
       <c r="A78" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E78" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C78" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D78" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E78" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="F78" s="18"/>
-      <c r="G78" s="19"/>
+      <c r="F78" s="15"/>
+      <c r="G78" s="16"/>
     </row>
     <row r="79">
       <c r="A79" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D79" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E79" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C79" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D79" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E79" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="F79" s="16"/>
-      <c r="G79" s="17"/>
+      <c r="F79" s="17"/>
+      <c r="G79" s="18"/>
     </row>
     <row r="80">
       <c r="A80" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D80" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E80" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C80" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D80" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E80" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="F80" s="16"/>
-      <c r="G80" s="17"/>
+      <c r="F80" s="15"/>
+      <c r="G80" s="16"/>
     </row>
     <row r="81">
       <c r="A81" s="13" t="s">
@@ -3555,36 +3647,36 @@
       <c r="B81" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C81" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D81" s="14" t="s">
+      <c r="C81" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E81" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="F81" s="16"/>
-      <c r="G81" s="17"/>
+      <c r="D81" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E81" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="F81" s="15"/>
+      <c r="G81" s="16"/>
     </row>
     <row r="82">
       <c r="A82" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D82" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E82" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C82" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D82" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E82" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="F82" s="16"/>
-      <c r="G82" s="17"/>
+      <c r="F82" s="15"/>
+      <c r="G82" s="16"/>
     </row>
     <row r="83">
       <c r="A83" s="13" t="s">
@@ -3593,112 +3685,112 @@
       <c r="B83" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C83" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D83" s="14" t="s">
+      <c r="C83" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E83" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="F83" s="16"/>
-      <c r="G83" s="17"/>
+      <c r="D83" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E83" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="F83" s="15"/>
+      <c r="G83" s="16"/>
     </row>
     <row r="84">
       <c r="A84" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D84" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E84" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="B84" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C84" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D84" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E84" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="F84" s="16"/>
-      <c r="G84" s="17"/>
+      <c r="F84" s="15"/>
+      <c r="G84" s="16"/>
     </row>
     <row r="85">
       <c r="A85" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D85" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E85" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C85" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D85" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E85" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="F85" s="16"/>
-      <c r="G85" s="17"/>
+      <c r="F85" s="15"/>
+      <c r="G85" s="16"/>
     </row>
     <row r="86">
       <c r="A86" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D86" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E86" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C86" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D86" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E86" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="F86" s="18"/>
-      <c r="G86" s="19"/>
+      <c r="F86" s="15"/>
+      <c r="G86" s="16"/>
     </row>
     <row r="87">
       <c r="A87" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E87" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="B87" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C87" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D87" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E87" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="F87" s="16"/>
-      <c r="G87" s="17"/>
+      <c r="F87" s="17"/>
+      <c r="G87" s="18"/>
     </row>
     <row r="88">
       <c r="A88" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D88" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E88" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="B88" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C88" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D88" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E88" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="F88" s="16"/>
-      <c r="G88" s="17"/>
+      <c r="F88" s="15"/>
+      <c r="G88" s="16"/>
     </row>
     <row r="89">
       <c r="A89" s="13" t="s">
@@ -3707,215 +3799,227 @@
       <c r="B89" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C89" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D89" s="14" t="s">
+      <c r="C89" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E89" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="F89" s="16"/>
-      <c r="G89" s="17"/>
+      <c r="D89" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E89" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F89" s="15"/>
+      <c r="G89" s="16"/>
     </row>
     <row r="90">
       <c r="A90" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E90" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="B90" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C90" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="D90" s="14"/>
-      <c r="E90" s="16"/>
       <c r="F90" s="15"/>
-      <c r="G90" s="15"/>
+      <c r="G90" s="16"/>
     </row>
     <row r="91">
       <c r="A91" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="B91" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C91" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="D91" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="E91" s="16"/>
-      <c r="F91" s="15"/>
-      <c r="G91" s="15"/>
+      <c r="D91" s="13"/>
+      <c r="E91" s="15"/>
+      <c r="F91" s="14"/>
+      <c r="G91" s="14"/>
     </row>
     <row r="92">
       <c r="A92" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D92" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="B92" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C92" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="D92" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="E92" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="F92" s="15"/>
-      <c r="G92" s="15"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="14"/>
+      <c r="G92" s="14"/>
     </row>
     <row r="93">
       <c r="A93" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D93" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="E93" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C93" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="D93" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="E93" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="F93" s="15"/>
-      <c r="G93" s="15"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
     </row>
     <row r="94">
       <c r="A94" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="E94" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="B94" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C94" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="F94" s="15"/>
-      <c r="G94" s="15"/>
+      <c r="F94" s="14"/>
+      <c r="G94" s="14"/>
     </row>
     <row r="95">
       <c r="A95" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="E95" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C95" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="D95" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="F95" s="15"/>
-      <c r="G95" s="15"/>
+      <c r="F95" s="14"/>
+      <c r="G95" s="14"/>
     </row>
     <row r="96">
       <c r="A96" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="E96" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="B96" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C96" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="D96" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="F96" s="15"/>
-      <c r="G96" s="15"/>
+      <c r="F96" s="14"/>
+      <c r="G96" s="14"/>
     </row>
     <row r="97">
       <c r="A97" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D97" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="E97" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="B97" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C97" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="D97" s="14"/>
-      <c r="F97" s="15"/>
-      <c r="G97" s="15"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
     </row>
     <row r="98">
       <c r="A98" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="E98" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="B98" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C98" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="D98" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="F98" s="15"/>
-      <c r="G98" s="15"/>
+      <c r="F98" s="14"/>
+      <c r="G98" s="14"/>
     </row>
     <row r="99">
       <c r="A99" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C99" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="D99" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="E99" s="15"/>
-      <c r="F99" s="15"/>
-      <c r="G99" s="15"/>
+      <c r="F99" s="14"/>
+      <c r="G99" s="14"/>
     </row>
     <row r="100">
       <c r="A100" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="D100" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="B100" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C100" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="D100" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="E100" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="F100" s="15"/>
-      <c r="G100" s="15"/>
+      <c r="F100" s="14"/>
+      <c r="G100" s="14"/>
     </row>
     <row r="101">
       <c r="A101" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="D101" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="B101" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C101" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="D101" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="E101" s="15"/>
-      <c r="F101" s="15"/>
-      <c r="G101" s="15"/>
+      <c r="F101" s="14"/>
+      <c r="G101" s="14"/>
     </row>
     <row r="102">
       <c r="A102" s="13" t="s">
@@ -3924,17 +4028,12 @@
       <c r="B102" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C102" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="D102" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="E102" s="14" t="s">
+      <c r="C102" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="F102" s="15"/>
-      <c r="G102" s="15"/>
+      <c r="D102" s="13"/>
+      <c r="F102" s="14"/>
+      <c r="G102" s="14"/>
     </row>
     <row r="103">
       <c r="A103" s="13" t="s">
@@ -3943,553 +4042,412 @@
       <c r="B103" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C103" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="D103" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="E103" s="14" t="s">
-        <v>203</v>
-      </c>
+      <c r="C103" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="D103" s="13"/>
       <c r="F103" s="14"/>
-      <c r="G103" s="15"/>
+      <c r="G103" s="14"/>
     </row>
     <row r="104">
       <c r="A104" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="D104" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="B104" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C104" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="D104" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="E104" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="F104" s="15"/>
-      <c r="G104" s="15"/>
+      <c r="E104" s="14"/>
+      <c r="F104" s="14"/>
+      <c r="G104" s="14"/>
     </row>
     <row r="105">
       <c r="A105" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="D105" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="E105" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="B105" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C105" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="D105" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="E105" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="F105" s="15"/>
-      <c r="G105" s="15"/>
+      <c r="F105" s="14"/>
+      <c r="G105" s="14"/>
     </row>
     <row r="106">
       <c r="A106" s="13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C106" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="D106" s="15"/>
-      <c r="E106" s="21"/>
-      <c r="F106" s="15"/>
-      <c r="G106" s="15"/>
+      <c r="C106" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="D106" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="E106" s="14"/>
+      <c r="F106" s="14"/>
+      <c r="G106" s="14"/>
     </row>
     <row r="107">
       <c r="A107" s="13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C107" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="D107" s="15"/>
-      <c r="E107" s="15"/>
-      <c r="F107" s="15"/>
-      <c r="G107" s="15"/>
+      <c r="C107" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="D107" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="E107" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="F107" s="14"/>
+      <c r="G107" s="14"/>
     </row>
     <row r="108">
       <c r="A108" s="13" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C108" s="14" t="s">
+      <c r="C108" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="D108" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="E108" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="D108" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="E108" s="15"/>
-      <c r="F108" s="15"/>
-      <c r="G108" s="15"/>
+      <c r="F108" s="13"/>
+      <c r="G108" s="14"/>
     </row>
     <row r="109">
       <c r="A109" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C109" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="D109" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="E109" s="15"/>
-      <c r="F109" s="15"/>
-      <c r="G109" s="15"/>
+      <c r="C109" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="D109" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="E109" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="F109" s="14"/>
+      <c r="G109" s="14"/>
     </row>
     <row r="110">
       <c r="A110" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C110" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="D110" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="E110" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="F110" s="14"/>
+      <c r="G110" s="14"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="B110" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C110" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="D110" s="14" t="s">
+      <c r="B111" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C111" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="E110" s="15"/>
-      <c r="F110" s="15"/>
-      <c r="G110" s="15"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="22" t="s">
+      <c r="D111" s="14"/>
+      <c r="E111" s="21"/>
+      <c r="F111" s="14"/>
+      <c r="G111" s="14"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="B112" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="13" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="22" t="s">
+      <c r="D112" s="14"/>
+      <c r="E112" s="14"/>
+      <c r="F112" s="14"/>
+      <c r="G112" s="14"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="B112" s="22" t="s">
+      <c r="B113" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C113" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="D112" s="22" t="s">
+      <c r="D113" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="G112" s="23" t="s">
+      <c r="E113" s="14"/>
+      <c r="F113" s="14"/>
+      <c r="G113" s="14"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="13" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="22" t="s">
+      <c r="B114" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C114" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="D114" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="B113" s="22" t="s">
+      <c r="E114" s="14"/>
+      <c r="F114" s="14"/>
+      <c r="G114" s="14"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C115" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="D113" s="16" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="22" t="s">
+      <c r="D115" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="B114" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D114" s="24" t="s">
+      <c r="E115" s="14"/>
+      <c r="F115" s="14"/>
+      <c r="G115" s="14"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="19" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="22" t="s">
-        <v>227</v>
-      </c>
-      <c r="B115" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D115" s="16" t="s">
+      <c r="B116" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="19" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="22" t="s">
+      <c r="B117" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D117" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="B116" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D116" s="16" t="s">
+      <c r="G117" s="22" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="22" t="s">
+    <row r="118">
+      <c r="A118" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="B117" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D117" s="16" t="s">
+      <c r="B118" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D118" s="15" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="22" t="s">
+    <row r="119">
+      <c r="A119" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="B118" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D118" s="24" t="s">
+      <c r="B119" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D119" s="15" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="22" t="s">
+    <row r="120">
+      <c r="A120" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="B119" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D119" s="24" t="s">
+      <c r="B120" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D120" s="23" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="22" t="s">
+    <row r="121">
+      <c r="A121" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="B120" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D120" s="24" t="s">
+      <c r="B121" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D121" s="15" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="22" t="s">
+    <row r="122">
+      <c r="A122" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="B121" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D121" s="24" t="s">
+      <c r="B122" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D122" s="15" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="22" t="s">
+    <row r="123">
+      <c r="A123" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="B122" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D122" s="24" t="s">
+      <c r="B123" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D123" s="15" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="22" t="s">
+    <row r="124">
+      <c r="A124" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="B123" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D123" s="24" t="s">
+      <c r="B124" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D124" s="23" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="22" t="s">
+    <row r="125">
+      <c r="A125" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="B124" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D124" s="16" t="s">
+      <c r="B125" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D125" s="23" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="25" t="s">
+    <row r="126">
+      <c r="A126" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="B125" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="C125" s="26"/>
-      <c r="D125" s="16" t="s">
+      <c r="B126" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D126" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="E126" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="E125" s="26"/>
-      <c r="F125" s="26"/>
-      <c r="G125" s="26"/>
-      <c r="H125" s="26"/>
-      <c r="I125" s="26"/>
-      <c r="J125" s="26"/>
-      <c r="K125" s="26"/>
-      <c r="L125" s="26"/>
-      <c r="M125" s="26"/>
-      <c r="N125" s="26"/>
-      <c r="O125" s="26"/>
-      <c r="P125" s="26"/>
-      <c r="Q125" s="26"/>
-      <c r="R125" s="26"/>
-      <c r="S125" s="26"/>
-      <c r="T125" s="26"/>
-      <c r="U125" s="26"/>
-      <c r="V125" s="26"/>
-      <c r="W125" s="26"/>
-      <c r="X125" s="26"/>
-      <c r="Y125" s="26"/>
-      <c r="Z125" s="26"/>
-      <c r="AA125" s="26"/>
-      <c r="AB125" s="26"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="25" t="s">
+    </row>
+    <row r="127">
+      <c r="A127" s="19" t="s">
         <v>249</v>
       </c>
-      <c r="B126" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="C126" s="26"/>
-      <c r="D126" s="16" t="s">
+      <c r="B127" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D127" s="23" t="s">
         <v>250</v>
       </c>
-      <c r="E126" s="26"/>
-      <c r="F126" s="26"/>
-      <c r="G126" s="26"/>
-      <c r="H126" s="26"/>
-      <c r="I126" s="26"/>
-      <c r="J126" s="26"/>
-      <c r="K126" s="26"/>
-      <c r="L126" s="26"/>
-      <c r="M126" s="26"/>
-      <c r="N126" s="26"/>
-      <c r="O126" s="26"/>
-      <c r="P126" s="26"/>
-      <c r="Q126" s="26"/>
-      <c r="R126" s="26"/>
-      <c r="S126" s="26"/>
-      <c r="T126" s="26"/>
-      <c r="U126" s="26"/>
-      <c r="V126" s="26"/>
-      <c r="W126" s="26"/>
-      <c r="X126" s="26"/>
-      <c r="Y126" s="26"/>
-      <c r="Z126" s="26"/>
-      <c r="AA126" s="26"/>
-      <c r="AB126" s="26"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="25" t="s">
+    </row>
+    <row r="128">
+      <c r="A128" s="19" t="s">
         <v>251</v>
       </c>
-      <c r="B127" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="C127" s="26"/>
-      <c r="D127" s="16" t="s">
+      <c r="B128" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D128" s="24" t="s">
         <v>252</v>
       </c>
-      <c r="E127" s="26"/>
-      <c r="F127" s="26"/>
-      <c r="G127" s="26"/>
-      <c r="H127" s="26"/>
-      <c r="I127" s="26"/>
-      <c r="J127" s="26"/>
-      <c r="K127" s="26"/>
-      <c r="L127" s="26"/>
-      <c r="M127" s="26"/>
-      <c r="N127" s="26"/>
-      <c r="O127" s="26"/>
-      <c r="P127" s="26"/>
-      <c r="Q127" s="26"/>
-      <c r="R127" s="26"/>
-      <c r="S127" s="26"/>
-      <c r="T127" s="26"/>
-      <c r="U127" s="26"/>
-      <c r="V127" s="26"/>
-      <c r="W127" s="26"/>
-      <c r="X127" s="26"/>
-      <c r="Y127" s="26"/>
-      <c r="Z127" s="26"/>
-      <c r="AA127" s="26"/>
-      <c r="AB127" s="26"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="25" t="s">
+    </row>
+    <row r="129">
+      <c r="A129" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="B128" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="C128" s="26"/>
-      <c r="D128" s="16" t="s">
+      <c r="B129" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D129" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="E128" s="26"/>
-      <c r="F128" s="26"/>
-      <c r="G128" s="26"/>
-      <c r="H128" s="26"/>
-      <c r="I128" s="26"/>
-      <c r="J128" s="26"/>
-      <c r="K128" s="26"/>
-      <c r="L128" s="26"/>
-      <c r="M128" s="26"/>
-      <c r="N128" s="26"/>
-      <c r="O128" s="26"/>
-      <c r="P128" s="26"/>
-      <c r="Q128" s="26"/>
-      <c r="R128" s="26"/>
-      <c r="S128" s="26"/>
-      <c r="T128" s="26"/>
-      <c r="U128" s="26"/>
-      <c r="V128" s="26"/>
-      <c r="W128" s="26"/>
-      <c r="X128" s="26"/>
-      <c r="Y128" s="26"/>
-      <c r="Z128" s="26"/>
-      <c r="AA128" s="26"/>
-      <c r="AB128" s="26"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="25" t="s">
+    </row>
+    <row r="130">
+      <c r="A130" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="B129" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="C129" s="26"/>
-      <c r="D129" s="16" t="s">
+      <c r="B130" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D130" s="23" t="s">
         <v>256</v>
       </c>
-      <c r="E129" s="26"/>
-      <c r="F129" s="26"/>
-      <c r="G129" s="26"/>
-      <c r="H129" s="26"/>
-      <c r="I129" s="26"/>
-      <c r="J129" s="26"/>
-      <c r="K129" s="26"/>
-      <c r="L129" s="26"/>
-      <c r="M129" s="26"/>
-      <c r="N129" s="26"/>
-      <c r="O129" s="26"/>
-      <c r="P129" s="26"/>
-      <c r="Q129" s="26"/>
-      <c r="R129" s="26"/>
-      <c r="S129" s="26"/>
-      <c r="T129" s="26"/>
-      <c r="U129" s="26"/>
-      <c r="V129" s="26"/>
-      <c r="W129" s="26"/>
-      <c r="X129" s="26"/>
-      <c r="Y129" s="26"/>
-      <c r="Z129" s="26"/>
-      <c r="AA129" s="26"/>
-      <c r="AB129" s="26"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="25" t="s">
+    </row>
+    <row r="131">
+      <c r="A131" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="B130" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="C130" s="26"/>
-      <c r="D130" s="16" t="s">
+      <c r="B131" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D131" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="E130" s="26"/>
-      <c r="F130" s="26"/>
-      <c r="G130" s="26"/>
-      <c r="H130" s="26"/>
-      <c r="I130" s="26"/>
-      <c r="J130" s="26"/>
-      <c r="K130" s="26"/>
-      <c r="L130" s="26"/>
-      <c r="M130" s="26"/>
-      <c r="N130" s="26"/>
-      <c r="O130" s="26"/>
-      <c r="P130" s="26"/>
-      <c r="Q130" s="26"/>
-      <c r="R130" s="26"/>
-      <c r="S130" s="26"/>
-      <c r="T130" s="26"/>
-      <c r="U130" s="26"/>
-      <c r="V130" s="26"/>
-      <c r="W130" s="26"/>
-      <c r="X130" s="26"/>
-      <c r="Y130" s="26"/>
-      <c r="Z130" s="26"/>
-      <c r="AA130" s="26"/>
-      <c r="AB130" s="26"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="25" t="s">
-        <v>259</v>
-      </c>
-      <c r="B131" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="C131" s="26"/>
-      <c r="D131" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="E131" s="26"/>
-      <c r="F131" s="26"/>
-      <c r="G131" s="26"/>
-      <c r="H131" s="26"/>
-      <c r="I131" s="26"/>
-      <c r="J131" s="26"/>
-      <c r="K131" s="26"/>
-      <c r="L131" s="26"/>
-      <c r="M131" s="26"/>
-      <c r="N131" s="26"/>
-      <c r="O131" s="26"/>
-      <c r="P131" s="26"/>
-      <c r="Q131" s="26"/>
-      <c r="R131" s="26"/>
-      <c r="S131" s="26"/>
-      <c r="T131" s="26"/>
-      <c r="U131" s="26"/>
-      <c r="V131" s="26"/>
-      <c r="W131" s="26"/>
-      <c r="X131" s="26"/>
-      <c r="Y131" s="26"/>
-      <c r="Z131" s="26"/>
-      <c r="AA131" s="26"/>
-      <c r="AB131" s="26"/>
     </row>
     <row r="132">
       <c r="A132" s="25" t="s">
-        <v>261</v>
-      </c>
-      <c r="B132" s="22" t="s">
-        <v>219</v>
+        <v>259</v>
+      </c>
+      <c r="B132" s="19" t="s">
+        <v>227</v>
       </c>
       <c r="C132" s="26"/>
-      <c r="D132" s="16" t="s">
-        <v>262</v>
+      <c r="D132" s="15" t="s">
+        <v>260</v>
       </c>
       <c r="E132" s="26"/>
       <c r="F132" s="26"/>
@@ -4518,14 +4476,14 @@
     </row>
     <row r="133">
       <c r="A133" s="25" t="s">
-        <v>263</v>
-      </c>
-      <c r="B133" s="22" t="s">
-        <v>219</v>
+        <v>261</v>
+      </c>
+      <c r="B133" s="19" t="s">
+        <v>227</v>
       </c>
       <c r="C133" s="26"/>
-      <c r="D133" s="24" t="s">
-        <v>264</v>
+      <c r="D133" s="15" t="s">
+        <v>262</v>
       </c>
       <c r="E133" s="26"/>
       <c r="F133" s="26"/>
@@ -4554,14 +4512,14 @@
     </row>
     <row r="134">
       <c r="A134" s="25" t="s">
-        <v>265</v>
-      </c>
-      <c r="B134" s="22" t="s">
-        <v>219</v>
+        <v>263</v>
+      </c>
+      <c r="B134" s="19" t="s">
+        <v>227</v>
       </c>
       <c r="C134" s="26"/>
-      <c r="D134" s="16" t="s">
-        <v>266</v>
+      <c r="D134" s="15" t="s">
+        <v>264</v>
       </c>
       <c r="E134" s="26"/>
       <c r="F134" s="26"/>
@@ -4590,14 +4548,14 @@
     </row>
     <row r="135">
       <c r="A135" s="25" t="s">
-        <v>267</v>
-      </c>
-      <c r="B135" s="22" t="s">
-        <v>219</v>
+        <v>265</v>
+      </c>
+      <c r="B135" s="19" t="s">
+        <v>227</v>
       </c>
       <c r="C135" s="26"/>
-      <c r="D135" s="16" t="s">
-        <v>268</v>
+      <c r="D135" s="15" t="s">
+        <v>266</v>
       </c>
       <c r="E135" s="26"/>
       <c r="F135" s="26"/>
@@ -4626,14 +4584,14 @@
     </row>
     <row r="136">
       <c r="A136" s="25" t="s">
-        <v>269</v>
-      </c>
-      <c r="B136" s="22" t="s">
-        <v>219</v>
+        <v>267</v>
+      </c>
+      <c r="B136" s="19" t="s">
+        <v>227</v>
       </c>
       <c r="C136" s="26"/>
-      <c r="D136" s="16" t="s">
-        <v>270</v>
+      <c r="D136" s="15" t="s">
+        <v>268</v>
       </c>
       <c r="E136" s="26"/>
       <c r="F136" s="26"/>
@@ -4662,14 +4620,14 @@
     </row>
     <row r="137">
       <c r="A137" s="25" t="s">
-        <v>271</v>
-      </c>
-      <c r="B137" s="22" t="s">
-        <v>219</v>
+        <v>269</v>
+      </c>
+      <c r="B137" s="19" t="s">
+        <v>227</v>
       </c>
       <c r="C137" s="26"/>
-      <c r="D137" s="16" t="s">
-        <v>272</v>
+      <c r="D137" s="15" t="s">
+        <v>270</v>
       </c>
       <c r="E137" s="26"/>
       <c r="F137" s="26"/>
@@ -4697,1898 +4655,2241 @@
       <c r="AB137" s="26"/>
     </row>
     <row r="138">
-      <c r="A138" s="22" t="s">
+      <c r="A138" s="25" t="s">
+        <v>271</v>
+      </c>
+      <c r="B138" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="C138" s="26"/>
+      <c r="D138" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="E138" s="26"/>
+      <c r="F138" s="26"/>
+      <c r="G138" s="26"/>
+      <c r="H138" s="26"/>
+      <c r="I138" s="26"/>
+      <c r="J138" s="26"/>
+      <c r="K138" s="26"/>
+      <c r="L138" s="26"/>
+      <c r="M138" s="26"/>
+      <c r="N138" s="26"/>
+      <c r="O138" s="26"/>
+      <c r="P138" s="26"/>
+      <c r="Q138" s="26"/>
+      <c r="R138" s="26"/>
+      <c r="S138" s="26"/>
+      <c r="T138" s="26"/>
+      <c r="U138" s="26"/>
+      <c r="V138" s="26"/>
+      <c r="W138" s="26"/>
+      <c r="X138" s="26"/>
+      <c r="Y138" s="26"/>
+      <c r="Z138" s="26"/>
+      <c r="AA138" s="26"/>
+      <c r="AB138" s="26"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="25" t="s">
         <v>273</v>
       </c>
-      <c r="B138" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D138" s="16" t="s">
+      <c r="B139" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="C139" s="26"/>
+      <c r="D139" s="15" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="22" t="s">
+      <c r="E139" s="26"/>
+      <c r="F139" s="26"/>
+      <c r="G139" s="26"/>
+      <c r="H139" s="26"/>
+      <c r="I139" s="26"/>
+      <c r="J139" s="26"/>
+      <c r="K139" s="26"/>
+      <c r="L139" s="26"/>
+      <c r="M139" s="26"/>
+      <c r="N139" s="26"/>
+      <c r="O139" s="26"/>
+      <c r="P139" s="26"/>
+      <c r="Q139" s="26"/>
+      <c r="R139" s="26"/>
+      <c r="S139" s="26"/>
+      <c r="T139" s="26"/>
+      <c r="U139" s="26"/>
+      <c r="V139" s="26"/>
+      <c r="W139" s="26"/>
+      <c r="X139" s="26"/>
+      <c r="Y139" s="26"/>
+      <c r="Z139" s="26"/>
+      <c r="AA139" s="26"/>
+      <c r="AB139" s="26"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="25" t="s">
         <v>275</v>
       </c>
-      <c r="B139" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D139" s="16" t="s">
+      <c r="B140" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="C140" s="26"/>
+      <c r="D140" s="23" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="22" t="s">
+      <c r="E140" s="26"/>
+      <c r="F140" s="26"/>
+      <c r="G140" s="26"/>
+      <c r="H140" s="26"/>
+      <c r="I140" s="26"/>
+      <c r="J140" s="26"/>
+      <c r="K140" s="26"/>
+      <c r="L140" s="26"/>
+      <c r="M140" s="26"/>
+      <c r="N140" s="26"/>
+      <c r="O140" s="26"/>
+      <c r="P140" s="26"/>
+      <c r="Q140" s="26"/>
+      <c r="R140" s="26"/>
+      <c r="S140" s="26"/>
+      <c r="T140" s="26"/>
+      <c r="U140" s="26"/>
+      <c r="V140" s="26"/>
+      <c r="W140" s="26"/>
+      <c r="X140" s="26"/>
+      <c r="Y140" s="26"/>
+      <c r="Z140" s="26"/>
+      <c r="AA140" s="26"/>
+      <c r="AB140" s="26"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="25" t="s">
         <v>277</v>
       </c>
-      <c r="B140" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D140" s="16" t="s">
+      <c r="B141" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="C141" s="26"/>
+      <c r="D141" s="15" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="22" t="s">
+      <c r="E141" s="26"/>
+      <c r="F141" s="26"/>
+      <c r="G141" s="26"/>
+      <c r="H141" s="26"/>
+      <c r="I141" s="26"/>
+      <c r="J141" s="26"/>
+      <c r="K141" s="26"/>
+      <c r="L141" s="26"/>
+      <c r="M141" s="26"/>
+      <c r="N141" s="26"/>
+      <c r="O141" s="26"/>
+      <c r="P141" s="26"/>
+      <c r="Q141" s="26"/>
+      <c r="R141" s="26"/>
+      <c r="S141" s="26"/>
+      <c r="T141" s="26"/>
+      <c r="U141" s="26"/>
+      <c r="V141" s="26"/>
+      <c r="W141" s="26"/>
+      <c r="X141" s="26"/>
+      <c r="Y141" s="26"/>
+      <c r="Z141" s="26"/>
+      <c r="AA141" s="26"/>
+      <c r="AB141" s="26"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="B141" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D141" s="16" t="s">
+      <c r="B142" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="C142" s="26"/>
+      <c r="D142" s="15" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="22" t="s">
+      <c r="E142" s="26"/>
+      <c r="F142" s="26"/>
+      <c r="G142" s="26"/>
+      <c r="H142" s="26"/>
+      <c r="I142" s="26"/>
+      <c r="J142" s="26"/>
+      <c r="K142" s="26"/>
+      <c r="L142" s="26"/>
+      <c r="M142" s="26"/>
+      <c r="N142" s="26"/>
+      <c r="O142" s="26"/>
+      <c r="P142" s="26"/>
+      <c r="Q142" s="26"/>
+      <c r="R142" s="26"/>
+      <c r="S142" s="26"/>
+      <c r="T142" s="26"/>
+      <c r="U142" s="26"/>
+      <c r="V142" s="26"/>
+      <c r="W142" s="26"/>
+      <c r="X142" s="26"/>
+      <c r="Y142" s="26"/>
+      <c r="Z142" s="26"/>
+      <c r="AA142" s="26"/>
+      <c r="AB142" s="26"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="25" t="s">
         <v>281</v>
       </c>
-      <c r="B142" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D142" s="16" t="s">
+      <c r="B143" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="C143" s="26"/>
+      <c r="D143" s="15" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="22" t="s">
+      <c r="E143" s="26"/>
+      <c r="F143" s="26"/>
+      <c r="G143" s="26"/>
+      <c r="H143" s="26"/>
+      <c r="I143" s="26"/>
+      <c r="J143" s="26"/>
+      <c r="K143" s="26"/>
+      <c r="L143" s="26"/>
+      <c r="M143" s="26"/>
+      <c r="N143" s="26"/>
+      <c r="O143" s="26"/>
+      <c r="P143" s="26"/>
+      <c r="Q143" s="26"/>
+      <c r="R143" s="26"/>
+      <c r="S143" s="26"/>
+      <c r="T143" s="26"/>
+      <c r="U143" s="26"/>
+      <c r="V143" s="26"/>
+      <c r="W143" s="26"/>
+      <c r="X143" s="26"/>
+      <c r="Y143" s="26"/>
+      <c r="Z143" s="26"/>
+      <c r="AA143" s="26"/>
+      <c r="AB143" s="26"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="25" t="s">
         <v>283</v>
       </c>
-      <c r="B143" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D143" s="16" t="s">
+      <c r="B144" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="C144" s="26"/>
+      <c r="D144" s="15" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="22" t="s">
+      <c r="E144" s="26"/>
+      <c r="F144" s="26"/>
+      <c r="G144" s="26"/>
+      <c r="H144" s="26"/>
+      <c r="I144" s="26"/>
+      <c r="J144" s="26"/>
+      <c r="K144" s="26"/>
+      <c r="L144" s="26"/>
+      <c r="M144" s="26"/>
+      <c r="N144" s="26"/>
+      <c r="O144" s="26"/>
+      <c r="P144" s="26"/>
+      <c r="Q144" s="26"/>
+      <c r="R144" s="26"/>
+      <c r="S144" s="26"/>
+      <c r="T144" s="26"/>
+      <c r="U144" s="26"/>
+      <c r="V144" s="26"/>
+      <c r="W144" s="26"/>
+      <c r="X144" s="26"/>
+      <c r="Y144" s="26"/>
+      <c r="Z144" s="26"/>
+      <c r="AA144" s="26"/>
+      <c r="AB144" s="26"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="19" t="s">
         <v>285</v>
       </c>
-      <c r="B144" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D144" s="16" t="s">
+      <c r="B145" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D145" s="15" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="22" t="s">
+    <row r="146">
+      <c r="A146" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="B145" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D145" s="16" t="s">
+      <c r="B146" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D146" s="15" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="22" t="s">
+    <row r="147">
+      <c r="A147" s="19" t="s">
         <v>289</v>
       </c>
-      <c r="B146" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D146" s="16" t="s">
+      <c r="B147" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D147" s="15" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="22" t="s">
+    <row r="148">
+      <c r="A148" s="19" t="s">
         <v>291</v>
       </c>
-      <c r="B147" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D147" s="16" t="s">
+      <c r="B148" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D148" s="15" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="22" t="s">
+    <row r="149">
+      <c r="A149" s="19" t="s">
         <v>293</v>
       </c>
-      <c r="B148" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D148" s="16" t="s">
+      <c r="B149" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D149" s="15" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="22" t="s">
+    <row r="150">
+      <c r="A150" s="19" t="s">
         <v>295</v>
       </c>
-      <c r="B149" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D149" s="16" t="s">
+      <c r="B150" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D150" s="15" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="22" t="s">
+    <row r="151">
+      <c r="A151" s="19" t="s">
         <v>297</v>
       </c>
-      <c r="B150" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D150" s="16" t="s">
+      <c r="B151" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D151" s="15" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="22" t="s">
+    <row r="152">
+      <c r="A152" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="B151" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D151" s="16" t="s">
+      <c r="B152" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D152" s="15" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="22" t="s">
+    <row r="153">
+      <c r="A153" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="B152" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D152" s="24" t="s">
+      <c r="B153" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D153" s="15" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="22" t="s">
+    <row r="154">
+      <c r="A154" s="19" t="s">
         <v>303</v>
       </c>
-      <c r="B153" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D153" s="16" t="s">
+      <c r="B154" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D154" s="15" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="22" t="s">
+    <row r="155">
+      <c r="A155" s="19" t="s">
         <v>305</v>
       </c>
-      <c r="B154" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D154" s="16" t="s">
+      <c r="B155" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D155" s="15" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="22" t="s">
+    <row r="156">
+      <c r="A156" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="B155" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D155" s="16" t="s">
+      <c r="B156" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D156" s="15" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="22" t="s">
+    <row r="157">
+      <c r="A157" s="19" t="s">
         <v>309</v>
       </c>
-      <c r="B156" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D156" s="16" t="s">
+      <c r="B157" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D157" s="15" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="22" t="s">
+    <row r="158">
+      <c r="A158" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="B157" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D157" s="16" t="s">
+      <c r="B158" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D158" s="15" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="22" t="s">
+    <row r="159">
+      <c r="A159" s="19" t="s">
         <v>313</v>
       </c>
-      <c r="B158" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D158" s="16" t="s">
+      <c r="B159" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D159" s="15" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="22" t="s">
+    <row r="160">
+      <c r="A160" s="19" t="s">
         <v>315</v>
       </c>
-      <c r="B159" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D159" s="16" t="s">
+      <c r="B160" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D160" s="15" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="22" t="s">
+    <row r="161">
+      <c r="A161" s="19" t="s">
         <v>317</v>
       </c>
-      <c r="B160" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D160" s="24" t="s">
+      <c r="B161" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D161" s="23" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="22" t="s">
+    <row r="162">
+      <c r="A162" s="19" t="s">
         <v>319</v>
       </c>
-      <c r="B161" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D161" s="16" t="s">
+      <c r="B162" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D162" s="15" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="22" t="s">
+    <row r="163">
+      <c r="A163" s="19" t="s">
         <v>321</v>
       </c>
-      <c r="B162" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D162" s="16" t="s">
+      <c r="B163" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D163" s="15" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="22" t="s">
+    <row r="164">
+      <c r="A164" s="19" t="s">
         <v>323</v>
       </c>
-      <c r="B163" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D163" s="16" t="s">
+      <c r="B164" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D164" s="15" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="22" t="s">
+    <row r="165">
+      <c r="A165" s="19" t="s">
         <v>325</v>
       </c>
-      <c r="B164" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D164" s="16" t="s">
+      <c r="B165" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D165" s="15" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="22" t="s">
+    <row r="166">
+      <c r="A166" s="19" t="s">
         <v>327</v>
       </c>
-      <c r="B165" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D165" s="24" t="s">
+      <c r="B166" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D166" s="15" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="22" t="s">
+    <row r="167">
+      <c r="A167" s="19" t="s">
         <v>329</v>
       </c>
-      <c r="B166" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D166" s="16" t="s">
+      <c r="B167" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D167" s="15" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="22" t="s">
+    <row r="168">
+      <c r="A168" s="19" t="s">
         <v>331</v>
       </c>
-      <c r="B167" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D167" s="16" t="s">
+      <c r="B168" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D168" s="15" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="22" t="s">
+    <row r="169">
+      <c r="A169" s="19" t="s">
         <v>333</v>
       </c>
-      <c r="B168" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D168" s="16" t="s">
+      <c r="B169" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D169" s="23" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="22" t="s">
+    <row r="170">
+      <c r="A170" s="19" t="s">
         <v>335</v>
       </c>
-      <c r="B169" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D169" s="16" t="s">
+      <c r="B170" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D170" s="15" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="22" t="s">
+    <row r="171">
+      <c r="A171" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="B170" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D170" s="16" t="s">
+      <c r="B171" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D171" s="15" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="22" t="s">
+    <row r="172">
+      <c r="A172" s="19" t="s">
         <v>339</v>
       </c>
-      <c r="B171" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D171" s="16" t="s">
+      <c r="B172" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D172" s="15" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="22" t="s">
+    <row r="173">
+      <c r="A173" s="19" t="s">
         <v>341</v>
       </c>
-      <c r="B172" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D172" s="16" t="s">
+      <c r="B173" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D173" s="15" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="22" t="s">
+    <row r="174">
+      <c r="A174" s="19" t="s">
         <v>343</v>
       </c>
-      <c r="B173" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D173" s="24" t="s">
+      <c r="B174" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D174" s="23" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="22" t="s">
+    <row r="175">
+      <c r="A175" s="19" t="s">
         <v>345</v>
       </c>
-      <c r="B174" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D174" s="16" t="s">
+      <c r="B175" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D175" s="15" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="22" t="s">
+    <row r="176">
+      <c r="A176" s="19" t="s">
         <v>347</v>
       </c>
-      <c r="B175" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D175" s="16" t="s">
+      <c r="B176" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D176" s="15" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="22" t="s">
+    <row r="177">
+      <c r="A177" s="19" t="s">
         <v>349</v>
       </c>
-      <c r="B176" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D176" s="18" t="s">
+      <c r="B177" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D177" s="15" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="22" t="s">
+    <row r="178">
+      <c r="A178" s="19" t="s">
         <v>351</v>
       </c>
-      <c r="B177" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D177" s="16" t="s">
+      <c r="B178" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D178" s="15" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="22" t="s">
+    <row r="179">
+      <c r="A179" s="19" t="s">
         <v>353</v>
       </c>
-      <c r="B178" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D178" s="16" t="s">
+      <c r="B179" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D179" s="15" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="22" t="s">
+    <row r="180">
+      <c r="A180" s="19" t="s">
         <v>355</v>
       </c>
-      <c r="B179" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D179" s="16" t="s">
+      <c r="B180" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D180" s="15" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="22" t="s">
+    <row r="181">
+      <c r="A181" s="19" t="s">
         <v>357</v>
       </c>
-      <c r="B180" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D180" s="16" t="s">
+      <c r="B181" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D181" s="15" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="22" t="s">
+    <row r="182">
+      <c r="A182" s="19" t="s">
         <v>359</v>
       </c>
-      <c r="B181" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D181" s="16" t="s">
+      <c r="B182" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D182" s="23" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="22" t="s">
+    <row r="183">
+      <c r="A183" s="19" t="s">
         <v>361</v>
       </c>
-      <c r="B182" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D182" s="16" t="s">
+      <c r="B183" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D183" s="15" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="22" t="s">
+    <row r="184">
+      <c r="A184" s="19" t="s">
         <v>363</v>
       </c>
-      <c r="B183" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D183" s="16" t="s">
+      <c r="B184" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D184" s="15" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="22" t="s">
+    <row r="185">
+      <c r="A185" s="19" t="s">
         <v>365</v>
       </c>
-      <c r="B184" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D184" s="16" t="s">
+      <c r="B185" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D185" s="27" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="22" t="s">
+    <row r="186">
+      <c r="A186" s="19" t="s">
         <v>367</v>
       </c>
-      <c r="B185" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D185" s="16" t="s">
+      <c r="B186" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D186" s="15" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="22" t="s">
+    <row r="187">
+      <c r="A187" s="19" t="s">
         <v>369</v>
       </c>
-      <c r="B186" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D186" s="24" t="s">
+      <c r="B187" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D187" s="15" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="22" t="s">
+    <row r="188">
+      <c r="A188" s="19" t="s">
         <v>371</v>
       </c>
-      <c r="B187" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D187" s="16" t="s">
+      <c r="B188" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D188" s="15" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="22" t="s">
+    <row r="189">
+      <c r="A189" s="19" t="s">
         <v>373</v>
       </c>
-      <c r="B188" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D188" s="16" t="s">
+      <c r="B189" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D189" s="15" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="22" t="s">
+    <row r="190">
+      <c r="A190" s="19" t="s">
         <v>375</v>
       </c>
-      <c r="B189" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D189" s="16" t="s">
+      <c r="B190" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D190" s="15" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="22" t="s">
+    <row r="191">
+      <c r="A191" s="19" t="s">
         <v>377</v>
       </c>
-      <c r="B190" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D190" s="16" t="s">
+      <c r="B191" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D191" s="15" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="22" t="s">
+    <row r="192">
+      <c r="A192" s="19" t="s">
         <v>379</v>
       </c>
-      <c r="B191" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D191" s="16" t="s">
+      <c r="B192" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D192" s="15" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="22" t="s">
+    <row r="193">
+      <c r="A193" s="19" t="s">
         <v>381</v>
       </c>
-      <c r="B192" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D192" s="3" t="s">
+      <c r="B193" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D193" s="15" t="s">
         <v>382</v>
       </c>
-      <c r="E192" s="27"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="22" t="s">
+    </row>
+    <row r="194">
+      <c r="A194" s="19" t="s">
         <v>383</v>
       </c>
-      <c r="B193" s="28" t="s">
-        <v>219</v>
-      </c>
-      <c r="D193" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="E193" s="27" t="s">
+      <c r="B194" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D194" s="15" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="22" t="s">
+    <row r="195">
+      <c r="A195" s="19" t="s">
         <v>385</v>
       </c>
-      <c r="B194" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D194" s="16" t="s">
+      <c r="B195" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D195" s="23" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="22" t="s">
+    <row r="196">
+      <c r="A196" s="19" t="s">
         <v>387</v>
       </c>
-      <c r="B195" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D195" s="16" t="s">
+      <c r="B196" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D196" s="15" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="22" t="s">
+    <row r="197">
+      <c r="A197" s="19" t="s">
         <v>389</v>
       </c>
-      <c r="B196" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D196" s="16" t="s">
+      <c r="B197" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D197" s="15" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="22" t="s">
+    <row r="198">
+      <c r="A198" s="19" t="s">
         <v>391</v>
       </c>
-      <c r="B197" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D197" s="16" t="s">
+      <c r="B198" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D198" s="15" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="22" t="s">
+    <row r="199">
+      <c r="A199" s="19" t="s">
         <v>393</v>
       </c>
-      <c r="B198" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D198" s="16" t="s">
+      <c r="B199" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D199" s="15" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="22" t="s">
+    <row r="200">
+      <c r="A200" s="19" t="s">
         <v>395</v>
       </c>
-      <c r="B199" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D199" s="16" t="s">
+      <c r="B200" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D200" s="15" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="22" t="s">
+    <row r="201">
+      <c r="A201" s="19" t="s">
         <v>397</v>
       </c>
-      <c r="B200" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D200" s="16" t="s">
+      <c r="B201" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D201" s="3" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="22" t="s">
+      <c r="E201" s="28"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="19" t="s">
         <v>399</v>
       </c>
-      <c r="B201" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D201" s="16" t="s">
+      <c r="B202" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="E202" s="28" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="22" t="s">
+    <row r="203">
+      <c r="A203" s="19" t="s">
         <v>401</v>
       </c>
-      <c r="B202" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D202" s="16" t="s">
+      <c r="B203" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D203" s="15" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="22" t="s">
+    <row r="204">
+      <c r="A204" s="19" t="s">
         <v>403</v>
       </c>
-      <c r="B203" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D203" s="16" t="s">
+      <c r="B204" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D204" s="15" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="22" t="s">
+    <row r="205">
+      <c r="A205" s="19" t="s">
         <v>405</v>
       </c>
-      <c r="B204" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D204" s="16" t="s">
+      <c r="B205" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D205" s="15" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="22" t="s">
+    <row r="206">
+      <c r="A206" s="19" t="s">
         <v>407</v>
       </c>
-      <c r="B205" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D205" s="16" t="s">
+      <c r="B206" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D206" s="15" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="22" t="s">
+    <row r="207">
+      <c r="A207" s="19" t="s">
         <v>409</v>
       </c>
-      <c r="B206" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D206" s="16" t="s">
+      <c r="B207" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D207" s="15" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="22" t="s">
+    <row r="208">
+      <c r="A208" s="19" t="s">
         <v>411</v>
       </c>
-      <c r="B207" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D207" s="16" t="s">
+      <c r="B208" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D208" s="15" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="22" t="s">
+    <row r="209">
+      <c r="A209" s="19" t="s">
         <v>413</v>
       </c>
-      <c r="B208" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D208" s="16" t="s">
+      <c r="B209" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D209" s="15" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="22" t="s">
+    <row r="210">
+      <c r="A210" s="19" t="s">
         <v>415</v>
       </c>
-      <c r="B209" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D209" s="16" t="s">
+      <c r="B210" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D210" s="15" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="22" t="s">
+    <row r="211">
+      <c r="A211" s="19" t="s">
         <v>417</v>
       </c>
-      <c r="B210" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D210" s="16" t="s">
+      <c r="B211" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D211" s="15" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="22" t="s">
+    <row r="212">
+      <c r="A212" s="19" t="s">
         <v>419</v>
       </c>
-      <c r="B211" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D211" s="16" t="s">
+      <c r="B212" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D212" s="15" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="22" t="s">
+    <row r="213">
+      <c r="A213" s="19" t="s">
         <v>421</v>
       </c>
-      <c r="B212" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D212" s="16" t="s">
+      <c r="B213" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D213" s="15" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="22" t="s">
+    <row r="214">
+      <c r="A214" s="19" t="s">
         <v>423</v>
       </c>
-      <c r="B213" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D213" s="16" t="s">
+      <c r="B214" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D214" s="15" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="22" t="s">
+    <row r="215">
+      <c r="A215" s="19" t="s">
         <v>425</v>
       </c>
-      <c r="B214" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D214" s="16" t="s">
+      <c r="B215" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D215" s="15" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="22" t="s">
+    <row r="216">
+      <c r="A216" s="19" t="s">
         <v>427</v>
       </c>
-      <c r="B215" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D215" s="16" t="s">
+      <c r="B216" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D216" s="15" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="22" t="s">
+    <row r="217">
+      <c r="A217" s="19" t="s">
         <v>429</v>
       </c>
-      <c r="B216" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D216" s="16" t="s">
+      <c r="B217" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D217" s="15" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="22" t="s">
+    <row r="218">
+      <c r="A218" s="19" t="s">
         <v>431</v>
       </c>
-      <c r="B217" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D217" s="16" t="s">
+      <c r="B218" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D218" s="15" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="22" t="s">
+    <row r="219">
+      <c r="A219" s="19" t="s">
         <v>433</v>
       </c>
-      <c r="B218" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D218" s="29" t="s">
+      <c r="B219" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D219" s="15" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="22" t="s">
+    <row r="220">
+      <c r="A220" s="19" t="s">
         <v>435</v>
       </c>
-      <c r="B219" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D219" s="16" t="s">
+      <c r="B220" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D220" s="15" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="22" t="s">
+    <row r="221">
+      <c r="A221" s="19" t="s">
         <v>437</v>
       </c>
-      <c r="B220" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D220" s="16" t="s">
+      <c r="B221" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D221" s="15" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="22" t="s">
+    <row r="222">
+      <c r="A222" s="19" t="s">
         <v>439</v>
       </c>
-      <c r="B221" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D221" s="16" t="s">
+      <c r="B222" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D222" s="15" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="22" t="s">
+    <row r="223">
+      <c r="A223" s="19" t="s">
         <v>441</v>
       </c>
-      <c r="B222" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D222" s="16" t="s">
+      <c r="B223" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D223" s="15" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="22" t="s">
+    <row r="224">
+      <c r="A224" s="19" t="s">
         <v>443</v>
       </c>
-      <c r="B223" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D223" s="16" t="s">
+      <c r="B224" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D224" s="15" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="22" t="s">
+    <row r="225">
+      <c r="A225" s="19" t="s">
         <v>445</v>
       </c>
-      <c r="B224" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D224" s="16" t="s">
+      <c r="B225" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D225" s="15" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="22" t="s">
+    <row r="226">
+      <c r="A226" s="19" t="s">
         <v>447</v>
       </c>
-      <c r="B225" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D225" s="16" t="s">
+      <c r="B226" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D226" s="15" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="22" t="s">
+    <row r="227">
+      <c r="A227" s="19" t="s">
         <v>449</v>
       </c>
-      <c r="B226" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D226" s="16" t="s">
+      <c r="B227" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D227" s="15" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="22" t="s">
+    <row r="228">
+      <c r="A228" s="19" t="s">
         <v>451</v>
       </c>
-      <c r="B227" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D227" s="16" t="s">
+      <c r="B228" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D228" s="29" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="22" t="s">
+    <row r="229">
+      <c r="A229" s="19" t="s">
         <v>453</v>
       </c>
-      <c r="B228" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D228" s="16" t="s">
+      <c r="B229" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D229" s="15" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="22" t="s">
+    <row r="230">
+      <c r="A230" s="19" t="s">
         <v>455</v>
       </c>
-      <c r="B229" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D229" s="16" t="s">
+      <c r="B230" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D230" s="15" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="22" t="s">
+    <row r="231">
+      <c r="A231" s="19" t="s">
         <v>457</v>
       </c>
-      <c r="B230" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D230" s="16" t="s">
+      <c r="B231" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D231" s="15" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="22" t="s">
+    <row r="232">
+      <c r="A232" s="19" t="s">
         <v>459</v>
       </c>
-      <c r="B231" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D231" s="16" t="s">
+      <c r="B232" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D232" s="15" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="22" t="s">
+    <row r="233">
+      <c r="A233" s="19" t="s">
         <v>461</v>
       </c>
-      <c r="B232" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D232" s="16" t="s">
+      <c r="B233" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D233" s="15" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="22" t="s">
+    <row r="234">
+      <c r="A234" s="19" t="s">
         <v>463</v>
       </c>
-      <c r="B233" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D233" s="16" t="s">
+      <c r="B234" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D234" s="15" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="22" t="s">
+    <row r="235">
+      <c r="A235" s="19" t="s">
         <v>465</v>
       </c>
-      <c r="B234" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D234" s="16" t="s">
+      <c r="B235" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D235" s="15" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="22" t="s">
+    <row r="236">
+      <c r="A236" s="19" t="s">
         <v>467</v>
       </c>
-      <c r="B235" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D235" s="16" t="s">
+      <c r="B236" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D236" s="15" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="22" t="s">
+    <row r="237">
+      <c r="A237" s="19" t="s">
         <v>469</v>
       </c>
-      <c r="B236" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D236" s="16" t="s">
+      <c r="B237" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D237" s="15" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="22" t="s">
+    <row r="238">
+      <c r="A238" s="19" t="s">
         <v>471</v>
       </c>
-      <c r="B237" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D237" s="16" t="s">
+      <c r="B238" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D238" s="15" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="22" t="s">
+    <row r="239">
+      <c r="A239" s="19" t="s">
         <v>473</v>
       </c>
-      <c r="B238" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D238" s="16" t="s">
+      <c r="B239" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D239" s="15" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="22" t="s">
+    <row r="240">
+      <c r="A240" s="19" t="s">
         <v>475</v>
       </c>
-      <c r="B239" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D239" s="16" t="s">
+      <c r="B240" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D240" s="15" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="22" t="s">
+    <row r="241">
+      <c r="A241" s="19" t="s">
         <v>477</v>
       </c>
-      <c r="B240" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D240" s="16" t="s">
+      <c r="B241" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D241" s="15" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="22" t="s">
+    <row r="242">
+      <c r="A242" s="19" t="s">
         <v>479</v>
       </c>
-      <c r="B241" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D241" s="16" t="s">
+      <c r="B242" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D242" s="15" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="22" t="s">
+    <row r="243">
+      <c r="A243" s="19" t="s">
         <v>481</v>
       </c>
-      <c r="B242" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D242" s="16" t="s">
+      <c r="B243" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D243" s="15" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="22" t="s">
+    <row r="244">
+      <c r="A244" s="19" t="s">
         <v>483</v>
       </c>
-      <c r="B243" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D243" s="16" t="s">
+      <c r="B244" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D244" s="15" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="22" t="s">
+    <row r="245">
+      <c r="A245" s="19" t="s">
         <v>485</v>
       </c>
-      <c r="B244" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D244" s="16" t="s">
+      <c r="B245" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D245" s="15" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="22" t="s">
+    <row r="246">
+      <c r="A246" s="19" t="s">
         <v>487</v>
       </c>
-      <c r="B245" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D245" s="16" t="s">
+      <c r="B246" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D246" s="15" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="22" t="s">
+    <row r="247">
+      <c r="A247" s="19" t="s">
         <v>489</v>
       </c>
-      <c r="B246" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D246" s="16" t="s">
+      <c r="B247" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D247" s="15" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="22" t="s">
+    <row r="248">
+      <c r="A248" s="19" t="s">
         <v>491</v>
       </c>
-      <c r="B247" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D247" s="16" t="s">
+      <c r="B248" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D248" s="15" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="22" t="s">
+    <row r="249">
+      <c r="A249" s="19" t="s">
         <v>493</v>
       </c>
-      <c r="B248" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D248" s="16" t="s">
+      <c r="B249" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D249" s="15" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="22" t="s">
+    <row r="250">
+      <c r="A250" s="19" t="s">
         <v>495</v>
       </c>
-      <c r="B249" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D249" s="16" t="s">
+      <c r="B250" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D250" s="15" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="22" t="s">
+    <row r="251">
+      <c r="A251" s="19" t="s">
         <v>497</v>
       </c>
-      <c r="B250" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D250" s="16" t="s">
+      <c r="B251" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D251" s="15" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="22" t="s">
+    <row r="252">
+      <c r="A252" s="19" t="s">
         <v>499</v>
       </c>
-      <c r="B251" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D251" s="16" t="s">
+      <c r="B252" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D252" s="15" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="22" t="s">
+    <row r="253">
+      <c r="A253" s="19" t="s">
         <v>501</v>
       </c>
-      <c r="B252" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D252" s="16" t="s">
+      <c r="B253" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D253" s="15" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="22" t="s">
+    <row r="254">
+      <c r="A254" s="19" t="s">
         <v>503</v>
       </c>
-      <c r="B253" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D253" s="16" t="s">
+      <c r="B254" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D254" s="15" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="22" t="s">
+    <row r="255">
+      <c r="A255" s="19" t="s">
         <v>505</v>
       </c>
-      <c r="B254" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D254" s="16" t="s">
+      <c r="B255" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D255" s="15" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" s="22" t="s">
+    <row r="256">
+      <c r="A256" s="19" t="s">
         <v>507</v>
       </c>
-      <c r="B255" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="C255" s="22"/>
-      <c r="D255" s="30" t="s">
+      <c r="B256" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D256" s="15" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" s="22" t="s">
+    <row r="257">
+      <c r="A257" s="19" t="s">
         <v>509</v>
       </c>
-      <c r="B256" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="C256" s="22" t="s">
+      <c r="B257" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D257" s="15" t="s">
         <v>510</v>
       </c>
-      <c r="D256" s="16"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="22" t="s">
+    </row>
+    <row r="258">
+      <c r="A258" s="19" t="s">
         <v>511</v>
       </c>
-      <c r="B257" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="C257" s="22" t="s">
-        <v>510</v>
-      </c>
-      <c r="D257" s="16" t="s">
+      <c r="B258" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D258" s="15" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" s="22" t="s">
+    <row r="259">
+      <c r="A259" s="19" t="s">
         <v>513</v>
       </c>
-      <c r="B258" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="C258" s="22" t="s">
-        <v>510</v>
-      </c>
-      <c r="D258" s="31" t="s">
+      <c r="B259" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D259" s="15" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="22" t="s">
+    <row r="260">
+      <c r="A260" s="19" t="s">
         <v>515</v>
       </c>
-      <c r="B259" s="22" t="s">
+      <c r="B260" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D260" s="15" t="s">
         <v>516</v>
       </c>
-      <c r="C259" s="22"/>
-      <c r="D259" s="32"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="22" t="s">
+    </row>
+    <row r="261">
+      <c r="A261" s="19" t="s">
         <v>517</v>
       </c>
-      <c r="B260" s="22" t="s">
-        <v>516</v>
-      </c>
-      <c r="C260" s="22" t="s">
+      <c r="B261" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D261" s="15" t="s">
         <v>518</v>
       </c>
-      <c r="D260" s="32"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="22" t="s">
+    </row>
+    <row r="262">
+      <c r="A262" s="19" t="s">
         <v>519</v>
       </c>
-      <c r="B261" s="22" t="s">
-        <v>516</v>
-      </c>
-      <c r="C261" s="22" t="s">
+      <c r="B262" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D262" s="15" t="s">
         <v>520</v>
       </c>
-      <c r="D261" s="32"/>
-    </row>
-    <row r="262">
-      <c r="A262" s="22" t="s">
+    </row>
+    <row r="263">
+      <c r="A263" s="19" t="s">
         <v>521</v>
       </c>
-      <c r="B262" s="22" t="s">
-        <v>516</v>
-      </c>
-      <c r="C262" s="22" t="s">
+      <c r="B263" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D263" s="15" t="s">
         <v>522</v>
       </c>
-      <c r="D262" s="32"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="22" t="s">
+    </row>
+    <row r="264">
+      <c r="A264" s="19" t="s">
         <v>523</v>
       </c>
-      <c r="B263" s="22" t="s">
-        <v>516</v>
-      </c>
-      <c r="C263" s="22" t="s">
+      <c r="B264" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D264" s="15" t="s">
         <v>524</v>
       </c>
-      <c r="D263" s="32"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="22" t="s">
+    </row>
+    <row r="265">
+      <c r="A265" s="19" t="s">
         <v>525</v>
       </c>
-      <c r="B264" s="22" t="s">
-        <v>516</v>
-      </c>
-      <c r="C264" s="22" t="s">
+      <c r="B265" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D265" s="15" t="s">
         <v>526</v>
       </c>
-      <c r="D264" s="33"/>
-    </row>
-    <row r="265">
-      <c r="D265" s="32"/>
     </row>
     <row r="266">
-      <c r="D266" s="32"/>
+      <c r="A266" s="19" t="s">
+        <v>527</v>
+      </c>
+      <c r="B266" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="C266" s="19"/>
+      <c r="D266" s="30" t="s">
+        <v>528</v>
+      </c>
     </row>
     <row r="267">
-      <c r="D267" s="32"/>
+      <c r="A267" s="19" t="s">
+        <v>529</v>
+      </c>
+      <c r="B267" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="C267" s="19" t="s">
+        <v>530</v>
+      </c>
+      <c r="D267" s="15"/>
     </row>
     <row r="268">
-      <c r="D268" s="34"/>
+      <c r="A268" s="19" t="s">
+        <v>531</v>
+      </c>
+      <c r="B268" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="C268" s="19" t="s">
+        <v>530</v>
+      </c>
+      <c r="D268" s="15" t="s">
+        <v>532</v>
+      </c>
     </row>
     <row r="269">
-      <c r="D269" s="32"/>
+      <c r="A269" s="19" t="s">
+        <v>533</v>
+      </c>
+      <c r="B269" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="C269" s="19" t="s">
+        <v>530</v>
+      </c>
+      <c r="D269" s="31" t="s">
+        <v>534</v>
+      </c>
     </row>
     <row r="270">
+      <c r="A270" s="19" t="s">
+        <v>535</v>
+      </c>
+      <c r="B270" s="19" t="s">
+        <v>536</v>
+      </c>
+      <c r="C270" s="19"/>
       <c r="D270" s="32"/>
     </row>
     <row r="271">
+      <c r="A271" s="19" t="s">
+        <v>537</v>
+      </c>
+      <c r="B271" s="33" t="s">
+        <v>536</v>
+      </c>
       <c r="D271" s="32"/>
     </row>
     <row r="272">
-      <c r="D272" s="34"/>
+      <c r="A272" s="19" t="s">
+        <v>538</v>
+      </c>
+      <c r="B272" s="33" t="s">
+        <v>536</v>
+      </c>
+      <c r="C272" s="19" t="s">
+        <v>539</v>
+      </c>
+      <c r="D272" s="32"/>
     </row>
     <row r="273">
-      <c r="D273" s="35"/>
+      <c r="A273" s="19" t="s">
+        <v>540</v>
+      </c>
+      <c r="B273" s="33" t="s">
+        <v>536</v>
+      </c>
+      <c r="C273" s="19" t="s">
+        <v>541</v>
+      </c>
+      <c r="D273" s="32"/>
     </row>
     <row r="274">
+      <c r="A274" s="19" t="s">
+        <v>542</v>
+      </c>
+      <c r="B274" s="33" t="s">
+        <v>536</v>
+      </c>
+      <c r="C274" s="19" t="s">
+        <v>543</v>
+      </c>
       <c r="D274" s="32"/>
     </row>
     <row r="275">
+      <c r="A275" s="19" t="s">
+        <v>544</v>
+      </c>
+      <c r="B275" s="33" t="s">
+        <v>536</v>
+      </c>
+      <c r="C275" s="19" t="s">
+        <v>545</v>
+      </c>
       <c r="D275" s="32"/>
     </row>
     <row r="276">
+      <c r="A276" s="19" t="s">
+        <v>546</v>
+      </c>
+      <c r="B276" s="33" t="s">
+        <v>536</v>
+      </c>
+      <c r="C276" s="33" t="s">
+        <v>547</v>
+      </c>
       <c r="D276" s="32"/>
     </row>
     <row r="277">
+      <c r="A277" s="19" t="s">
+        <v>548</v>
+      </c>
+      <c r="B277" s="33" t="s">
+        <v>536</v>
+      </c>
+      <c r="C277" s="19" t="s">
+        <v>549</v>
+      </c>
       <c r="D277" s="34"/>
     </row>
     <row r="278">
+      <c r="A278" s="19" t="s">
+        <v>550</v>
+      </c>
+      <c r="B278" s="33" t="s">
+        <v>551</v>
+      </c>
       <c r="D278" s="32"/>
     </row>
     <row r="279">
+      <c r="A279" s="19" t="s">
+        <v>552</v>
+      </c>
+      <c r="B279" s="33" t="s">
+        <v>551</v>
+      </c>
+      <c r="C279" s="19" t="s">
+        <v>553</v>
+      </c>
       <c r="D279" s="32"/>
     </row>
     <row r="280">
+      <c r="A280" s="19" t="s">
+        <v>554</v>
+      </c>
+      <c r="B280" s="33" t="s">
+        <v>551</v>
+      </c>
+      <c r="C280" s="19" t="s">
+        <v>555</v>
+      </c>
       <c r="D280" s="32"/>
     </row>
     <row r="281">
-      <c r="D281" s="34"/>
+      <c r="D281" s="35"/>
     </row>
     <row r="282">
+      <c r="C282" s="33"/>
       <c r="D282" s="32"/>
     </row>
     <row r="283">
-      <c r="D283" s="36"/>
+      <c r="C283" s="33"/>
+      <c r="D283" s="32"/>
     </row>
     <row r="284">
-      <c r="D284" s="34"/>
+      <c r="D284" s="32"/>
     </row>
     <row r="285">
-      <c r="D285" s="34"/>
+      <c r="D285" s="35"/>
     </row>
     <row r="286">
       <c r="D286" s="36"/>
     </row>
     <row r="287">
-      <c r="D287" s="36"/>
+      <c r="D287" s="32"/>
     </row>
     <row r="288">
-      <c r="D288" s="36"/>
+      <c r="D288" s="32"/>
     </row>
     <row r="289">
-      <c r="D289" s="36"/>
+      <c r="D289" s="32"/>
     </row>
     <row r="290">
-      <c r="D290" s="34"/>
+      <c r="D290" s="35"/>
     </row>
     <row r="291">
-      <c r="D291" s="37"/>
+      <c r="D291" s="32"/>
     </row>
     <row r="292">
-      <c r="D292" s="36"/>
+      <c r="D292" s="32"/>
     </row>
     <row r="293">
-      <c r="D293" s="36"/>
+      <c r="D293" s="32"/>
     </row>
     <row r="294">
-      <c r="D294" s="34"/>
+      <c r="D294" s="35"/>
     </row>
     <row r="295">
-      <c r="D295" s="36"/>
+      <c r="D295" s="32"/>
     </row>
     <row r="296">
-      <c r="D296" s="36"/>
+      <c r="D296" s="37"/>
     </row>
     <row r="297">
-      <c r="D297" s="34"/>
+      <c r="D297" s="35"/>
     </row>
     <row r="298">
-      <c r="D298" s="36"/>
+      <c r="D298" s="35"/>
     </row>
     <row r="299">
-      <c r="D299" s="36"/>
+      <c r="D299" s="37"/>
     </row>
     <row r="300">
-      <c r="D300" s="34"/>
+      <c r="D300" s="37"/>
     </row>
     <row r="301">
-      <c r="D301" s="34"/>
+      <c r="D301" s="37"/>
     </row>
     <row r="302">
-      <c r="D302" s="36"/>
+      <c r="D302" s="37"/>
     </row>
     <row r="303">
-      <c r="D303" s="36"/>
+      <c r="D303" s="35"/>
     </row>
     <row r="304">
-      <c r="D304" s="36"/>
+      <c r="D304" s="38"/>
     </row>
     <row r="305">
-      <c r="D305" s="34"/>
+      <c r="D305" s="37"/>
     </row>
     <row r="306">
-      <c r="D306" s="36"/>
+      <c r="D306" s="37"/>
     </row>
     <row r="307">
-      <c r="D307" s="36"/>
+      <c r="D307" s="35"/>
     </row>
     <row r="308">
-      <c r="D308" s="36"/>
+      <c r="D308" s="37"/>
     </row>
     <row r="309">
-      <c r="D309" s="36"/>
+      <c r="D309" s="37"/>
     </row>
     <row r="310">
-      <c r="D310" s="36"/>
+      <c r="D310" s="35"/>
     </row>
     <row r="311">
-      <c r="D311" s="36"/>
+      <c r="D311" s="37"/>
     </row>
     <row r="312">
-      <c r="D312" s="34"/>
+      <c r="D312" s="37"/>
     </row>
     <row r="313">
-      <c r="D313" s="36"/>
+      <c r="D313" s="35"/>
     </row>
     <row r="314">
-      <c r="D314" s="36"/>
+      <c r="D314" s="35"/>
     </row>
     <row r="315">
-      <c r="D315" s="34"/>
+      <c r="D315" s="37"/>
     </row>
     <row r="316">
-      <c r="D316" s="36"/>
+      <c r="D316" s="37"/>
     </row>
     <row r="317">
-      <c r="D317" s="36"/>
+      <c r="D317" s="37"/>
     </row>
     <row r="318">
-      <c r="D318" s="34"/>
+      <c r="D318" s="35"/>
     </row>
     <row r="319">
-      <c r="D319" s="34"/>
+      <c r="D319" s="37"/>
     </row>
     <row r="320">
-      <c r="D320" s="34"/>
+      <c r="D320" s="37"/>
     </row>
     <row r="321">
-      <c r="D321" s="36"/>
+      <c r="D321" s="37"/>
     </row>
     <row r="322">
-      <c r="D322" s="36"/>
+      <c r="D322" s="37"/>
     </row>
     <row r="323">
-      <c r="D323" s="34"/>
+      <c r="D323" s="37"/>
     </row>
     <row r="324">
-      <c r="D324" s="34"/>
+      <c r="D324" s="37"/>
     </row>
     <row r="325">
-      <c r="D325" s="36"/>
+      <c r="D325" s="35"/>
     </row>
     <row r="326">
-      <c r="D326" s="36"/>
+      <c r="D326" s="37"/>
     </row>
     <row r="327">
-      <c r="D327" s="36"/>
+      <c r="D327" s="37"/>
     </row>
     <row r="328">
-      <c r="D328" s="36"/>
+      <c r="D328" s="35"/>
     </row>
     <row r="329">
-      <c r="D329" s="34"/>
+      <c r="D329" s="37"/>
     </row>
     <row r="330">
-      <c r="D330" s="36"/>
+      <c r="D330" s="37"/>
     </row>
     <row r="331">
-      <c r="D331" s="34"/>
+      <c r="D331" s="35"/>
     </row>
     <row r="332">
-      <c r="D332" s="34"/>
+      <c r="D332" s="35"/>
     </row>
     <row r="333">
-      <c r="D333" s="36"/>
+      <c r="D333" s="35"/>
     </row>
     <row r="334">
-      <c r="D334" s="36"/>
+      <c r="D334" s="37"/>
     </row>
     <row r="335">
-      <c r="D335" s="36"/>
+      <c r="D335" s="37"/>
     </row>
     <row r="336">
-      <c r="D336" s="34"/>
+      <c r="D336" s="35"/>
     </row>
     <row r="337">
-      <c r="D337" s="34"/>
+      <c r="D337" s="35"/>
     </row>
     <row r="338">
-      <c r="D338" s="36"/>
+      <c r="D338" s="37"/>
     </row>
     <row r="339">
-      <c r="D339" s="36"/>
+      <c r="D339" s="37"/>
     </row>
     <row r="340">
       <c r="D340" s="37"/>
     </row>
     <row r="341">
-      <c r="D341" s="36"/>
+      <c r="D341" s="37"/>
     </row>
     <row r="342">
-      <c r="D342" s="36"/>
+      <c r="D342" s="35"/>
     </row>
     <row r="343">
-      <c r="D343" s="36"/>
+      <c r="D343" s="37"/>
     </row>
     <row r="344">
-      <c r="D344" s="36"/>
+      <c r="D344" s="35"/>
     </row>
     <row r="345">
-      <c r="D345" s="36"/>
+      <c r="D345" s="35"/>
     </row>
     <row r="346">
-      <c r="D346" s="36"/>
+      <c r="D346" s="37"/>
     </row>
     <row r="347">
-      <c r="D347" s="36"/>
+      <c r="D347" s="37"/>
     </row>
     <row r="348">
-      <c r="D348" s="36"/>
+      <c r="D348" s="37"/>
     </row>
     <row r="349">
-      <c r="D349" s="37"/>
+      <c r="D349" s="35"/>
     </row>
     <row r="350">
-      <c r="D350" s="36"/>
+      <c r="D350" s="35"/>
     </row>
     <row r="351">
-      <c r="D351" s="36"/>
+      <c r="D351" s="37"/>
     </row>
     <row r="352">
-      <c r="D352" s="36"/>
+      <c r="D352" s="37"/>
     </row>
     <row r="353">
-      <c r="D353" s="36"/>
+      <c r="D353" s="38"/>
     </row>
     <row r="354">
-      <c r="D354" s="36"/>
+      <c r="D354" s="37"/>
     </row>
     <row r="355">
-      <c r="D355" s="38"/>
+      <c r="D355" s="37"/>
     </row>
     <row r="356">
-      <c r="D356" s="38"/>
+      <c r="D356" s="37"/>
     </row>
     <row r="357">
-      <c r="D357" s="36"/>
+      <c r="D357" s="37"/>
     </row>
     <row r="358">
-      <c r="D358" s="39"/>
+      <c r="D358" s="37"/>
     </row>
     <row r="359">
-      <c r="D359" s="36"/>
+      <c r="D359" s="37"/>
     </row>
     <row r="360">
-      <c r="D360" s="36"/>
+      <c r="D360" s="37"/>
     </row>
     <row r="361">
-      <c r="D361" s="36"/>
+      <c r="D361" s="37"/>
     </row>
     <row r="362">
-      <c r="D362" s="36"/>
+      <c r="D362" s="38"/>
     </row>
     <row r="363">
-      <c r="D363" s="36"/>
+      <c r="D363" s="37"/>
     </row>
     <row r="364">
-      <c r="D364" s="36"/>
+      <c r="D364" s="37"/>
     </row>
     <row r="365">
-      <c r="D365" s="36"/>
+      <c r="D365" s="37"/>
     </row>
     <row r="366">
-      <c r="D366" s="36"/>
+      <c r="D366" s="37"/>
     </row>
     <row r="367">
-      <c r="D367" s="36"/>
+      <c r="D367" s="37"/>
     </row>
     <row r="368">
-      <c r="D368" s="36"/>
+      <c r="D368" s="39"/>
     </row>
     <row r="369">
       <c r="D369" s="39"/>
     </row>
     <row r="370">
-      <c r="D370" s="36"/>
+      <c r="D370" s="37"/>
     </row>
     <row r="371">
-      <c r="D371" s="36"/>
+      <c r="D371" s="40"/>
     </row>
     <row r="372">
-      <c r="D372" s="36"/>
+      <c r="D372" s="37"/>
     </row>
     <row r="373">
-      <c r="D373" s="36"/>
+      <c r="D373" s="37"/>
     </row>
     <row r="374">
-      <c r="D374" s="36"/>
+      <c r="D374" s="37"/>
     </row>
     <row r="375">
-      <c r="D375" s="36"/>
+      <c r="D375" s="37"/>
     </row>
     <row r="376">
-      <c r="D376" s="36"/>
+      <c r="D376" s="37"/>
     </row>
     <row r="377">
-      <c r="D377" s="36"/>
+      <c r="D377" s="37"/>
     </row>
     <row r="378">
-      <c r="D378" s="36"/>
+      <c r="D378" s="37"/>
     </row>
     <row r="379">
-      <c r="D379" s="36"/>
+      <c r="D379" s="37"/>
     </row>
     <row r="380">
-      <c r="D380" s="36"/>
+      <c r="D380" s="37"/>
     </row>
     <row r="381">
-      <c r="D381" s="36"/>
+      <c r="D381" s="37"/>
     </row>
     <row r="382">
-      <c r="D382" s="36"/>
+      <c r="D382" s="40"/>
     </row>
     <row r="383">
-      <c r="D383" s="40"/>
+      <c r="D383" s="37"/>
     </row>
     <row r="384">
-      <c r="D384" s="36"/>
+      <c r="D384" s="37"/>
     </row>
     <row r="385">
-      <c r="D385" s="36"/>
+      <c r="D385" s="37"/>
     </row>
     <row r="386">
-      <c r="D386" s="36"/>
+      <c r="D386" s="37"/>
     </row>
     <row r="387">
-      <c r="D387" s="36"/>
+      <c r="D387" s="37"/>
     </row>
     <row r="388">
-      <c r="D388" s="36"/>
+      <c r="D388" s="37"/>
     </row>
     <row r="389">
-      <c r="D389" s="39"/>
+      <c r="D389" s="37"/>
     </row>
     <row r="390">
-      <c r="D390" s="39"/>
+      <c r="D390" s="37"/>
     </row>
     <row r="391">
-      <c r="D391" s="36"/>
+      <c r="D391" s="37"/>
     </row>
     <row r="392">
-      <c r="D392" s="36"/>
+      <c r="D392" s="37"/>
     </row>
     <row r="393">
-      <c r="D393" s="36"/>
+      <c r="D393" s="37"/>
     </row>
     <row r="394">
       <c r="D394" s="37"/>
     </row>
     <row r="395">
-      <c r="D395" s="36"/>
+      <c r="D395" s="37"/>
     </row>
     <row r="396">
-      <c r="D396" s="36"/>
+      <c r="D396" s="41"/>
     </row>
     <row r="397">
-      <c r="D397" s="36"/>
+      <c r="D397" s="37"/>
     </row>
     <row r="398">
-      <c r="D398" s="36"/>
+      <c r="D398" s="37"/>
     </row>
     <row r="399">
-      <c r="D399" s="36"/>
+      <c r="D399" s="37"/>
     </row>
     <row r="400">
-      <c r="D400" s="36"/>
+      <c r="D400" s="37"/>
     </row>
     <row r="401">
       <c r="D401" s="37"/>
     </row>
     <row r="402">
-      <c r="D402" s="36"/>
+      <c r="D402" s="40"/>
     </row>
     <row r="403">
-      <c r="D403" s="36"/>
+      <c r="D403" s="40"/>
     </row>
     <row r="404">
-      <c r="D404" s="39"/>
+      <c r="D404" s="37"/>
     </row>
     <row r="405">
-      <c r="D405" s="41"/>
+      <c r="D405" s="37"/>
     </row>
     <row r="406">
-      <c r="D406" s="39"/>
+      <c r="D406" s="37"/>
     </row>
     <row r="407">
-      <c r="D407" s="39"/>
+      <c r="D407" s="38"/>
     </row>
     <row r="408">
-      <c r="D408" s="39"/>
+      <c r="D408" s="37"/>
     </row>
     <row r="409">
-      <c r="D409" s="39"/>
+      <c r="D409" s="37"/>
     </row>
     <row r="410">
-      <c r="D410" s="39"/>
+      <c r="D410" s="37"/>
     </row>
     <row r="411">
-      <c r="D411" s="39"/>
+      <c r="D411" s="37"/>
     </row>
     <row r="412">
-      <c r="D412" s="41"/>
+      <c r="D412" s="37"/>
     </row>
     <row r="413">
-      <c r="D413" s="41"/>
+      <c r="D413" s="37"/>
     </row>
     <row r="414">
-      <c r="D414" s="39"/>
+      <c r="D414" s="38"/>
     </row>
     <row r="415">
-      <c r="D415" s="39"/>
+      <c r="D415" s="37"/>
     </row>
     <row r="416">
-      <c r="D416" s="39"/>
+      <c r="D416" s="37"/>
     </row>
     <row r="417">
-      <c r="D417" s="39"/>
+      <c r="D417" s="40"/>
     </row>
     <row r="418">
-      <c r="D418" s="39"/>
+      <c r="D418" s="42"/>
     </row>
     <row r="419">
-      <c r="D419" s="39"/>
+      <c r="D419" s="40"/>
     </row>
     <row r="420">
-      <c r="D420" s="42"/>
+      <c r="D420" s="40"/>
     </row>
     <row r="421">
-      <c r="D421" s="39"/>
+      <c r="D421" s="40"/>
     </row>
     <row r="422">
-      <c r="D422" s="39"/>
+      <c r="D422" s="40"/>
     </row>
     <row r="423">
-      <c r="D423" s="39"/>
+      <c r="D423" s="40"/>
+    </row>
+    <row r="424">
+      <c r="D424" s="40"/>
+    </row>
+    <row r="425">
+      <c r="D425" s="42"/>
+    </row>
+    <row r="426">
+      <c r="D426" s="42"/>
+    </row>
+    <row r="427">
+      <c r="D427" s="40"/>
+    </row>
+    <row r="428">
+      <c r="D428" s="40"/>
+    </row>
+    <row r="429">
+      <c r="D429" s="40"/>
+    </row>
+    <row r="430">
+      <c r="D430" s="40"/>
+    </row>
+    <row r="431">
+      <c r="D431" s="40"/>
+    </row>
+    <row r="432">
+      <c r="D432" s="40"/>
+    </row>
+    <row r="433">
+      <c r="D433" s="43"/>
+    </row>
+    <row r="434">
+      <c r="D434" s="40"/>
+    </row>
+    <row r="435">
+      <c r="D435" s="40"/>
+    </row>
+    <row r="436">
+      <c r="D436" s="40"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId2" ref="G112"/>
+    <hyperlink r:id="rId2" ref="G117"/>
   </hyperlinks>
   <drawing r:id="rId3"/>
   <legacyDrawing r:id="rId4"/>
